--- a/data/한국_버추얼아이돌_전수조사_v8.xlsx
+++ b/data/한국_버추얼아이돌_전수조사_v8.xlsx
@@ -13,6 +13,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="데뷔예정·신규(2026)" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개인세(무소속) 기준안+시드" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개인세 수집PoC(3만+)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI 생성형 아티스트" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'버추얼 그룹 전수목록'!$A$3:$H$126</definedName>
@@ -24,7 +25,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="24">
+  <fonts count="28">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -184,8 +185,28 @@
       <family val="0"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <color rgb="FF666666"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <b val="1"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="맑은 고딕"/>
+      <sz val="10"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="16">
     <fill>
       <patternFill/>
     </fill>
@@ -270,8 +291,13 @@
         <bgColor rgb="FFFFF6DD"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF2F3B52"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -309,6 +335,20 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFD0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFD0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFD0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFD0D0D0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -320,7 +360,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="87">
+  <cellXfs count="100">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -578,6 +618,39 @@
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="11" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="27" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -930,7 +1003,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H129"/>
+  <dimension ref="A1:H147"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="40" min="1" max="1"/>
@@ -4078,7 +4151,7 @@
       </c>
       <c r="C84" s="47" t="inlineStr">
         <is>
-          <t>LINK</t>
+          <t>L.I.N.C / LINK</t>
         </is>
       </c>
       <c r="D84" s="48" t="inlineStr">
@@ -5703,7 +5776,7 @@
       </c>
       <c r="H124" s="54" t="inlineStr">
         <is>
-          <t>메타버스엔터 프로젝트. 2025 종료</t>
+          <t>메타버스엔터 프로젝트. 2025 종료 | 2025.11.2 넷마블 메타버스엔터 레이블 활동 종료 발표(톱셀럽)</t>
         </is>
       </c>
     </row>
@@ -5904,6 +5977,726 @@
       <c r="H129" s="66" t="inlineStr">
         <is>
           <t>5인조 버추얼 보이그룹(마하진·나이선·안석우·원주율·임온). 2026.6.16 데뷔앨범 'Middle.i' 발매. 애니 연출 '체인소맨' 나카야마 류 감독, 음악 LUCY 조원상 참여. 팬덤 '미들아이'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="87" t="n">
+        <v>127</v>
+      </c>
+      <c r="B130" s="88" t="inlineStr">
+        <is>
+          <t>이브닛</t>
+        </is>
+      </c>
+      <c r="C130" s="87" t="inlineStr">
+        <is>
+          <t>IVNIT</t>
+        </is>
+      </c>
+      <c r="D130" s="88" t="inlineStr">
+        <is>
+          <t>아카이브 스튜디오(AkaiV Studio)</t>
+        </is>
+      </c>
+      <c r="E130" s="87" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F130" s="89" t="inlineStr">
+        <is>
+          <t>음반/아이돌형</t>
+        </is>
+      </c>
+      <c r="G130" s="90" t="inlineStr">
+        <is>
+          <t>활동중</t>
+        </is>
+      </c>
+      <c r="H130" s="66" t="inlineStr">
+        <is>
+          <t>스트리머 출신 5인조(비몽·여르미·u32·한결·샤르망). 2025.11.15 데뷔 싱글 'Even If'(타이틀 Hummer), 2집 'Even Though'. 스트리머 겸 음원 활동. 딩고뮤직 출연. (KMJ 2026.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="87" t="n">
+        <v>128</v>
+      </c>
+      <c r="B131" s="88" t="inlineStr">
+        <is>
+          <t>수소진</t>
+        </is>
+      </c>
+      <c r="C131" s="87" t="inlineStr">
+        <is>
+          <t>SOOSOJIN</t>
+        </is>
+      </c>
+      <c r="D131" s="88" t="inlineStr">
+        <is>
+          <t>브라더후드 엔터테인먼트(제작 로코베리)</t>
+        </is>
+      </c>
+      <c r="E131" s="87" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F131" s="89" t="inlineStr">
+        <is>
+          <t>음반/아이돌형</t>
+        </is>
+      </c>
+      <c r="G131" s="90" t="inlineStr">
+        <is>
+          <t>활동중</t>
+        </is>
+      </c>
+      <c r="H131" s="66" t="inlineStr">
+        <is>
+          <t>3인조 버추얼 걸그룹(수·소·진). 2025.12.18 첫 미니앨범 '아직 너를 사랑하는 건 맞아'. 2026.3 다비치 '별이 빛나는 밤' 리메이크, 스포티파이 홍콩 1위. 발라드 중심이라 스트리밍 집계 누락형. (KMJ 2025.12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="87" t="n">
+        <v>129</v>
+      </c>
+      <c r="B132" s="88" t="inlineStr">
+        <is>
+          <t>스파클즈</t>
+        </is>
+      </c>
+      <c r="C132" s="87" t="inlineStr">
+        <is>
+          <t>SPAKLZ</t>
+        </is>
+      </c>
+      <c r="D132" s="88" t="inlineStr">
+        <is>
+          <t>레진엔터테인먼트</t>
+        </is>
+      </c>
+      <c r="E132" s="87" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F132" s="89" t="inlineStr">
+        <is>
+          <t>음반/아이돌형</t>
+        </is>
+      </c>
+      <c r="G132" s="90" t="inlineStr">
+        <is>
+          <t>활동중</t>
+        </is>
+      </c>
+      <c r="H132" s="66" t="inlineStr">
+        <is>
+          <t>레진 웹툰 14작품 남주 캐릭터 기반 프로젝트 버추얼 보이그룹. 2025.11.25 데뷔 싱글 'COMET'. 시즌그리팅 해외 동시판매, 2026.6 월드투어 팝업. 음반·MV 중심. (연합 2025.11.22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="87" t="n">
+        <v>130</v>
+      </c>
+      <c r="B133" s="88" t="inlineStr">
+        <is>
+          <t>헥시아</t>
+        </is>
+      </c>
+      <c r="C133" s="87" t="inlineStr">
+        <is>
+          <t>HEXIA</t>
+        </is>
+      </c>
+      <c r="D133" s="88" t="inlineStr">
+        <is>
+          <t>스콘(SCON)</t>
+        </is>
+      </c>
+      <c r="E133" s="87" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F133" s="91" t="inlineStr">
+        <is>
+          <t>스트리밍/MCN형</t>
+        </is>
+      </c>
+      <c r="G133" s="90" t="inlineStr">
+        <is>
+          <t>활동중</t>
+        </is>
+      </c>
+      <c r="H133" s="66" t="inlineStr">
+        <is>
+          <t>미츄 운영사 스콘의 버추얼 스트리머 그룹. 7대 죄악 악마 콘셉트, 초기 멤버 마무·아즈·레비얀·루시. 2025.11.1 치지직 첫 방송. (톱셀럽 2025.10.18)</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="87" t="n">
+        <v>131</v>
+      </c>
+      <c r="B134" s="88" t="inlineStr">
+        <is>
+          <t>h.a.l.o</t>
+        </is>
+      </c>
+      <c r="C134" s="87" t="inlineStr">
+        <is>
+          <t>헤일로</t>
+        </is>
+      </c>
+      <c r="D134" s="88" t="inlineStr">
+        <is>
+          <t>스콘(SCON)</t>
+        </is>
+      </c>
+      <c r="E134" s="87" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F134" s="92" t="inlineStr">
+        <is>
+          <t>혼합형</t>
+        </is>
+      </c>
+      <c r="G134" s="90" t="inlineStr">
+        <is>
+          <t>활동중</t>
+        </is>
+      </c>
+      <c r="H134" s="66" t="inlineStr">
+        <is>
+          <t>스콘 첫 음악 유닛. 블루점프 하로하+미츄 모아+헥시아 레비얀+아오토라 유키 4인 여성 유닛. 2026.8.21 데뷔 싱글 '푸름주의보'. (톱셀럽 2026.8.12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="87" t="n">
+        <v>132</v>
+      </c>
+      <c r="B135" s="88" t="inlineStr">
+        <is>
+          <t>제나</t>
+        </is>
+      </c>
+      <c r="C135" s="87" t="inlineStr">
+        <is>
+          <t>JENA</t>
+        </is>
+      </c>
+      <c r="D135" s="88" t="inlineStr">
+        <is>
+          <t>뮤즈온</t>
+        </is>
+      </c>
+      <c r="E135" s="87" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F135" s="93" t="inlineStr">
+        <is>
+          <t>버추얼휴먼/솔로</t>
+        </is>
+      </c>
+      <c r="G135" s="90" t="inlineStr">
+        <is>
+          <t>활동중</t>
+        </is>
+      </c>
+      <c r="H135" s="66" t="inlineStr">
+        <is>
+          <t>솔로 버추얼 아티스트. 2026.7.24~26 워터밤 서울 무대로 데뷔, 첫 싱글 'STARDUST'(워터밤 월드투어 공식 테마곡). 부산·속초 워터밤 참여. (이데일리 2026.7.30)</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="87" t="n">
+        <v>133</v>
+      </c>
+      <c r="B136" s="88" t="inlineStr">
+        <is>
+          <t>청솔</t>
+        </is>
+      </c>
+      <c r="C136" s="87" t="inlineStr">
+        <is>
+          <t>CHEONGSOL</t>
+        </is>
+      </c>
+      <c r="D136" s="88" t="inlineStr">
+        <is>
+          <t>(미확인)</t>
+        </is>
+      </c>
+      <c r="E136" s="87" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F136" s="93" t="inlineStr">
+        <is>
+          <t>버추얼휴먼/솔로</t>
+        </is>
+      </c>
+      <c r="G136" s="90" t="inlineStr">
+        <is>
+          <t>활동중</t>
+        </is>
+      </c>
+      <c r="H136" s="66" t="inlineStr">
+        <is>
+          <t>버추얼 싱어송라이터(전곡 자작). 삼색빗자루 도깨비 콘셉트, 대형 기획사 연습생 출신. 첫 자작곡 '봄의 아이' 2026.5.20, 공식 데뷔 방송 2026.6.20 치지직·유튜브. 소속사 기사 미기재. (스포츠투데이 2026.6.10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="87" t="n">
+        <v>134</v>
+      </c>
+      <c r="B137" s="88" t="inlineStr">
+        <is>
+          <t>아이시아</t>
+        </is>
+      </c>
+      <c r="C137" s="87" t="inlineStr">
+        <is>
+          <t>IXIA</t>
+        </is>
+      </c>
+      <c r="D137" s="88" t="inlineStr">
+        <is>
+          <t>(미확인)</t>
+        </is>
+      </c>
+      <c r="E137" s="87" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F137" s="89" t="inlineStr">
+        <is>
+          <t>음반/아이돌형</t>
+        </is>
+      </c>
+      <c r="G137" s="94" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="H137" s="66" t="inlineStr">
+        <is>
+          <t>2025.8 데뷔 싱글 'Hide &amp; Find'. 소속·현황 추가 확인 필요. (톱셀럽 2025.10.23)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="87" t="n">
+        <v>135</v>
+      </c>
+      <c r="B138" s="88" t="inlineStr">
+        <is>
+          <t>클루즈</t>
+        </is>
+      </c>
+      <c r="C138" s="87" t="inlineStr">
+        <is>
+          <t>CLUEZ</t>
+        </is>
+      </c>
+      <c r="D138" s="88" t="inlineStr">
+        <is>
+          <t>카론 유니버스(카론 크리에이티브)</t>
+        </is>
+      </c>
+      <c r="E138" s="87" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F138" s="89" t="inlineStr">
+        <is>
+          <t>음반/아이돌형</t>
+        </is>
+      </c>
+      <c r="G138" s="90" t="inlineStr">
+        <is>
+          <t>활동중</t>
+        </is>
+      </c>
+      <c r="H138" s="66" t="inlineStr">
+        <is>
+          <t>2인조 버추얼 걸그룹(키유·미하루). 2025.11.29 데뷔. 에스더(AESTHER)·PJX와 같은 카론 유니버스 소속. 추가 멤버 합류 가능성. (나무위키 카론 유니버스)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="87" t="n">
+        <v>136</v>
+      </c>
+      <c r="B139" s="88" t="inlineStr">
+        <is>
+          <t>루나데이즈</t>
+        </is>
+      </c>
+      <c r="C139" s="87" t="inlineStr">
+        <is>
+          <t>LUNADAYS</t>
+        </is>
+      </c>
+      <c r="D139" s="88" t="inlineStr">
+        <is>
+          <t>루나데이즈(개인사업자 MCN)</t>
+        </is>
+      </c>
+      <c r="E139" s="87" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F139" s="91" t="inlineStr">
+        <is>
+          <t>스트리밍/MCN형</t>
+        </is>
+      </c>
+      <c r="G139" s="94" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="H139" s="66" t="inlineStr">
+        <is>
+          <t>2025.3 1기 셀레네 3인 SOOP 데뷔→2025.9 계약해지. 2기 아이즈키 2025.8 치지직, 3기 츠키아라 3인 2026.6 PV 공개. 기사 미확인(나무위키 단일).</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="87" t="n">
+        <v>137</v>
+      </c>
+      <c r="B140" s="88" t="inlineStr">
+        <is>
+          <t>애프터라이브</t>
+        </is>
+      </c>
+      <c r="C140" s="87" t="inlineStr">
+        <is>
+          <t>AfterLive</t>
+        </is>
+      </c>
+      <c r="D140" s="88" t="inlineStr">
+        <is>
+          <t>애프터라이브(자체 런칭)</t>
+        </is>
+      </c>
+      <c r="E140" s="87" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F140" s="91" t="inlineStr">
+        <is>
+          <t>스트리밍/MCN형</t>
+        </is>
+      </c>
+      <c r="G140" s="94" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="H140" s="66" t="inlineStr">
+        <is>
+          <t>2026.1.3~4 소속 그룹 '비바체' 4인(아마네루 피요·콘야 유메이·하루야 치에·시노 레이) 데뷔. 기사 미확인(나무위키 단일).</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="87" t="n">
+        <v>138</v>
+      </c>
+      <c r="B141" s="88" t="inlineStr">
+        <is>
+          <t>벨로디</t>
+        </is>
+      </c>
+      <c r="C141" s="87" t="inlineStr">
+        <is>
+          <t>VELODY</t>
+        </is>
+      </c>
+      <c r="D141" s="88" t="inlineStr">
+        <is>
+          <t>벨로디(자체 런칭)</t>
+        </is>
+      </c>
+      <c r="E141" s="87" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F141" s="91" t="inlineStr">
+        <is>
+          <t>스트리밍/MCN형</t>
+        </is>
+      </c>
+      <c r="G141" s="94" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="H141" s="66" t="inlineStr">
+        <is>
+          <t>2026.3.28 1기 유닛 하나메(HANAME) 2인(쿠로사와 쿄코·토카미 키나) 치지직 데뷔, 2026.9.4 2.0 비주얼 재데뷔. 기사 미확인(나무위키 단일).</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="87" t="n">
+        <v>139</v>
+      </c>
+      <c r="B142" s="88" t="inlineStr">
+        <is>
+          <t>아르포나</t>
+        </is>
+      </c>
+      <c r="C142" s="87" t="inlineStr">
+        <is>
+          <t>Arfauna</t>
+        </is>
+      </c>
+      <c r="D142" s="88" t="inlineStr">
+        <is>
+          <t>아르포나(버추얼 기획사)</t>
+        </is>
+      </c>
+      <c r="E142" s="87" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F142" s="91" t="inlineStr">
+        <is>
+          <t>스트리밍/MCN형</t>
+        </is>
+      </c>
+      <c r="G142" s="94" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="H142" s="66" t="inlineStr">
+        <is>
+          <t>2026.5.16 소속 그룹 '유모어' 3인(냐페르·디아푸·선아린) 데뷔. 기사 미확인(나무위키 단일).</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="87" t="n">
+        <v>140</v>
+      </c>
+      <c r="B143" s="88" t="inlineStr">
+        <is>
+          <t>바라바라</t>
+        </is>
+      </c>
+      <c r="C143" s="87" t="inlineStr">
+        <is>
+          <t>BARABARA</t>
+        </is>
+      </c>
+      <c r="D143" s="88" t="inlineStr">
+        <is>
+          <t>보쿠하이</t>
+        </is>
+      </c>
+      <c r="E143" s="87" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F143" s="91" t="inlineStr">
+        <is>
+          <t>스트리밍/MCN형</t>
+        </is>
+      </c>
+      <c r="G143" s="95" t="inlineStr">
+        <is>
+          <t>해체/종료</t>
+        </is>
+      </c>
+      <c r="H143" s="66" t="inlineStr">
+        <is>
+          <t>동아리형 6인조, 치지직. 2025.8.9~2026.2.27 순차 데뷔, 2025.12 보쿠하이 소속 전환. 2026.9.1 해체(카페 9.8 폐쇄). (나무위키)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="87" t="n">
+        <v>141</v>
+      </c>
+      <c r="B144" s="88" t="inlineStr">
+        <is>
+          <t>신디에잇</t>
+        </is>
+      </c>
+      <c r="C144" s="87" t="inlineStr">
+        <is>
+          <t>SYNDI8</t>
+        </is>
+      </c>
+      <c r="D144" s="88" t="inlineStr">
+        <is>
+          <t>수퍼톤(HYBE 자회사)</t>
+        </is>
+      </c>
+      <c r="E144" s="87" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F144" s="89" t="inlineStr">
+        <is>
+          <t>음반/아이돌형</t>
+        </is>
+      </c>
+      <c r="G144" s="94" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="H144" s="66" t="inlineStr">
+        <is>
+          <t>AI 보이스 기반 4인조 버추얼 걸그룹(카나리·네스트·고요·레이븐). 2024.6.27 데뷔 음반 'MVP'. 2026 활동 여부 미확인. 표절 논란 문서화. (나무위키)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="87" t="n">
+        <v>142</v>
+      </c>
+      <c r="B145" s="88" t="inlineStr">
+        <is>
+          <t>피버스</t>
+        </is>
+      </c>
+      <c r="C145" s="87" t="inlineStr">
+        <is>
+          <t>Feverse</t>
+        </is>
+      </c>
+      <c r="D145" s="88" t="inlineStr">
+        <is>
+          <t>카카오엔터테인먼트</t>
+        </is>
+      </c>
+      <c r="E145" s="87" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F145" s="92" t="inlineStr">
+        <is>
+          <t>혼합형</t>
+        </is>
+      </c>
+      <c r="G145" s="95" t="inlineStr">
+        <is>
+          <t>해체/종료</t>
+        </is>
+      </c>
+      <c r="H145" s="66" t="inlineStr">
+        <is>
+          <t>'소녀 리버스' 출신 현역 아이돌 5인의 버추얼 걸그룹. 2023.5.9 1집 'CHO' 데뷔, 일본어판 발매. 2024.3.8 해체. (나무위키)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="87" t="n">
+        <v>143</v>
+      </c>
+      <c r="B146" s="88" t="inlineStr">
+        <is>
+          <t>이진법소년들</t>
+        </is>
+      </c>
+      <c r="C146" s="87" t="inlineStr">
+        <is>
+          <t>ØXONE</t>
+        </is>
+      </c>
+      <c r="D146" s="88" t="inlineStr">
+        <is>
+          <t>완구 기업(유통 워너뮤직 ADA)</t>
+        </is>
+      </c>
+      <c r="E146" s="87" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F146" s="89" t="inlineStr">
+        <is>
+          <t>음반/아이돌형</t>
+        </is>
+      </c>
+      <c r="G146" s="95" t="inlineStr">
+        <is>
+          <t>해체/종료</t>
+        </is>
+      </c>
+      <c r="H146" s="66" t="inlineStr">
+        <is>
+          <t>5인조 버추얼 보이그룹(세계·비한·윤·아민·혜규). 2023.6.14 디지털싱글 'Designer' 데뷔. 2023.9 이후 활동중단·영상 비공개(해체 추정). (나무위키)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="87" t="n">
+        <v>144</v>
+      </c>
+      <c r="B147" s="88" t="inlineStr">
+        <is>
+          <t>홀린</t>
+        </is>
+      </c>
+      <c r="C147" s="87" t="inlineStr">
+        <is>
+          <t>WhOLLiN</t>
+        </is>
+      </c>
+      <c r="D147" s="88" t="inlineStr">
+        <is>
+          <t>플레이리스트(PLAYLIST)</t>
+        </is>
+      </c>
+      <c r="E147" s="87" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F147" s="89" t="inlineStr">
+        <is>
+          <t>음반/아이돌형</t>
+        </is>
+      </c>
+      <c r="G147" s="90" t="inlineStr">
+        <is>
+          <t>활동중</t>
+        </is>
+      </c>
+      <c r="H147" s="66" t="inlineStr">
+        <is>
+          <t>'약한영웅' 제작사 플레이리스트 첫 버추얼 보이그룹 5인(시오·태이·이소·강우·도언). 2026.9.1 디지털 싱글 '깨어나다'(타이틀 Time Sleep, 펜타곤 후이 프로듀싱)로 정식 데뷔. (톱셀럽 2026.9.1)</t>
         </is>
       </c>
     </row>
@@ -5925,7 +6718,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D51"/>
+  <dimension ref="A1:D63"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="40" min="1" max="1"/>
@@ -5937,7 +6730,7 @@
     <row r="1" ht="25.5" customHeight="1" s="41">
       <c r="A1" s="42" t="inlineStr">
         <is>
-          <t>주요 소속사·운영사 정리 (v8: 2026-07-17 뉴스조사로 6개사 추가)</t>
+          <t>주요 소속사·운영사 정리 (2026-09-12 조사로 12개사 추가)</t>
         </is>
       </c>
     </row>
@@ -6998,6 +7791,270 @@
       <c r="D51" s="86" t="inlineStr">
         <is>
           <t>INCS toenter(일본)와 합작. 실사+버추얼 하이브리드</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="86" t="inlineStr">
+        <is>
+          <t>브라더후드 엔터테인먼트</t>
+        </is>
+      </c>
+      <c r="B52" s="86" t="inlineStr">
+        <is>
+          <t>엔터(제작 로코베리)</t>
+        </is>
+      </c>
+      <c r="C52" s="86" t="inlineStr">
+        <is>
+          <t>수소진</t>
+        </is>
+      </c>
+      <c r="D52" s="86" t="inlineStr">
+        <is>
+          <t>3인 버추얼 걸그룹. 발라드·리메이크</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="86" t="inlineStr">
+        <is>
+          <t>레진엔터테인먼트</t>
+        </is>
+      </c>
+      <c r="B53" s="86" t="inlineStr">
+        <is>
+          <t>웹툰 IP</t>
+        </is>
+      </c>
+      <c r="C53" s="86" t="inlineStr">
+        <is>
+          <t>스파클즈(SPAKLZ)</t>
+        </is>
+      </c>
+      <c r="D53" s="86" t="inlineStr">
+        <is>
+          <t>웹툰 남주 캐릭터 기반 프로젝트 그룹</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="86" t="inlineStr">
+        <is>
+          <t>스콘(SCON)</t>
+        </is>
+      </c>
+      <c r="B54" s="86" t="inlineStr">
+        <is>
+          <t>버튜버 기획사</t>
+        </is>
+      </c>
+      <c r="C54" s="86" t="inlineStr">
+        <is>
+          <t>미츄, 헥시아, h.a.l.o</t>
+        </is>
+      </c>
+      <c r="D54" s="86" t="inlineStr">
+        <is>
+          <t>미츄 운영사. 2026.8 첫 음악 유닛 h.a.l.o</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="86" t="inlineStr">
+        <is>
+          <t>뮤즈온</t>
+        </is>
+      </c>
+      <c r="B55" s="86" t="inlineStr">
+        <is>
+          <t>엔터</t>
+        </is>
+      </c>
+      <c r="C55" s="86" t="inlineStr">
+        <is>
+          <t>제나(JENA)</t>
+        </is>
+      </c>
+      <c r="D55" s="86" t="inlineStr">
+        <is>
+          <t>솔로 버추얼 아티스트. 워터밤 테마곡</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="86" t="inlineStr">
+        <is>
+          <t>카론 유니버스</t>
+        </is>
+      </c>
+      <c r="B56" s="86" t="inlineStr">
+        <is>
+          <t>버추얼 레이블</t>
+        </is>
+      </c>
+      <c r="C56" s="86" t="inlineStr">
+        <is>
+          <t>AESTHER, PJX, CLUEZ</t>
+        </is>
+      </c>
+      <c r="D56" s="86" t="inlineStr">
+        <is>
+          <t>카론 크리에이티브</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="86" t="inlineStr">
+        <is>
+          <t>에이탑유니버스</t>
+        </is>
+      </c>
+      <c r="B57" s="86" t="inlineStr">
+        <is>
+          <t>엔터(SM 보컬트레이너 출신)</t>
+        </is>
+      </c>
+      <c r="C57" s="86" t="inlineStr">
+        <is>
+          <t>코스믹코드</t>
+        </is>
+      </c>
+      <c r="D57" s="86" t="inlineStr">
+        <is>
+          <t>日 우타이테 시장 겨냥 2.5D. YOANI 3억엔 투자</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="86" t="inlineStr">
+        <is>
+          <t>밀리언볼트</t>
+        </is>
+      </c>
+      <c r="B58" s="86" t="inlineStr">
+        <is>
+          <t>애니메이션 스튜디오</t>
+        </is>
+      </c>
+      <c r="C58" s="86" t="inlineStr">
+        <is>
+          <t>STUN-X</t>
+        </is>
+      </c>
+      <c r="D58" s="86" t="inlineStr">
+        <is>
+          <t>2D 버추얼 아이돌 IP, 웹소설 연계</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="86" t="inlineStr">
+        <is>
+          <t>타이탄콘텐츠 × 대원미디어</t>
+        </is>
+      </c>
+      <c r="B59" s="86" t="inlineStr">
+        <is>
+          <t>콘텐츠·미디어</t>
+        </is>
+      </c>
+      <c r="C59" s="86" t="inlineStr">
+        <is>
+          <t>WINKX(예정)</t>
+        </is>
+      </c>
+      <c r="D59" s="86" t="inlineStr">
+        <is>
+          <t>360도 글로벌 IP 공동사업</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="86" t="inlineStr">
+        <is>
+          <t>코드판타지아</t>
+        </is>
+      </c>
+      <c r="B60" s="86" t="inlineStr">
+        <is>
+          <t>엔터</t>
+        </is>
+      </c>
+      <c r="C60" s="86" t="inlineStr">
+        <is>
+          <t>레드소다써클</t>
+        </is>
+      </c>
+      <c r="D60" s="86" t="inlineStr">
+        <is>
+          <t>실사+버추얼 하이브리드 한일 듀오</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="86" t="inlineStr">
+        <is>
+          <t>루나데이즈</t>
+        </is>
+      </c>
+      <c r="B61" s="86" t="inlineStr">
+        <is>
+          <t>개인사업자 MCN</t>
+        </is>
+      </c>
+      <c r="C61" s="86" t="inlineStr">
+        <is>
+          <t>루나데이즈 1~3기</t>
+        </is>
+      </c>
+      <c r="D61" s="86" t="inlineStr">
+        <is>
+          <t>2024.8 설립. 기사 미확인</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="86" t="inlineStr">
+        <is>
+          <t>보쿠하이</t>
+        </is>
+      </c>
+      <c r="B62" s="86" t="inlineStr">
+        <is>
+          <t>버튜버 기획사</t>
+        </is>
+      </c>
+      <c r="C62" s="86" t="inlineStr">
+        <is>
+          <t>바라바라(해체)</t>
+        </is>
+      </c>
+      <c r="D62" s="86" t="inlineStr">
+        <is>
+          <t>2026.9.1 해체</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="86" t="inlineStr">
+        <is>
+          <t>수퍼톤(HYBE)</t>
+        </is>
+      </c>
+      <c r="B63" s="86" t="inlineStr">
+        <is>
+          <t>AI 오디오</t>
+        </is>
+      </c>
+      <c r="C63" s="86" t="inlineStr">
+        <is>
+          <t>SYNDI8</t>
+        </is>
+      </c>
+      <c r="D63" s="86" t="inlineStr">
+        <is>
+          <t>AI 보이스 기반 버추얼 걸그룹</t>
         </is>
       </c>
     </row>
@@ -7165,7 +8222,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E16"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="40" min="1" max="1"/>
@@ -7178,7 +8235,7 @@
     <row r="1" ht="25.5" customHeight="1" s="41">
       <c r="A1" s="74" t="inlineStr">
         <is>
-          <t>2026 신규 데뷔 · 데뷔 예정 워치리스트 (2026-07-17 뉴스 조사 반영)</t>
+          <t>2026 신규 데뷔 · 데뷔 예정 워치리스트 (2026-09-12 3갈래 조사 반영)</t>
         </is>
       </c>
     </row>
@@ -7546,7 +8603,7 @@
       </c>
       <c r="C15" s="63" t="inlineStr">
         <is>
-          <t>데뷔 예정</t>
+          <t>정식 데뷔 완료(2026.9.1) → 전수목록 편입</t>
         </is>
       </c>
       <c r="D15" s="62" t="inlineStr">
@@ -7584,6 +8641,114 @@
       <c r="E16" s="66" t="inlineStr">
         <is>
           <t>※실사 멤버+버추얼 캐릭터 연동 하이브리드(2.5D) — 완전 버추얼 아님, 경계 사례. 5인(유이사·에나·서연·히나리·소정). 싱글 'Reborn'=넷플릭스 '리본 히어로' 주제곡. 숀·허니웍스 프로듀싱, 캐릭터 디자인 LAM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="88" t="inlineStr">
+        <is>
+          <t>코스믹코드 (COSMIC CODE)</t>
+        </is>
+      </c>
+      <c r="B17" s="87" t="inlineStr">
+        <is>
+          <t>에이탑유니버스</t>
+        </is>
+      </c>
+      <c r="C17" s="88" t="inlineStr">
+        <is>
+          <t>프리데뷔(멤버 순차 공개)</t>
+        </is>
+      </c>
+      <c r="D17" s="87" t="inlineStr">
+        <is>
+          <t>2026.9.9~</t>
+        </is>
+      </c>
+      <c r="E17" s="66" t="inlineStr">
+        <is>
+          <t>일본 우타이테 시장 겨냥 2.5D 버추얼 아이돌 5인. 프리데뷔 싱글 'POKER FACE', 2026.11 도쿄·오사카 공연 추진. 日 YOANI 3억엔 투자. (한국일보 2026.9.9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="88" t="inlineStr">
+        <is>
+          <t>STUN-X (우주아이돌리그)</t>
+        </is>
+      </c>
+      <c r="B18" s="87" t="inlineStr">
+        <is>
+          <t>밀리언볼트(애니 스튜디오)</t>
+        </is>
+      </c>
+      <c r="C18" s="88" t="inlineStr">
+        <is>
+          <t>데뷔 예정</t>
+        </is>
+      </c>
+      <c r="D18" s="87" t="inlineStr">
+        <is>
+          <t>2026.10.2</t>
+        </is>
+      </c>
+      <c r="E18" s="66" t="inlineStr">
+        <is>
+          <t>2D 버추얼 아이돌 IP. 웹소설 2026.9.10 카카오페이지 연재, 10.2 첫 디지털 싱글 예정. 캐릭터 콘텐츠 누적 2,000만뷰. (MBN 2026.9.11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="88" t="inlineStr">
+        <is>
+          <t>WINKX (윙스)</t>
+        </is>
+      </c>
+      <c r="B19" s="87" t="inlineStr">
+        <is>
+          <t>타이탄콘텐츠 × 대원미디어</t>
+        </is>
+      </c>
+      <c r="C19" s="88" t="inlineStr">
+        <is>
+          <t>데뷔 예정(MOU 단계)</t>
+        </is>
+      </c>
+      <c r="D19" s="87" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="E19" s="66" t="inlineStr">
+        <is>
+          <t>360도 글로벌 IP(음악·만화·애니) 공동사업. 모션캡처 대원 자회사 이엠피. 일정 미확인. (스타뉴스 2026.4.15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="88" t="inlineStr">
+        <is>
+          <t>레드소다써클 (Red Soda Circle)</t>
+        </is>
+      </c>
+      <c r="B20" s="87" t="inlineStr">
+        <is>
+          <t>코드판타지아</t>
+        </is>
+      </c>
+      <c r="C20" s="88" t="inlineStr">
+        <is>
+          <t>프리데뷔</t>
+        </is>
+      </c>
+      <c r="D20" s="87" t="inlineStr">
+        <is>
+          <t>2025.12.22</t>
+        </is>
+      </c>
+      <c r="E20" s="66" t="inlineStr">
+        <is>
+          <t>※실사+버추얼 병행 하이브리드('리얼 라이프 듀얼 포맷'). 한일 2인조(리나·하루). 2025.12.22 첫 버추얼 라이브. (스포츠경향 2025.12.22)</t>
         </is>
       </c>
     </row>
@@ -10717,4 +11882,325 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" scale="100" fitToHeight="1" fitToWidth="1" pageOrder="downThenOver" blackAndWhite="0" draft="0" horizontalDpi="300" verticalDpi="300" copies="1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:I9"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="10" customWidth="1" style="41" min="1" max="1"/>
+    <col width="14" customWidth="1" style="41" min="2" max="2"/>
+    <col width="30" customWidth="1" style="41" min="3" max="3"/>
+    <col width="20" customWidth="1" style="41" min="4" max="4"/>
+    <col width="14" customWidth="1" style="41" min="5" max="5"/>
+    <col width="14" customWidth="1" style="41" min="6" max="6"/>
+    <col width="26" customWidth="1" style="41" min="7" max="7"/>
+    <col width="44" customWidth="1" style="41" min="8" max="8"/>
+    <col width="30" customWidth="1" style="41" min="9" max="9"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="96" t="inlineStr">
+        <is>
+          <t>전 과정 생성형 AI / AI 보컬 아티스트 (버추얼 아이돌 명부와 별도 관리)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="97" t="inlineStr">
+        <is>
+          <t>구분 기준: 사람 연기자(모션캡처·성우) 없이 생성형 AI로 제작·가창되는 아티스트. 명부(전수목록)의 버추얼 아이돌과 성격이 달라 분리 관리. 2026-09-12 조사.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="98" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="B4" s="98" t="inlineStr">
+        <is>
+          <t>영문</t>
+        </is>
+      </c>
+      <c r="C4" s="98" t="inlineStr">
+        <is>
+          <t>소속사·제작사</t>
+        </is>
+      </c>
+      <c r="D4" s="98" t="inlineStr">
+        <is>
+          <t>유형</t>
+        </is>
+      </c>
+      <c r="E4" s="98" t="inlineStr">
+        <is>
+          <t>상태</t>
+        </is>
+      </c>
+      <c r="F4" s="98" t="inlineStr">
+        <is>
+          <t>데뷔(예정)일</t>
+        </is>
+      </c>
+      <c r="G4" s="98" t="inlineStr">
+        <is>
+          <t>발매작</t>
+        </is>
+      </c>
+      <c r="H4" s="98" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="I4" s="98" t="inlineStr">
+        <is>
+          <t>근거</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="99" t="inlineStr">
+        <is>
+          <t>서리아</t>
+        </is>
+      </c>
+      <c r="B5" s="99" t="inlineStr">
+        <is>
+          <t>SEORIA</t>
+        </is>
+      </c>
+      <c r="C5" s="99" t="inlineStr">
+        <is>
+          <t>지로(드롭샷 AI)</t>
+        </is>
+      </c>
+      <c r="D5" s="99" t="inlineStr">
+        <is>
+          <t>생성형 AI 걸그룹 4인</t>
+        </is>
+      </c>
+      <c r="E5" s="99" t="inlineStr">
+        <is>
+          <t>데뷔</t>
+        </is>
+      </c>
+      <c r="F5" s="99" t="inlineStr">
+        <is>
+          <t>2026.8.31</t>
+        </is>
+      </c>
+      <c r="G5" s="99" t="inlineStr">
+        <is>
+          <t>싱글 'Burning'</t>
+        </is>
+      </c>
+      <c r="H5" s="99" t="inlineStr">
+        <is>
+          <t>리예·코라·이설·프레야. 전 과정 생성형 AI. 문체부·콘진원 제작지원.</t>
+        </is>
+      </c>
+      <c r="I5" s="99" t="inlineStr">
+        <is>
+          <t>텐아시아 2026.8.31 / 머니투데이 2026.9.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="99" t="inlineStr">
+        <is>
+          <t>뮤오</t>
+        </is>
+      </c>
+      <c r="B6" s="99" t="inlineStr">
+        <is>
+          <t>muuo:23</t>
+        </is>
+      </c>
+      <c r="C6" s="99" t="inlineStr">
+        <is>
+          <t>크리에이션집업(유통 CJ ENM)</t>
+        </is>
+      </c>
+      <c r="D6" s="99" t="inlineStr">
+        <is>
+          <t>생성형 AI 보이그룹 5인</t>
+        </is>
+      </c>
+      <c r="E6" s="99" t="inlineStr">
+        <is>
+          <t>데뷔 예정</t>
+        </is>
+      </c>
+      <c r="F6" s="99" t="inlineStr">
+        <is>
+          <t>2026.10 중순</t>
+        </is>
+      </c>
+      <c r="G6" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H6" s="99" t="inlineStr">
+        <is>
+          <t>태원·하민·연우·이현·세이. '23세기 미래에서 온 아이돌' 콘셉트. ※23세기아이들과 관계는 기사 미확인. 인스타 @muuo.wav</t>
+        </is>
+      </c>
+      <c r="I6" s="99" t="inlineStr">
+        <is>
+          <t>뉴스1 2026.9.1 / 머니투데이 2026.9.9</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="99" t="inlineStr">
+        <is>
+          <t>로진</t>
+        </is>
+      </c>
+      <c r="B7" s="99" t="inlineStr">
+        <is>
+          <t>RŌSIEN</t>
+        </is>
+      </c>
+      <c r="C7" s="99" t="inlineStr">
+        <is>
+          <t>우유미디어랩 × 스튜디오 명불허전</t>
+        </is>
+      </c>
+      <c r="D7" s="99" t="inlineStr">
+        <is>
+          <t>대화형 AI 솔로</t>
+        </is>
+      </c>
+      <c r="E7" s="99" t="inlineStr">
+        <is>
+          <t>데뷔</t>
+        </is>
+      </c>
+      <c r="F7" s="99" t="inlineStr">
+        <is>
+          <t>2026.8.19</t>
+        </is>
+      </c>
+      <c r="G7" s="99" t="inlineStr">
+        <is>
+          <t>싱글 '너의 고막으로 닿았으면 해'</t>
+        </is>
+      </c>
+      <c r="H7" s="99" t="inlineStr">
+        <is>
+          <t>보사노바+누디스코+시티팝. 2026 KGMA 라인업 보도.</t>
+        </is>
+      </c>
+      <c r="I7" s="99" t="inlineStr">
+        <is>
+          <t>스포츠경향 2026.8.12 / 톱셀럽 2026.8.13</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="99" t="inlineStr">
+        <is>
+          <t>슬릭트</t>
+        </is>
+      </c>
+      <c r="B8" s="99" t="inlineStr">
+        <is>
+          <t>SLIKT (ryft)</t>
+        </is>
+      </c>
+      <c r="C8" s="99" t="inlineStr">
+        <is>
+          <t>ryft 프로젝트(팬 플랫폼 LiNC 기반, 운영사 미기재)</t>
+        </is>
+      </c>
+      <c r="D8" s="99" t="inlineStr">
+        <is>
+          <t>AI 솔로 아티스트</t>
+        </is>
+      </c>
+      <c r="E8" s="99" t="inlineStr">
+        <is>
+          <t>데뷔</t>
+        </is>
+      </c>
+      <c r="F8" s="99" t="inlineStr">
+        <is>
+          <t>2026.7.31</t>
+        </is>
+      </c>
+      <c r="G8" s="99" t="inlineStr">
+        <is>
+          <t>앨범 'FALLEN'(타이틀 Devil's Prayer)</t>
+        </is>
+      </c>
+      <c r="H8" s="99" t="inlineStr">
+        <is>
+          <t>MV 1주 만에 80만뷰. ryft는 총 52명 AI 아티스트 순차 공개 계획.</t>
+        </is>
+      </c>
+      <c r="I8" s="99" t="inlineStr">
+        <is>
+          <t>일간스포츠 2026.8.10 / 텐아시아 2026.8.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="99" t="inlineStr">
+        <is>
+          <t>채아</t>
+        </is>
+      </c>
+      <c r="B9" s="99" t="inlineStr">
+        <is>
+          <t>ChaeA</t>
+        </is>
+      </c>
+      <c r="C9" s="99" t="inlineStr">
+        <is>
+          <t>사운드리퍼블리카</t>
+        </is>
+      </c>
+      <c r="D9" s="99" t="inlineStr">
+        <is>
+          <t>AI 가수(협업 싱글)</t>
+        </is>
+      </c>
+      <c r="E9" s="99" t="inlineStr">
+        <is>
+          <t>첫 음원(정식 데뷔 표현 없음)</t>
+        </is>
+      </c>
+      <c r="F9" s="99" t="inlineStr">
+        <is>
+          <t>2026.6.23</t>
+        </is>
+      </c>
+      <c r="G9" s="99" t="inlineStr">
+        <is>
+          <t>전영록 듀엣 '돌이키지마'</t>
+        </is>
+      </c>
+      <c r="H9" s="99" t="inlineStr">
+        <is>
+          <t>협업 싱글로 첫 등장. 정식 데뷔 여부 판단 보류.</t>
+        </is>
+      </c>
+      <c r="I9" s="99" t="inlineStr">
+        <is>
+          <t>Korea IT Times 2026.6.4</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/한국_버추얼아이돌_전수조사_v8.xlsx
+++ b/data/한국_버추얼아이돌_전수조사_v8.xlsx
@@ -5861,35 +5861,35 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="62" t="n">
+      <c r="A127" s="87" t="n">
         <v>124</v>
       </c>
-      <c r="B127" s="63" t="inlineStr">
+      <c r="B127" s="88" t="inlineStr">
         <is>
           <t>오위스</t>
         </is>
       </c>
-      <c r="C127" s="62" t="inlineStr">
+      <c r="C127" s="87" t="inlineStr">
         <is>
           <t>OWIS</t>
         </is>
       </c>
-      <c r="D127" s="63" t="inlineStr">
+      <c r="D127" s="88" t="inlineStr">
         <is>
           <t>올마이애닉도츠(ama)</t>
         </is>
       </c>
-      <c r="E127" s="62" t="inlineStr">
+      <c r="E127" s="87" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F127" s="64" t="inlineStr">
+      <c r="F127" s="89" t="inlineStr">
         <is>
           <t>음반/아이돌형</t>
         </is>
       </c>
-      <c r="G127" s="65" t="inlineStr">
+      <c r="G127" s="90" t="inlineStr">
         <is>
           <t>활동중</t>
         </is>
@@ -5901,35 +5901,35 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="62" t="n">
+      <c r="A128" s="87" t="n">
         <v>125</v>
       </c>
-      <c r="B128" s="63" t="inlineStr">
+      <c r="B128" s="88" t="inlineStr">
         <is>
           <t>우주괴담</t>
         </is>
       </c>
-      <c r="C128" s="62" t="inlineStr">
+      <c r="C128" s="87" t="inlineStr">
         <is>
           <t>SPACE HORROR</t>
         </is>
       </c>
-      <c r="D128" s="63" t="inlineStr">
+      <c r="D128" s="88" t="inlineStr">
         <is>
           <t>그림 프로덕션(마운드미디어)</t>
         </is>
       </c>
-      <c r="E128" s="62" t="inlineStr">
+      <c r="E128" s="87" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F128" s="67" t="inlineStr">
+      <c r="F128" s="92" t="inlineStr">
         <is>
           <t>혼합형</t>
         </is>
       </c>
-      <c r="G128" s="65" t="inlineStr">
+      <c r="G128" s="90" t="inlineStr">
         <is>
           <t>활동중</t>
         </is>
@@ -5941,35 +5941,35 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="62" t="n">
+      <c r="A129" s="87" t="n">
         <v>126</v>
       </c>
-      <c r="B129" s="63" t="inlineStr">
+      <c r="B129" s="88" t="inlineStr">
         <is>
           <t>미완소년</t>
         </is>
       </c>
-      <c r="C129" s="62" t="inlineStr">
+      <c r="C129" s="87" t="inlineStr">
         <is>
           <t>美完少年</t>
         </is>
       </c>
-      <c r="D129" s="63" t="inlineStr">
+      <c r="D129" s="88" t="inlineStr">
         <is>
           <t>어비스컴퍼니</t>
         </is>
       </c>
-      <c r="E129" s="62" t="inlineStr">
+      <c r="E129" s="87" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F129" s="64" t="inlineStr">
+      <c r="F129" s="89" t="inlineStr">
         <is>
           <t>음반/아이돌형</t>
         </is>
       </c>
-      <c r="G129" s="65" t="inlineStr">
+      <c r="G129" s="90" t="inlineStr">
         <is>
           <t>활동중</t>
         </is>
@@ -8537,49 +8537,49 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="63" t="inlineStr">
+      <c r="A13" s="88" t="inlineStr">
         <is>
           <t>비더후드 (B THE HOOD)</t>
         </is>
       </c>
-      <c r="B13" s="62" t="inlineStr">
+      <c r="B13" s="87" t="inlineStr">
         <is>
           <t>레벨스(LEVVELS·하이브×두나무 합작)</t>
         </is>
       </c>
-      <c r="C13" s="63" t="inlineStr">
-        <is>
-          <t>프리데뷔(정식 데뷔일 미확인)</t>
-        </is>
-      </c>
-      <c r="D13" s="62" t="inlineStr">
-        <is>
-          <t>2026.6.26 선공개</t>
+      <c r="C13" s="88" t="inlineStr">
+        <is>
+          <t>프리데뷔 완료(선공개 3장) · 정식 데뷔 임박</t>
+        </is>
+      </c>
+      <c r="D13" s="87" t="inlineStr">
+        <is>
+          <t>선공개 2026.6.26/7.31/8.21 · 정식 데뷔일 미확인</t>
         </is>
       </c>
       <c r="E13" s="66" t="inlineStr">
         <is>
-          <t>5인조(이언·제이스·퍼비·기류·루안). 선공개 싱글 'Lowkey'. 행성 노버스를 떠난 외계인 다크SF 세계관. 데뷔 전 유튜브 4만·쇼츠 일간 14위.</t>
+          <t>5인조(이언·제이스·퍼비·기류·루안). 선공개 싱글 3장 — 'Lowkey'(6.26), 'The Baddest'(7.31), 'JADED'(8.21, 기사상 '정식 데뷔 전 마지막 선공개'). 행성 노버스를 떠난 외계인 다크SF 세계관. 유튜브 개설 7주 만에 구독 10만, 쇼츠 누적 500만뷰. 정식 데뷔 시 전수목록 편입 예정. (스포츠경향 2026.8.13, 텐아시아 2026.7.29)</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="63" t="inlineStr">
+      <c r="A14" s="88" t="inlineStr">
         <is>
           <t>비그릿츠 (BEGRITZ)</t>
         </is>
       </c>
-      <c r="B14" s="62" t="inlineStr">
+      <c r="B14" s="87" t="inlineStr">
         <is>
           <t>디네이블(DNABLE)</t>
         </is>
       </c>
-      <c r="C14" s="63" t="inlineStr">
+      <c r="C14" s="88" t="inlineStr">
         <is>
           <t>데뷔 예정</t>
         </is>
       </c>
-      <c r="D14" s="62" t="inlineStr">
+      <c r="D14" s="87" t="inlineStr">
         <is>
           <t>2026.8(론칭 예정)</t>
         </is>
@@ -8591,22 +8591,22 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="63" t="inlineStr">
+      <c r="A15" s="88" t="inlineStr">
         <is>
           <t>홀린 (WhOLLiN)</t>
         </is>
       </c>
-      <c r="B15" s="62" t="inlineStr">
+      <c r="B15" s="87" t="inlineStr">
         <is>
           <t>플레이리스트(PLAYLIST)</t>
         </is>
       </c>
-      <c r="C15" s="63" t="inlineStr">
+      <c r="C15" s="88" t="inlineStr">
         <is>
           <t>정식 데뷔 완료(2026.9.1) → 전수목록 편입</t>
         </is>
       </c>
-      <c r="D15" s="62" t="inlineStr">
+      <c r="D15" s="87" t="inlineStr">
         <is>
           <t>2026.9.1</t>
         </is>
@@ -8618,22 +8618,22 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="63" t="inlineStr">
+      <c r="A16" s="88" t="inlineStr">
         <is>
           <t>걸스 아카이브 (Girls Archives.)</t>
         </is>
       </c>
-      <c r="B16" s="62" t="inlineStr">
+      <c r="B16" s="87" t="inlineStr">
         <is>
           <t>하이브 NEB × INCS toenter(일본)</t>
         </is>
       </c>
-      <c r="C16" s="63" t="inlineStr">
+      <c r="C16" s="88" t="inlineStr">
         <is>
           <t>프리데뷔 예정</t>
         </is>
       </c>
-      <c r="D16" s="62" t="inlineStr">
+      <c r="D16" s="87" t="inlineStr">
         <is>
           <t>2026.8.7 프리데뷔</t>
         </is>

--- a/data/한국_버추얼아이돌_전수조사_v8.xlsx
+++ b/data/한국_버추얼아이돌_전수조사_v8.xlsx
@@ -206,7 +206,7 @@
       <sz val="10"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill/>
     </fill>
@@ -296,6 +296,11 @@
         <fgColor rgb="FF2F3B52"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF3E8FF"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="4">
     <border>
@@ -360,7 +365,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="100">
+  <cellXfs count="111">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -652,6 +657,35 @@
     <xf numFmtId="0" fontId="26" fillId="15" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="27" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1003,7 +1037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H147"/>
+  <dimension ref="A1:H154"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="40" min="1" max="1"/>
@@ -1026,7 +1060,7 @@
     <row r="2" ht="15.75" customHeight="1" s="41">
       <c r="A2" s="43" t="inlineStr">
         <is>
-          <t>출처: thewiki.kr 버추얼그룹목록 + 언론보도(머니투데이·이데일리·한경·스포츠경향·전자신문·톱셀럽·KMJ 등) + MBC 버추얼라이브페스티벌 라인업 / 활동성 검증 2026-06-06 / ※'확인필요' = 실재하나 (a)소속·데뷔 미확정 또는 (b)최근 1년 내 활동(업로드) 미확인 — 추가조사 대상 / v8: 확인필요 재판정·소속사 확정(2026-06-06 웹 재조사), 상태값 '휴면' 신설</t>
+          <t>출처: thewiki.kr 버추얼그룹목록 + 언론보도(머니투데이·이데일리·한경·스포츠경향·전자신문·톱셀럽·KMJ 등) + MBC 버추얼라이브페스티벌 라인업 / 활동성 검증 2026-06-06 / ※'확인필요' = 실재하나 (a)소속·데뷔 미확정 또는 (b)최근 1년 내 활동(업로드) 미확인 — 추가조사 대상 / v8: 확인필요 재판정·소속사 확정(2026-06-06 웹 재조사), 상태값 '휴면' 신설 / 상태 '데뷔전' 신설(프리데뷔·데뷔예정 그룹도 전수목록에 표기, 2026-09-12)</t>
         </is>
       </c>
     </row>
@@ -5861,30 +5895,30 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="87" t="n">
+      <c r="A127" s="100" t="n">
         <v>124</v>
       </c>
-      <c r="B127" s="88" t="inlineStr">
+      <c r="B127" s="101" t="inlineStr">
         <is>
           <t>오위스</t>
         </is>
       </c>
-      <c r="C127" s="87" t="inlineStr">
+      <c r="C127" s="100" t="inlineStr">
         <is>
           <t>OWIS</t>
         </is>
       </c>
-      <c r="D127" s="88" t="inlineStr">
+      <c r="D127" s="101" t="inlineStr">
         <is>
           <t>올마이애닉도츠(ama)</t>
         </is>
       </c>
-      <c r="E127" s="87" t="inlineStr">
+      <c r="E127" s="100" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F127" s="89" t="inlineStr">
+      <c r="F127" s="102" t="inlineStr">
         <is>
           <t>음반/아이돌형</t>
         </is>
@@ -5901,30 +5935,30 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="87" t="n">
+      <c r="A128" s="100" t="n">
         <v>125</v>
       </c>
-      <c r="B128" s="88" t="inlineStr">
+      <c r="B128" s="101" t="inlineStr">
         <is>
           <t>우주괴담</t>
         </is>
       </c>
-      <c r="C128" s="87" t="inlineStr">
+      <c r="C128" s="100" t="inlineStr">
         <is>
           <t>SPACE HORROR</t>
         </is>
       </c>
-      <c r="D128" s="88" t="inlineStr">
+      <c r="D128" s="101" t="inlineStr">
         <is>
           <t>그림 프로덕션(마운드미디어)</t>
         </is>
       </c>
-      <c r="E128" s="87" t="inlineStr">
+      <c r="E128" s="100" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F128" s="92" t="inlineStr">
+      <c r="F128" s="104" t="inlineStr">
         <is>
           <t>혼합형</t>
         </is>
@@ -5941,30 +5975,30 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="87" t="n">
+      <c r="A129" s="100" t="n">
         <v>126</v>
       </c>
-      <c r="B129" s="88" t="inlineStr">
+      <c r="B129" s="101" t="inlineStr">
         <is>
           <t>미완소년</t>
         </is>
       </c>
-      <c r="C129" s="87" t="inlineStr">
+      <c r="C129" s="100" t="inlineStr">
         <is>
           <t>美完少年</t>
         </is>
       </c>
-      <c r="D129" s="88" t="inlineStr">
+      <c r="D129" s="101" t="inlineStr">
         <is>
           <t>어비스컴퍼니</t>
         </is>
       </c>
-      <c r="E129" s="87" t="inlineStr">
+      <c r="E129" s="100" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F129" s="89" t="inlineStr">
+      <c r="F129" s="102" t="inlineStr">
         <is>
           <t>음반/아이돌형</t>
         </is>
@@ -5981,30 +6015,30 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="87" t="n">
+      <c r="A130" s="100" t="n">
         <v>127</v>
       </c>
-      <c r="B130" s="88" t="inlineStr">
+      <c r="B130" s="101" t="inlineStr">
         <is>
           <t>이브닛</t>
         </is>
       </c>
-      <c r="C130" s="87" t="inlineStr">
+      <c r="C130" s="100" t="inlineStr">
         <is>
           <t>IVNIT</t>
         </is>
       </c>
-      <c r="D130" s="88" t="inlineStr">
+      <c r="D130" s="101" t="inlineStr">
         <is>
           <t>아카이브 스튜디오(AkaiV Studio)</t>
         </is>
       </c>
-      <c r="E130" s="87" t="inlineStr">
+      <c r="E130" s="100" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F130" s="89" t="inlineStr">
+      <c r="F130" s="102" t="inlineStr">
         <is>
           <t>음반/아이돌형</t>
         </is>
@@ -6021,30 +6055,30 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="87" t="n">
+      <c r="A131" s="100" t="n">
         <v>128</v>
       </c>
-      <c r="B131" s="88" t="inlineStr">
+      <c r="B131" s="101" t="inlineStr">
         <is>
           <t>수소진</t>
         </is>
       </c>
-      <c r="C131" s="87" t="inlineStr">
+      <c r="C131" s="100" t="inlineStr">
         <is>
           <t>SOOSOJIN</t>
         </is>
       </c>
-      <c r="D131" s="88" t="inlineStr">
+      <c r="D131" s="101" t="inlineStr">
         <is>
           <t>브라더후드 엔터테인먼트(제작 로코베리)</t>
         </is>
       </c>
-      <c r="E131" s="87" t="inlineStr">
+      <c r="E131" s="100" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F131" s="89" t="inlineStr">
+      <c r="F131" s="102" t="inlineStr">
         <is>
           <t>음반/아이돌형</t>
         </is>
@@ -6061,30 +6095,30 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="87" t="n">
+      <c r="A132" s="100" t="n">
         <v>129</v>
       </c>
-      <c r="B132" s="88" t="inlineStr">
+      <c r="B132" s="101" t="inlineStr">
         <is>
           <t>스파클즈</t>
         </is>
       </c>
-      <c r="C132" s="87" t="inlineStr">
+      <c r="C132" s="100" t="inlineStr">
         <is>
           <t>SPAKLZ</t>
         </is>
       </c>
-      <c r="D132" s="88" t="inlineStr">
+      <c r="D132" s="101" t="inlineStr">
         <is>
           <t>레진엔터테인먼트</t>
         </is>
       </c>
-      <c r="E132" s="87" t="inlineStr">
+      <c r="E132" s="100" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F132" s="89" t="inlineStr">
+      <c r="F132" s="102" t="inlineStr">
         <is>
           <t>음반/아이돌형</t>
         </is>
@@ -6101,25 +6135,25 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="87" t="n">
+      <c r="A133" s="100" t="n">
         <v>130</v>
       </c>
-      <c r="B133" s="88" t="inlineStr">
+      <c r="B133" s="101" t="inlineStr">
         <is>
           <t>헥시아</t>
         </is>
       </c>
-      <c r="C133" s="87" t="inlineStr">
+      <c r="C133" s="100" t="inlineStr">
         <is>
           <t>HEXIA</t>
         </is>
       </c>
-      <c r="D133" s="88" t="inlineStr">
+      <c r="D133" s="101" t="inlineStr">
         <is>
           <t>스콘(SCON)</t>
         </is>
       </c>
-      <c r="E133" s="87" t="inlineStr">
+      <c r="E133" s="100" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
@@ -6141,30 +6175,30 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="87" t="n">
+      <c r="A134" s="100" t="n">
         <v>131</v>
       </c>
-      <c r="B134" s="88" t="inlineStr">
+      <c r="B134" s="101" t="inlineStr">
         <is>
           <t>h.a.l.o</t>
         </is>
       </c>
-      <c r="C134" s="87" t="inlineStr">
+      <c r="C134" s="100" t="inlineStr">
         <is>
           <t>헤일로</t>
         </is>
       </c>
-      <c r="D134" s="88" t="inlineStr">
+      <c r="D134" s="101" t="inlineStr">
         <is>
           <t>스콘(SCON)</t>
         </is>
       </c>
-      <c r="E134" s="87" t="inlineStr">
+      <c r="E134" s="100" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F134" s="92" t="inlineStr">
+      <c r="F134" s="104" t="inlineStr">
         <is>
           <t>혼합형</t>
         </is>
@@ -6181,25 +6215,25 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="87" t="n">
+      <c r="A135" s="100" t="n">
         <v>132</v>
       </c>
-      <c r="B135" s="88" t="inlineStr">
+      <c r="B135" s="101" t="inlineStr">
         <is>
           <t>제나</t>
         </is>
       </c>
-      <c r="C135" s="87" t="inlineStr">
+      <c r="C135" s="100" t="inlineStr">
         <is>
           <t>JENA</t>
         </is>
       </c>
-      <c r="D135" s="88" t="inlineStr">
+      <c r="D135" s="101" t="inlineStr">
         <is>
           <t>뮤즈온</t>
         </is>
       </c>
-      <c r="E135" s="87" t="inlineStr">
+      <c r="E135" s="100" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
@@ -6221,25 +6255,25 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="87" t="n">
+      <c r="A136" s="100" t="n">
         <v>133</v>
       </c>
-      <c r="B136" s="88" t="inlineStr">
+      <c r="B136" s="101" t="inlineStr">
         <is>
           <t>청솔</t>
         </is>
       </c>
-      <c r="C136" s="87" t="inlineStr">
+      <c r="C136" s="100" t="inlineStr">
         <is>
           <t>CHEONGSOL</t>
         </is>
       </c>
-      <c r="D136" s="88" t="inlineStr">
+      <c r="D136" s="101" t="inlineStr">
         <is>
           <t>(미확인)</t>
         </is>
       </c>
-      <c r="E136" s="87" t="inlineStr">
+      <c r="E136" s="100" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
@@ -6261,30 +6295,30 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="87" t="n">
+      <c r="A137" s="100" t="n">
         <v>134</v>
       </c>
-      <c r="B137" s="88" t="inlineStr">
+      <c r="B137" s="101" t="inlineStr">
         <is>
           <t>아이시아</t>
         </is>
       </c>
-      <c r="C137" s="87" t="inlineStr">
+      <c r="C137" s="100" t="inlineStr">
         <is>
           <t>IXIA</t>
         </is>
       </c>
-      <c r="D137" s="88" t="inlineStr">
+      <c r="D137" s="101" t="inlineStr">
         <is>
           <t>(미확인)</t>
         </is>
       </c>
-      <c r="E137" s="87" t="inlineStr">
+      <c r="E137" s="100" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F137" s="89" t="inlineStr">
+      <c r="F137" s="102" t="inlineStr">
         <is>
           <t>음반/아이돌형</t>
         </is>
@@ -6301,30 +6335,30 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="87" t="n">
+      <c r="A138" s="100" t="n">
         <v>135</v>
       </c>
-      <c r="B138" s="88" t="inlineStr">
+      <c r="B138" s="101" t="inlineStr">
         <is>
           <t>클루즈</t>
         </is>
       </c>
-      <c r="C138" s="87" t="inlineStr">
+      <c r="C138" s="100" t="inlineStr">
         <is>
           <t>CLUEZ</t>
         </is>
       </c>
-      <c r="D138" s="88" t="inlineStr">
+      <c r="D138" s="101" t="inlineStr">
         <is>
           <t>카론 유니버스(카론 크리에이티브)</t>
         </is>
       </c>
-      <c r="E138" s="87" t="inlineStr">
+      <c r="E138" s="100" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F138" s="89" t="inlineStr">
+      <c r="F138" s="102" t="inlineStr">
         <is>
           <t>음반/아이돌형</t>
         </is>
@@ -6341,25 +6375,25 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="87" t="n">
+      <c r="A139" s="100" t="n">
         <v>136</v>
       </c>
-      <c r="B139" s="88" t="inlineStr">
+      <c r="B139" s="101" t="inlineStr">
         <is>
           <t>루나데이즈</t>
         </is>
       </c>
-      <c r="C139" s="87" t="inlineStr">
+      <c r="C139" s="100" t="inlineStr">
         <is>
           <t>LUNADAYS</t>
         </is>
       </c>
-      <c r="D139" s="88" t="inlineStr">
+      <c r="D139" s="101" t="inlineStr">
         <is>
           <t>루나데이즈(개인사업자 MCN)</t>
         </is>
       </c>
-      <c r="E139" s="87" t="inlineStr">
+      <c r="E139" s="100" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
@@ -6381,25 +6415,25 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="87" t="n">
+      <c r="A140" s="100" t="n">
         <v>137</v>
       </c>
-      <c r="B140" s="88" t="inlineStr">
+      <c r="B140" s="101" t="inlineStr">
         <is>
           <t>애프터라이브</t>
         </is>
       </c>
-      <c r="C140" s="87" t="inlineStr">
+      <c r="C140" s="100" t="inlineStr">
         <is>
           <t>AfterLive</t>
         </is>
       </c>
-      <c r="D140" s="88" t="inlineStr">
+      <c r="D140" s="101" t="inlineStr">
         <is>
           <t>애프터라이브(자체 런칭)</t>
         </is>
       </c>
-      <c r="E140" s="87" t="inlineStr">
+      <c r="E140" s="100" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
@@ -6421,25 +6455,25 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="87" t="n">
+      <c r="A141" s="100" t="n">
         <v>138</v>
       </c>
-      <c r="B141" s="88" t="inlineStr">
+      <c r="B141" s="101" t="inlineStr">
         <is>
           <t>벨로디</t>
         </is>
       </c>
-      <c r="C141" s="87" t="inlineStr">
+      <c r="C141" s="100" t="inlineStr">
         <is>
           <t>VELODY</t>
         </is>
       </c>
-      <c r="D141" s="88" t="inlineStr">
+      <c r="D141" s="101" t="inlineStr">
         <is>
           <t>벨로디(자체 런칭)</t>
         </is>
       </c>
-      <c r="E141" s="87" t="inlineStr">
+      <c r="E141" s="100" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
@@ -6461,25 +6495,25 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="87" t="n">
+      <c r="A142" s="100" t="n">
         <v>139</v>
       </c>
-      <c r="B142" s="88" t="inlineStr">
+      <c r="B142" s="101" t="inlineStr">
         <is>
           <t>아르포나</t>
         </is>
       </c>
-      <c r="C142" s="87" t="inlineStr">
+      <c r="C142" s="100" t="inlineStr">
         <is>
           <t>Arfauna</t>
         </is>
       </c>
-      <c r="D142" s="88" t="inlineStr">
+      <c r="D142" s="101" t="inlineStr">
         <is>
           <t>아르포나(버추얼 기획사)</t>
         </is>
       </c>
-      <c r="E142" s="87" t="inlineStr">
+      <c r="E142" s="100" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
@@ -6501,25 +6535,25 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="87" t="n">
+      <c r="A143" s="100" t="n">
         <v>140</v>
       </c>
-      <c r="B143" s="88" t="inlineStr">
+      <c r="B143" s="101" t="inlineStr">
         <is>
           <t>바라바라</t>
         </is>
       </c>
-      <c r="C143" s="87" t="inlineStr">
+      <c r="C143" s="100" t="inlineStr">
         <is>
           <t>BARABARA</t>
         </is>
       </c>
-      <c r="D143" s="88" t="inlineStr">
+      <c r="D143" s="101" t="inlineStr">
         <is>
           <t>보쿠하이</t>
         </is>
       </c>
-      <c r="E143" s="87" t="inlineStr">
+      <c r="E143" s="100" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
@@ -6541,30 +6575,30 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="87" t="n">
+      <c r="A144" s="100" t="n">
         <v>141</v>
       </c>
-      <c r="B144" s="88" t="inlineStr">
+      <c r="B144" s="101" t="inlineStr">
         <is>
           <t>신디에잇</t>
         </is>
       </c>
-      <c r="C144" s="87" t="inlineStr">
+      <c r="C144" s="100" t="inlineStr">
         <is>
           <t>SYNDI8</t>
         </is>
       </c>
-      <c r="D144" s="88" t="inlineStr">
+      <c r="D144" s="101" t="inlineStr">
         <is>
           <t>수퍼톤(HYBE 자회사)</t>
         </is>
       </c>
-      <c r="E144" s="87" t="inlineStr">
+      <c r="E144" s="100" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="F144" s="89" t="inlineStr">
+      <c r="F144" s="102" t="inlineStr">
         <is>
           <t>음반/아이돌형</t>
         </is>
@@ -6581,30 +6615,30 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="87" t="n">
+      <c r="A145" s="100" t="n">
         <v>142</v>
       </c>
-      <c r="B145" s="88" t="inlineStr">
+      <c r="B145" s="101" t="inlineStr">
         <is>
           <t>피버스</t>
         </is>
       </c>
-      <c r="C145" s="87" t="inlineStr">
+      <c r="C145" s="100" t="inlineStr">
         <is>
           <t>Feverse</t>
         </is>
       </c>
-      <c r="D145" s="88" t="inlineStr">
+      <c r="D145" s="101" t="inlineStr">
         <is>
           <t>카카오엔터테인먼트</t>
         </is>
       </c>
-      <c r="E145" s="87" t="inlineStr">
+      <c r="E145" s="100" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="F145" s="92" t="inlineStr">
+      <c r="F145" s="104" t="inlineStr">
         <is>
           <t>혼합형</t>
         </is>
@@ -6621,30 +6655,30 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="87" t="n">
+      <c r="A146" s="100" t="n">
         <v>143</v>
       </c>
-      <c r="B146" s="88" t="inlineStr">
+      <c r="B146" s="101" t="inlineStr">
         <is>
           <t>이진법소년들</t>
         </is>
       </c>
-      <c r="C146" s="87" t="inlineStr">
+      <c r="C146" s="100" t="inlineStr">
         <is>
           <t>ØXONE</t>
         </is>
       </c>
-      <c r="D146" s="88" t="inlineStr">
+      <c r="D146" s="101" t="inlineStr">
         <is>
           <t>완구 기업(유통 워너뮤직 ADA)</t>
         </is>
       </c>
-      <c r="E146" s="87" t="inlineStr">
+      <c r="E146" s="100" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="F146" s="89" t="inlineStr">
+      <c r="F146" s="102" t="inlineStr">
         <is>
           <t>음반/아이돌형</t>
         </is>
@@ -6661,30 +6695,30 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="87" t="n">
+      <c r="A147" s="100" t="n">
         <v>144</v>
       </c>
-      <c r="B147" s="88" t="inlineStr">
+      <c r="B147" s="101" t="inlineStr">
         <is>
           <t>홀린</t>
         </is>
       </c>
-      <c r="C147" s="87" t="inlineStr">
+      <c r="C147" s="100" t="inlineStr">
         <is>
           <t>WhOLLiN</t>
         </is>
       </c>
-      <c r="D147" s="88" t="inlineStr">
+      <c r="D147" s="101" t="inlineStr">
         <is>
           <t>플레이리스트(PLAYLIST)</t>
         </is>
       </c>
-      <c r="E147" s="87" t="inlineStr">
+      <c r="E147" s="100" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F147" s="89" t="inlineStr">
+      <c r="F147" s="102" t="inlineStr">
         <is>
           <t>음반/아이돌형</t>
         </is>
@@ -6697,6 +6731,286 @@
       <c r="H147" s="66" t="inlineStr">
         <is>
           <t>'약한영웅' 제작사 플레이리스트 첫 버추얼 보이그룹 5인(시오·태이·이소·강우·도언). 2026.9.1 디지털 싱글 '깨어나다'(타이틀 Time Sleep, 펜타곤 후이 프로듀싱)로 정식 데뷔. (톱셀럽 2026.9.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="100" t="n">
+        <v>145</v>
+      </c>
+      <c r="B148" s="101" t="inlineStr">
+        <is>
+          <t>비그릿츠</t>
+        </is>
+      </c>
+      <c r="C148" s="100" t="inlineStr">
+        <is>
+          <t>BEGRITZ</t>
+        </is>
+      </c>
+      <c r="D148" s="101" t="inlineStr">
+        <is>
+          <t>디네이블(DNABLE)</t>
+        </is>
+      </c>
+      <c r="E148" s="100" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F148" s="102" t="inlineStr">
+        <is>
+          <t>음반/아이돌형</t>
+        </is>
+      </c>
+      <c r="G148" s="103" t="inlineStr">
+        <is>
+          <t>데뷔전</t>
+        </is>
+      </c>
+      <c r="H148" s="66" t="inlineStr">
+        <is>
+          <t>[데뷔 예정 · 2026.8(론칭 예정)] 5인조. '시공간을 모험하는 도깨비' 세계관. 프로듀서 알티(R.Tee) 음악 총괄, 블락비 태일 A&amp;R·보컬디렉터. 실시간 CG·AI·퍼포먼스캡처 결합.</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="100" t="n">
+        <v>146</v>
+      </c>
+      <c r="B149" s="101" t="inlineStr">
+        <is>
+          <t>걸스 아카이브</t>
+        </is>
+      </c>
+      <c r="C149" s="100" t="inlineStr">
+        <is>
+          <t>Girls Archives.</t>
+        </is>
+      </c>
+      <c r="D149" s="101" t="inlineStr">
+        <is>
+          <t>하이브 NEB × INCS toenter(일본)</t>
+        </is>
+      </c>
+      <c r="E149" s="100" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F149" s="104" t="inlineStr">
+        <is>
+          <t>혼합형</t>
+        </is>
+      </c>
+      <c r="G149" s="103" t="inlineStr">
+        <is>
+          <t>데뷔전</t>
+        </is>
+      </c>
+      <c r="H149" s="66" t="inlineStr">
+        <is>
+          <t>[프리데뷔 예정 · 2026.8.7 프리데뷔] ※실사 멤버+버추얼 캐릭터 연동 하이브리드(2.5D) — 완전 버추얼 아님, 경계 사례. 5인(유이사·에나·서연·히나리·소정). 싱글 'Reborn'=넷플릭스 '리본 히어로' 주제곡. 숀·허니웍스 프로듀싱, 캐릭터 디자인 LAM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="100" t="n">
+        <v>147</v>
+      </c>
+      <c r="B150" s="101" t="inlineStr">
+        <is>
+          <t>코스믹코드</t>
+        </is>
+      </c>
+      <c r="C150" s="100" t="inlineStr">
+        <is>
+          <t>COSMIC CODE</t>
+        </is>
+      </c>
+      <c r="D150" s="101" t="inlineStr">
+        <is>
+          <t>에이탑유니버스</t>
+        </is>
+      </c>
+      <c r="E150" s="100" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F150" s="102" t="inlineStr">
+        <is>
+          <t>음반/아이돌형</t>
+        </is>
+      </c>
+      <c r="G150" s="103" t="inlineStr">
+        <is>
+          <t>데뷔전</t>
+        </is>
+      </c>
+      <c r="H150" s="66" t="inlineStr">
+        <is>
+          <t>[프리데뷔(멤버 순차 공개) · 2026.9.9~] 일본 우타이테 시장 겨냥 2.5D 버추얼 아이돌 5인. 프리데뷔 싱글 'POKER FACE', 2026.11 도쿄·오사카 공연 추진. 日 YOANI 3억엔 투자. (한국일보 2026.9.9)</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="100" t="n">
+        <v>148</v>
+      </c>
+      <c r="B151" s="101" t="inlineStr">
+        <is>
+          <t>STUN-X</t>
+        </is>
+      </c>
+      <c r="C151" s="100" t="inlineStr">
+        <is>
+          <t>우주아이돌리그</t>
+        </is>
+      </c>
+      <c r="D151" s="101" t="inlineStr">
+        <is>
+          <t>밀리언볼트(애니 스튜디오)</t>
+        </is>
+      </c>
+      <c r="E151" s="100" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F151" s="102" t="inlineStr">
+        <is>
+          <t>음반/아이돌형</t>
+        </is>
+      </c>
+      <c r="G151" s="103" t="inlineStr">
+        <is>
+          <t>데뷔전</t>
+        </is>
+      </c>
+      <c r="H151" s="66" t="inlineStr">
+        <is>
+          <t>[데뷔 예정 · 2026.10.2] 2D 버추얼 아이돌 IP. 웹소설 2026.9.10 카카오페이지 연재, 10.2 첫 디지털 싱글 예정. 캐릭터 콘텐츠 누적 2,000만뷰. (MBN 2026.9.11)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="100" t="n">
+        <v>149</v>
+      </c>
+      <c r="B152" s="101" t="inlineStr">
+        <is>
+          <t>WINKX</t>
+        </is>
+      </c>
+      <c r="C152" s="100" t="inlineStr">
+        <is>
+          <t>윙스</t>
+        </is>
+      </c>
+      <c r="D152" s="101" t="inlineStr">
+        <is>
+          <t>타이탄콘텐츠 × 대원미디어</t>
+        </is>
+      </c>
+      <c r="E152" s="100" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F152" s="102" t="inlineStr">
+        <is>
+          <t>음반/아이돌형</t>
+        </is>
+      </c>
+      <c r="G152" s="103" t="inlineStr">
+        <is>
+          <t>데뷔전</t>
+        </is>
+      </c>
+      <c r="H152" s="66" t="inlineStr">
+        <is>
+          <t>[데뷔 예정(MOU 단계) · 미확인] 360도 글로벌 IP(음악·만화·애니) 공동사업. 모션캡처 대원 자회사 이엠피. 일정 미확인. (스타뉴스 2026.4.15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="100" t="n">
+        <v>150</v>
+      </c>
+      <c r="B153" s="101" t="inlineStr">
+        <is>
+          <t>레드소다써클</t>
+        </is>
+      </c>
+      <c r="C153" s="100" t="inlineStr">
+        <is>
+          <t>Red Soda Circle</t>
+        </is>
+      </c>
+      <c r="D153" s="101" t="inlineStr">
+        <is>
+          <t>코드판타지아</t>
+        </is>
+      </c>
+      <c r="E153" s="100" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F153" s="104" t="inlineStr">
+        <is>
+          <t>혼합형</t>
+        </is>
+      </c>
+      <c r="G153" s="103" t="inlineStr">
+        <is>
+          <t>데뷔전</t>
+        </is>
+      </c>
+      <c r="H153" s="66" t="inlineStr">
+        <is>
+          <t>[프리데뷔 · 2025.12.22] ※실사+버추얼 병행 하이브리드('리얼 라이프 듀얼 포맷'). 한일 2인조(리나·하루). 2025.12.22 첫 버추얼 라이브. (스포츠경향 2025.12.22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="107" t="n">
+        <v>151</v>
+      </c>
+      <c r="B154" s="108" t="inlineStr">
+        <is>
+          <t>비더후드</t>
+        </is>
+      </c>
+      <c r="C154" s="107" t="inlineStr">
+        <is>
+          <t>B THE HOOD</t>
+        </is>
+      </c>
+      <c r="D154" s="108" t="inlineStr">
+        <is>
+          <t>레벨스(LEVVELS·하이브×두나무 합작)</t>
+        </is>
+      </c>
+      <c r="E154" s="107" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F154" s="109" t="inlineStr">
+        <is>
+          <t>음반/아이돌형</t>
+        </is>
+      </c>
+      <c r="G154" s="110" t="inlineStr">
+        <is>
+          <t>데뷔전</t>
+        </is>
+      </c>
+      <c r="H154" s="66" t="inlineStr">
+        <is>
+          <t>[프리데뷔 · 선공개 3장] 5인조(이언·제이스·퍼비·기류·루안). 'Lowkey'(6.26)·'The Baddest'(7.31)·'JADED'(8.21, 정식 데뷔 전 마지막 선공개). 다크SF 세계관. 유튜브 개설 7주 만에 구독 10만, 쇼츠 500만뷰. 정식 데뷔 시 활동중 전환.</t>
         </is>
       </c>
     </row>
@@ -8074,7 +8388,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="22" customWidth="1" style="40" min="1" max="1"/>
@@ -8095,7 +8409,7 @@
         </is>
       </c>
       <c r="B3" s="46">
-        <f>COUNTA('버추얼 그룹 전수목록'!B4:B126)</f>
+        <f>COUNTA('버추얼 그룹 전수목록'!B4:B153)</f>
         <v/>
       </c>
     </row>
@@ -8106,7 +8420,7 @@
         </is>
       </c>
       <c r="B4" s="46">
-        <f>COUNTIF('버추얼 그룹 전수목록'!G4:G126,"활동중")</f>
+        <f>COUNTIF('버추얼 그룹 전수목록'!G4:G153,"활동중")</f>
         <v/>
       </c>
     </row>
@@ -8117,7 +8431,7 @@
         </is>
       </c>
       <c r="B5" s="46">
-        <f>COUNTIF('버추얼 그룹 전수목록'!G4:G126,"해체/종료")</f>
+        <f>COUNTIF('버추얼 그룹 전수목록'!G4:G153,"해체/종료")</f>
         <v/>
       </c>
     </row>
@@ -8128,7 +8442,7 @@
         </is>
       </c>
       <c r="B6" s="46">
-        <f>COUNTIF('버추얼 그룹 전수목록'!G4:G126,"전환")</f>
+        <f>COUNTIF('버추얼 그룹 전수목록'!G4:G153,"전환")</f>
         <v/>
       </c>
     </row>
@@ -8139,7 +8453,7 @@
         </is>
       </c>
       <c r="B7" s="46">
-        <f>COUNTIF('버추얼 그룹 전수목록'!G4:G126,"확인필요")</f>
+        <f>COUNTIF('버추얼 그룹 전수목록'!G4:G153,"확인필요")</f>
         <v/>
       </c>
     </row>
@@ -8150,59 +8464,70 @@
         </is>
       </c>
       <c r="B8" s="73">
-        <f>COUNTIF('버추얼 그룹 전수목록'!G4:G126,"휴면")</f>
+        <f>COUNTIF('버추얼 그룹 전수목록'!G4:G153,"휴면")</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="15" customHeight="1" s="41">
-      <c r="A9" s="71" t="inlineStr">
-        <is>
-          <t>─ 분류별 ─</t>
-        </is>
-      </c>
-      <c r="B9" s="46" t="n"/>
+      <c r="A9" s="105" t="inlineStr">
+        <is>
+          <t>데뷔전(프리데뷔·예정)</t>
+        </is>
+      </c>
+      <c r="B9" s="106">
+        <f>COUNTIF('버추얼 그룹 전수목록'!G4:G153,"데뷔전")</f>
+        <v/>
+      </c>
     </row>
     <row r="10" ht="15" customHeight="1" s="41">
       <c r="A10" s="71" t="inlineStr">
         <is>
-          <t>음반/아이돌형</t>
-        </is>
-      </c>
-      <c r="B10" s="46">
-        <f>COUNTIF('버추얼 그룹 전수목록'!F4:F126,"음반/아이돌형")</f>
-        <v/>
-      </c>
+          <t>─ 분류별 ─</t>
+        </is>
+      </c>
+      <c r="B10" s="46" t="n"/>
     </row>
     <row r="11" ht="15" customHeight="1" s="41">
       <c r="A11" s="71" t="inlineStr">
         <is>
-          <t>버추얼휴먼/솔로</t>
+          <t>음반/아이돌형</t>
         </is>
       </c>
       <c r="B11" s="46">
-        <f>COUNTIF('버추얼 그룹 전수목록'!F4:F126,"버추얼휴먼/솔로")</f>
+        <f>COUNTIF('버추얼 그룹 전수목록'!F4:F153,"음반/아이돌형")</f>
         <v/>
       </c>
     </row>
     <row r="12" ht="15" customHeight="1" s="41">
       <c r="A12" s="71" t="inlineStr">
         <is>
-          <t>스트리밍/MCN형</t>
+          <t>버추얼휴먼/솔로</t>
         </is>
       </c>
       <c r="B12" s="46">
-        <f>COUNTIF('버추얼 그룹 전수목록'!F4:F126,"스트리밍/MCN형")</f>
+        <f>COUNTIF('버추얼 그룹 전수목록'!F4:F153,"버추얼휴먼/솔로")</f>
         <v/>
       </c>
     </row>
     <row r="13" ht="15" customHeight="1" s="41">
       <c r="A13" s="71" t="inlineStr">
         <is>
+          <t>스트리밍/MCN형</t>
+        </is>
+      </c>
+      <c r="B13" s="46">
+        <f>COUNTIF('버추얼 그룹 전수목록'!F4:F153,"스트리밍/MCN형")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="71" t="inlineStr">
+        <is>
           <t>혼합형</t>
         </is>
       </c>
-      <c r="B13" s="46">
-        <f>COUNTIF('버추얼 그룹 전수목록'!F4:F126,"혼합형")</f>
+      <c r="B14" s="46">
+        <f>COUNTIF('버추얼 그룹 전수목록'!F4:F153,"혼합형")</f>
         <v/>
       </c>
     </row>
@@ -8537,22 +8862,22 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="88" t="inlineStr">
+      <c r="A13" s="101" t="inlineStr">
         <is>
           <t>비더후드 (B THE HOOD)</t>
         </is>
       </c>
-      <c r="B13" s="87" t="inlineStr">
+      <c r="B13" s="100" t="inlineStr">
         <is>
           <t>레벨스(LEVVELS·하이브×두나무 합작)</t>
         </is>
       </c>
-      <c r="C13" s="88" t="inlineStr">
+      <c r="C13" s="101" t="inlineStr">
         <is>
           <t>프리데뷔 완료(선공개 3장) · 정식 데뷔 임박</t>
         </is>
       </c>
-      <c r="D13" s="87" t="inlineStr">
+      <c r="D13" s="100" t="inlineStr">
         <is>
           <t>선공개 2026.6.26/7.31/8.21 · 정식 데뷔일 미확인</t>
         </is>
@@ -8564,22 +8889,22 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="88" t="inlineStr">
+      <c r="A14" s="101" t="inlineStr">
         <is>
           <t>비그릿츠 (BEGRITZ)</t>
         </is>
       </c>
-      <c r="B14" s="87" t="inlineStr">
+      <c r="B14" s="100" t="inlineStr">
         <is>
           <t>디네이블(DNABLE)</t>
         </is>
       </c>
-      <c r="C14" s="88" t="inlineStr">
+      <c r="C14" s="101" t="inlineStr">
         <is>
           <t>데뷔 예정</t>
         </is>
       </c>
-      <c r="D14" s="87" t="inlineStr">
+      <c r="D14" s="100" t="inlineStr">
         <is>
           <t>2026.8(론칭 예정)</t>
         </is>
@@ -8591,22 +8916,22 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="88" t="inlineStr">
+      <c r="A15" s="101" t="inlineStr">
         <is>
           <t>홀린 (WhOLLiN)</t>
         </is>
       </c>
-      <c r="B15" s="87" t="inlineStr">
+      <c r="B15" s="100" t="inlineStr">
         <is>
           <t>플레이리스트(PLAYLIST)</t>
         </is>
       </c>
-      <c r="C15" s="88" t="inlineStr">
+      <c r="C15" s="101" t="inlineStr">
         <is>
           <t>정식 데뷔 완료(2026.9.1) → 전수목록 편입</t>
         </is>
       </c>
-      <c r="D15" s="87" t="inlineStr">
+      <c r="D15" s="100" t="inlineStr">
         <is>
           <t>2026.9.1</t>
         </is>
@@ -8618,22 +8943,22 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="88" t="inlineStr">
+      <c r="A16" s="101" t="inlineStr">
         <is>
           <t>걸스 아카이브 (Girls Archives.)</t>
         </is>
       </c>
-      <c r="B16" s="87" t="inlineStr">
+      <c r="B16" s="100" t="inlineStr">
         <is>
           <t>하이브 NEB × INCS toenter(일본)</t>
         </is>
       </c>
-      <c r="C16" s="88" t="inlineStr">
+      <c r="C16" s="101" t="inlineStr">
         <is>
           <t>프리데뷔 예정</t>
         </is>
       </c>
-      <c r="D16" s="87" t="inlineStr">
+      <c r="D16" s="100" t="inlineStr">
         <is>
           <t>2026.8.7 프리데뷔</t>
         </is>
@@ -8645,22 +8970,22 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="88" t="inlineStr">
+      <c r="A17" s="101" t="inlineStr">
         <is>
           <t>코스믹코드 (COSMIC CODE)</t>
         </is>
       </c>
-      <c r="B17" s="87" t="inlineStr">
+      <c r="B17" s="100" t="inlineStr">
         <is>
           <t>에이탑유니버스</t>
         </is>
       </c>
-      <c r="C17" s="88" t="inlineStr">
+      <c r="C17" s="101" t="inlineStr">
         <is>
           <t>프리데뷔(멤버 순차 공개)</t>
         </is>
       </c>
-      <c r="D17" s="87" t="inlineStr">
+      <c r="D17" s="100" t="inlineStr">
         <is>
           <t>2026.9.9~</t>
         </is>
@@ -8672,22 +8997,22 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="88" t="inlineStr">
+      <c r="A18" s="101" t="inlineStr">
         <is>
           <t>STUN-X (우주아이돌리그)</t>
         </is>
       </c>
-      <c r="B18" s="87" t="inlineStr">
+      <c r="B18" s="100" t="inlineStr">
         <is>
           <t>밀리언볼트(애니 스튜디오)</t>
         </is>
       </c>
-      <c r="C18" s="88" t="inlineStr">
+      <c r="C18" s="101" t="inlineStr">
         <is>
           <t>데뷔 예정</t>
         </is>
       </c>
-      <c r="D18" s="87" t="inlineStr">
+      <c r="D18" s="100" t="inlineStr">
         <is>
           <t>2026.10.2</t>
         </is>
@@ -8699,22 +9024,22 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="88" t="inlineStr">
+      <c r="A19" s="101" t="inlineStr">
         <is>
           <t>WINKX (윙스)</t>
         </is>
       </c>
-      <c r="B19" s="87" t="inlineStr">
+      <c r="B19" s="100" t="inlineStr">
         <is>
           <t>타이탄콘텐츠 × 대원미디어</t>
         </is>
       </c>
-      <c r="C19" s="88" t="inlineStr">
+      <c r="C19" s="101" t="inlineStr">
         <is>
           <t>데뷔 예정(MOU 단계)</t>
         </is>
       </c>
-      <c r="D19" s="87" t="inlineStr">
+      <c r="D19" s="100" t="inlineStr">
         <is>
           <t>미확인</t>
         </is>
@@ -8726,22 +9051,22 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="88" t="inlineStr">
+      <c r="A20" s="101" t="inlineStr">
         <is>
           <t>레드소다써클 (Red Soda Circle)</t>
         </is>
       </c>
-      <c r="B20" s="87" t="inlineStr">
+      <c r="B20" s="100" t="inlineStr">
         <is>
           <t>코드판타지아</t>
         </is>
       </c>
-      <c r="C20" s="88" t="inlineStr">
+      <c r="C20" s="101" t="inlineStr">
         <is>
           <t>프리데뷔</t>
         </is>
       </c>
-      <c r="D20" s="87" t="inlineStr">
+      <c r="D20" s="100" t="inlineStr">
         <is>
           <t>2025.12.22</t>
         </is>

--- a/data/한국_버추얼아이돌_전수조사_v8.xlsx
+++ b/data/한국_버추얼아이돌_전수조사_v8.xlsx
@@ -1037,7 +1037,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H154"/>
+  <dimension ref="A1:H157"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="40" min="1" max="1"/>
@@ -2675,12 +2675,16 @@
           <t>스트리밍/MCN형</t>
         </is>
       </c>
-      <c r="G43" s="50" t="inlineStr">
-        <is>
-          <t>활동중</t>
-        </is>
-      </c>
-      <c r="H43" s="51" t="n"/>
+      <c r="G43" s="55" t="inlineStr">
+        <is>
+          <t>해체/종료</t>
+        </is>
+      </c>
+      <c r="H43" s="51" t="inlineStr">
+        <is>
+          <t>구 카토 유니버스(전 솔레어 출신). 나무위키 목록 「2025년 활동 종료」 분류. (2026-10-06 확인)</t>
+        </is>
+      </c>
     </row>
     <row r="44" ht="15" customHeight="1" s="41">
       <c r="A44" s="46" t="n">
@@ -3047,12 +3051,16 @@
           <t>스트리밍/MCN형</t>
         </is>
       </c>
-      <c r="G53" s="50" t="inlineStr">
-        <is>
-          <t>활동중</t>
-        </is>
-      </c>
-      <c r="H53" s="51" t="n"/>
+      <c r="G53" s="55" t="inlineStr">
+        <is>
+          <t>해체/종료</t>
+        </is>
+      </c>
+      <c r="H53" s="51" t="inlineStr">
+        <is>
+          <t>2026.2.23 사업 해체, 전원 개인세 전환. (나무위키 버츄얼 그룹 목록 「2026년 활동 종료」, 2026-10-06 확인)</t>
+        </is>
+      </c>
     </row>
     <row r="54" ht="15" customHeight="1" s="41">
       <c r="A54" s="46" t="n">
@@ -3126,7 +3134,7 @@
       </c>
       <c r="H55" s="51" t="inlineStr">
         <is>
-          <t>2024.1 데뷔. 2024.2 치지직 이적</t>
+          <t>2024.1 데뷔. 2024.2 치지직 이적 2026.9.22 멤버 망내 전속계약 위반으로 퇴출(톱셀럽 2026.9.29).</t>
         </is>
       </c>
     </row>
@@ -3267,12 +3275,16 @@
           <t>스트리밍/MCN형</t>
         </is>
       </c>
-      <c r="G59" s="50" t="inlineStr">
-        <is>
-          <t>활동중</t>
-        </is>
-      </c>
-      <c r="H59" s="51" t="n"/>
+      <c r="G59" s="55" t="inlineStr">
+        <is>
+          <t>해체/종료</t>
+        </is>
+      </c>
+      <c r="H59" s="51" t="inlineStr">
+        <is>
+          <t>2026.8.31 사업 철수, 남은 멤버 졸업·개인세 전환. (나무위키 목록 「2026년 활동 종료」, 2026-10-06 확인)</t>
+        </is>
+      </c>
     </row>
     <row r="60" ht="15" customHeight="1" s="41">
       <c r="A60" s="46" t="n">
@@ -3339,12 +3351,16 @@
           <t>스트리밍/MCN형</t>
         </is>
       </c>
-      <c r="G61" s="50" t="inlineStr">
-        <is>
-          <t>활동중</t>
-        </is>
-      </c>
-      <c r="H61" s="51" t="n"/>
+      <c r="G61" s="55" t="inlineStr">
+        <is>
+          <t>해체/종료</t>
+        </is>
+      </c>
+      <c r="H61" s="51" t="inlineStr">
+        <is>
+          <t>2024.6.30 데뷔 크루(치지직). 나무위키 목록 「2025년 활동 종료」 분류. (2026-10-06 확인)</t>
+        </is>
+      </c>
     </row>
     <row r="62" ht="15" customHeight="1" s="41">
       <c r="A62" s="46" t="n">
@@ -4410,7 +4426,7 @@
       </c>
       <c r="H89" s="51" t="inlineStr">
         <is>
-          <t>5인조 걸그룹(고양이 모티브). 지한·이비·수아·리츠·초은. 2025.11 프리데뷔→2026.4 정식데뷔</t>
+          <t>5인조 걸그룹(고양이 모티브). 지한·이비·수아·리츠·초은. 2025.11 프리데뷔→2026.4 정식데뷔 2026.8 새 멤버 카나 합류. 2026.9.15 첫 미니 'With U' 발매(일간스포츠 2026.9.16).</t>
         </is>
       </c>
     </row>
@@ -4450,7 +4466,7 @@
       </c>
       <c r="H90" s="51" t="inlineStr">
         <is>
-          <t>5인조 보이그룹(새온·유성·하이든·제하·전설). 전생 톱아이돌 환생 컨셉. 2026.1 데뷔, 月 연속 서사 발매</t>
+          <t>5인조 보이그룹(새온·유성·하이든·제하·전설). 전생 톱아이돌 환생 컨셉. 2026.1 데뷔, 月 연속 서사 발매 2026.8.24 새 멤버 지운 합류 공개(5인 체제). 2026.9 어코드엔터 프리A 20억 투자, 9.30 신곡 '구름보다 빠르게'.</t>
         </is>
       </c>
     </row>
@@ -5895,30 +5911,30 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="100" t="n">
+      <c r="A127" s="107" t="n">
         <v>124</v>
       </c>
-      <c r="B127" s="101" t="inlineStr">
+      <c r="B127" s="108" t="inlineStr">
         <is>
           <t>오위스</t>
         </is>
       </c>
-      <c r="C127" s="100" t="inlineStr">
+      <c r="C127" s="107" t="inlineStr">
         <is>
           <t>OWIS</t>
         </is>
       </c>
-      <c r="D127" s="101" t="inlineStr">
+      <c r="D127" s="108" t="inlineStr">
         <is>
           <t>올마이애닉도츠(ama)</t>
         </is>
       </c>
-      <c r="E127" s="100" t="inlineStr">
+      <c r="E127" s="107" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F127" s="102" t="inlineStr">
+      <c r="F127" s="109" t="inlineStr">
         <is>
           <t>음반/아이돌형</t>
         </is>
@@ -5935,25 +5951,25 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="100" t="n">
+      <c r="A128" s="107" t="n">
         <v>125</v>
       </c>
-      <c r="B128" s="101" t="inlineStr">
+      <c r="B128" s="108" t="inlineStr">
         <is>
           <t>우주괴담</t>
         </is>
       </c>
-      <c r="C128" s="100" t="inlineStr">
+      <c r="C128" s="107" t="inlineStr">
         <is>
           <t>SPACE HORROR</t>
         </is>
       </c>
-      <c r="D128" s="101" t="inlineStr">
+      <c r="D128" s="108" t="inlineStr">
         <is>
           <t>그림 프로덕션(마운드미디어)</t>
         </is>
       </c>
-      <c r="E128" s="100" t="inlineStr">
+      <c r="E128" s="107" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
@@ -5975,30 +5991,30 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="100" t="n">
+      <c r="A129" s="107" t="n">
         <v>126</v>
       </c>
-      <c r="B129" s="101" t="inlineStr">
+      <c r="B129" s="108" t="inlineStr">
         <is>
           <t>미완소년</t>
         </is>
       </c>
-      <c r="C129" s="100" t="inlineStr">
+      <c r="C129" s="107" t="inlineStr">
         <is>
           <t>美完少年</t>
         </is>
       </c>
-      <c r="D129" s="101" t="inlineStr">
+      <c r="D129" s="108" t="inlineStr">
         <is>
           <t>어비스컴퍼니</t>
         </is>
       </c>
-      <c r="E129" s="100" t="inlineStr">
+      <c r="E129" s="107" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F129" s="102" t="inlineStr">
+      <c r="F129" s="109" t="inlineStr">
         <is>
           <t>음반/아이돌형</t>
         </is>
@@ -6015,30 +6031,30 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="100" t="n">
+      <c r="A130" s="107" t="n">
         <v>127</v>
       </c>
-      <c r="B130" s="101" t="inlineStr">
+      <c r="B130" s="108" t="inlineStr">
         <is>
           <t>이브닛</t>
         </is>
       </c>
-      <c r="C130" s="100" t="inlineStr">
+      <c r="C130" s="107" t="inlineStr">
         <is>
           <t>IVNIT</t>
         </is>
       </c>
-      <c r="D130" s="101" t="inlineStr">
+      <c r="D130" s="108" t="inlineStr">
         <is>
           <t>아카이브 스튜디오(AkaiV Studio)</t>
         </is>
       </c>
-      <c r="E130" s="100" t="inlineStr">
+      <c r="E130" s="107" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F130" s="102" t="inlineStr">
+      <c r="F130" s="109" t="inlineStr">
         <is>
           <t>음반/아이돌형</t>
         </is>
@@ -6055,30 +6071,30 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="100" t="n">
+      <c r="A131" s="107" t="n">
         <v>128</v>
       </c>
-      <c r="B131" s="101" t="inlineStr">
+      <c r="B131" s="108" t="inlineStr">
         <is>
           <t>수소진</t>
         </is>
       </c>
-      <c r="C131" s="100" t="inlineStr">
+      <c r="C131" s="107" t="inlineStr">
         <is>
           <t>SOOSOJIN</t>
         </is>
       </c>
-      <c r="D131" s="101" t="inlineStr">
+      <c r="D131" s="108" t="inlineStr">
         <is>
           <t>브라더후드 엔터테인먼트(제작 로코베리)</t>
         </is>
       </c>
-      <c r="E131" s="100" t="inlineStr">
+      <c r="E131" s="107" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F131" s="102" t="inlineStr">
+      <c r="F131" s="109" t="inlineStr">
         <is>
           <t>음반/아이돌형</t>
         </is>
@@ -6095,30 +6111,30 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="100" t="n">
+      <c r="A132" s="107" t="n">
         <v>129</v>
       </c>
-      <c r="B132" s="101" t="inlineStr">
+      <c r="B132" s="108" t="inlineStr">
         <is>
           <t>스파클즈</t>
         </is>
       </c>
-      <c r="C132" s="100" t="inlineStr">
+      <c r="C132" s="107" t="inlineStr">
         <is>
           <t>SPAKLZ</t>
         </is>
       </c>
-      <c r="D132" s="101" t="inlineStr">
+      <c r="D132" s="108" t="inlineStr">
         <is>
           <t>레진엔터테인먼트</t>
         </is>
       </c>
-      <c r="E132" s="100" t="inlineStr">
+      <c r="E132" s="107" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F132" s="102" t="inlineStr">
+      <c r="F132" s="109" t="inlineStr">
         <is>
           <t>음반/아이돌형</t>
         </is>
@@ -6135,25 +6151,25 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="100" t="n">
+      <c r="A133" s="107" t="n">
         <v>130</v>
       </c>
-      <c r="B133" s="101" t="inlineStr">
+      <c r="B133" s="108" t="inlineStr">
         <is>
           <t>헥시아</t>
         </is>
       </c>
-      <c r="C133" s="100" t="inlineStr">
+      <c r="C133" s="107" t="inlineStr">
         <is>
           <t>HEXIA</t>
         </is>
       </c>
-      <c r="D133" s="101" t="inlineStr">
+      <c r="D133" s="108" t="inlineStr">
         <is>
           <t>스콘(SCON)</t>
         </is>
       </c>
-      <c r="E133" s="100" t="inlineStr">
+      <c r="E133" s="107" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
@@ -6175,25 +6191,25 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="100" t="n">
+      <c r="A134" s="107" t="n">
         <v>131</v>
       </c>
-      <c r="B134" s="101" t="inlineStr">
+      <c r="B134" s="108" t="inlineStr">
         <is>
           <t>h.a.l.o</t>
         </is>
       </c>
-      <c r="C134" s="100" t="inlineStr">
+      <c r="C134" s="107" t="inlineStr">
         <is>
           <t>헤일로</t>
         </is>
       </c>
-      <c r="D134" s="101" t="inlineStr">
+      <c r="D134" s="108" t="inlineStr">
         <is>
           <t>스콘(SCON)</t>
         </is>
       </c>
-      <c r="E134" s="100" t="inlineStr">
+      <c r="E134" s="107" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
@@ -6215,25 +6231,25 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="100" t="n">
+      <c r="A135" s="107" t="n">
         <v>132</v>
       </c>
-      <c r="B135" s="101" t="inlineStr">
+      <c r="B135" s="108" t="inlineStr">
         <is>
           <t>제나</t>
         </is>
       </c>
-      <c r="C135" s="100" t="inlineStr">
+      <c r="C135" s="107" t="inlineStr">
         <is>
           <t>JENA</t>
         </is>
       </c>
-      <c r="D135" s="101" t="inlineStr">
+      <c r="D135" s="108" t="inlineStr">
         <is>
           <t>뮤즈온</t>
         </is>
       </c>
-      <c r="E135" s="100" t="inlineStr">
+      <c r="E135" s="107" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
@@ -6255,25 +6271,25 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="100" t="n">
+      <c r="A136" s="107" t="n">
         <v>133</v>
       </c>
-      <c r="B136" s="101" t="inlineStr">
+      <c r="B136" s="108" t="inlineStr">
         <is>
           <t>청솔</t>
         </is>
       </c>
-      <c r="C136" s="100" t="inlineStr">
+      <c r="C136" s="107" t="inlineStr">
         <is>
           <t>CHEONGSOL</t>
         </is>
       </c>
-      <c r="D136" s="101" t="inlineStr">
+      <c r="D136" s="108" t="inlineStr">
         <is>
           <t>(미확인)</t>
         </is>
       </c>
-      <c r="E136" s="100" t="inlineStr">
+      <c r="E136" s="107" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
@@ -6295,30 +6311,30 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="100" t="n">
+      <c r="A137" s="107" t="n">
         <v>134</v>
       </c>
-      <c r="B137" s="101" t="inlineStr">
+      <c r="B137" s="108" t="inlineStr">
         <is>
           <t>아이시아</t>
         </is>
       </c>
-      <c r="C137" s="100" t="inlineStr">
+      <c r="C137" s="107" t="inlineStr">
         <is>
           <t>IXIA</t>
         </is>
       </c>
-      <c r="D137" s="101" t="inlineStr">
+      <c r="D137" s="108" t="inlineStr">
         <is>
           <t>(미확인)</t>
         </is>
       </c>
-      <c r="E137" s="100" t="inlineStr">
+      <c r="E137" s="107" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F137" s="102" t="inlineStr">
+      <c r="F137" s="109" t="inlineStr">
         <is>
           <t>음반/아이돌형</t>
         </is>
@@ -6335,30 +6351,30 @@
       </c>
     </row>
     <row r="138">
-      <c r="A138" s="100" t="n">
+      <c r="A138" s="107" t="n">
         <v>135</v>
       </c>
-      <c r="B138" s="101" t="inlineStr">
+      <c r="B138" s="108" t="inlineStr">
         <is>
           <t>클루즈</t>
         </is>
       </c>
-      <c r="C138" s="100" t="inlineStr">
+      <c r="C138" s="107" t="inlineStr">
         <is>
           <t>CLUEZ</t>
         </is>
       </c>
-      <c r="D138" s="101" t="inlineStr">
+      <c r="D138" s="108" t="inlineStr">
         <is>
           <t>카론 유니버스(카론 크리에이티브)</t>
         </is>
       </c>
-      <c r="E138" s="100" t="inlineStr">
+      <c r="E138" s="107" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F138" s="102" t="inlineStr">
+      <c r="F138" s="109" t="inlineStr">
         <is>
           <t>음반/아이돌형</t>
         </is>
@@ -6375,25 +6391,25 @@
       </c>
     </row>
     <row r="139">
-      <c r="A139" s="100" t="n">
+      <c r="A139" s="107" t="n">
         <v>136</v>
       </c>
-      <c r="B139" s="101" t="inlineStr">
+      <c r="B139" s="108" t="inlineStr">
         <is>
           <t>루나데이즈</t>
         </is>
       </c>
-      <c r="C139" s="100" t="inlineStr">
+      <c r="C139" s="107" t="inlineStr">
         <is>
           <t>LUNADAYS</t>
         </is>
       </c>
-      <c r="D139" s="101" t="inlineStr">
+      <c r="D139" s="108" t="inlineStr">
         <is>
           <t>루나데이즈(개인사업자 MCN)</t>
         </is>
       </c>
-      <c r="E139" s="100" t="inlineStr">
+      <c r="E139" s="107" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
@@ -6415,25 +6431,25 @@
       </c>
     </row>
     <row r="140">
-      <c r="A140" s="100" t="n">
+      <c r="A140" s="107" t="n">
         <v>137</v>
       </c>
-      <c r="B140" s="101" t="inlineStr">
+      <c r="B140" s="108" t="inlineStr">
         <is>
           <t>애프터라이브</t>
         </is>
       </c>
-      <c r="C140" s="100" t="inlineStr">
+      <c r="C140" s="107" t="inlineStr">
         <is>
           <t>AfterLive</t>
         </is>
       </c>
-      <c r="D140" s="101" t="inlineStr">
+      <c r="D140" s="108" t="inlineStr">
         <is>
           <t>애프터라이브(자체 런칭)</t>
         </is>
       </c>
-      <c r="E140" s="100" t="inlineStr">
+      <c r="E140" s="107" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
@@ -6455,25 +6471,25 @@
       </c>
     </row>
     <row r="141">
-      <c r="A141" s="100" t="n">
+      <c r="A141" s="107" t="n">
         <v>138</v>
       </c>
-      <c r="B141" s="101" t="inlineStr">
+      <c r="B141" s="108" t="inlineStr">
         <is>
           <t>벨로디</t>
         </is>
       </c>
-      <c r="C141" s="100" t="inlineStr">
+      <c r="C141" s="107" t="inlineStr">
         <is>
           <t>VELODY</t>
         </is>
       </c>
-      <c r="D141" s="101" t="inlineStr">
+      <c r="D141" s="108" t="inlineStr">
         <is>
           <t>벨로디(자체 런칭)</t>
         </is>
       </c>
-      <c r="E141" s="100" t="inlineStr">
+      <c r="E141" s="107" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
@@ -6495,25 +6511,25 @@
       </c>
     </row>
     <row r="142">
-      <c r="A142" s="100" t="n">
+      <c r="A142" s="107" t="n">
         <v>139</v>
       </c>
-      <c r="B142" s="101" t="inlineStr">
+      <c r="B142" s="108" t="inlineStr">
         <is>
           <t>아르포나</t>
         </is>
       </c>
-      <c r="C142" s="100" t="inlineStr">
+      <c r="C142" s="107" t="inlineStr">
         <is>
           <t>Arfauna</t>
         </is>
       </c>
-      <c r="D142" s="101" t="inlineStr">
+      <c r="D142" s="108" t="inlineStr">
         <is>
           <t>아르포나(버추얼 기획사)</t>
         </is>
       </c>
-      <c r="E142" s="100" t="inlineStr">
+      <c r="E142" s="107" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
@@ -6535,25 +6551,25 @@
       </c>
     </row>
     <row r="143">
-      <c r="A143" s="100" t="n">
+      <c r="A143" s="107" t="n">
         <v>140</v>
       </c>
-      <c r="B143" s="101" t="inlineStr">
+      <c r="B143" s="108" t="inlineStr">
         <is>
           <t>바라바라</t>
         </is>
       </c>
-      <c r="C143" s="100" t="inlineStr">
+      <c r="C143" s="107" t="inlineStr">
         <is>
           <t>BARABARA</t>
         </is>
       </c>
-      <c r="D143" s="101" t="inlineStr">
+      <c r="D143" s="108" t="inlineStr">
         <is>
           <t>보쿠하이</t>
         </is>
       </c>
-      <c r="E143" s="100" t="inlineStr">
+      <c r="E143" s="107" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
@@ -6575,30 +6591,30 @@
       </c>
     </row>
     <row r="144">
-      <c r="A144" s="100" t="n">
+      <c r="A144" s="107" t="n">
         <v>141</v>
       </c>
-      <c r="B144" s="101" t="inlineStr">
+      <c r="B144" s="108" t="inlineStr">
         <is>
           <t>신디에잇</t>
         </is>
       </c>
-      <c r="C144" s="100" t="inlineStr">
+      <c r="C144" s="107" t="inlineStr">
         <is>
           <t>SYNDI8</t>
         </is>
       </c>
-      <c r="D144" s="101" t="inlineStr">
+      <c r="D144" s="108" t="inlineStr">
         <is>
           <t>수퍼톤(HYBE 자회사)</t>
         </is>
       </c>
-      <c r="E144" s="100" t="inlineStr">
+      <c r="E144" s="107" t="inlineStr">
         <is>
           <t>2024</t>
         </is>
       </c>
-      <c r="F144" s="102" t="inlineStr">
+      <c r="F144" s="109" t="inlineStr">
         <is>
           <t>음반/아이돌형</t>
         </is>
@@ -6615,25 +6631,25 @@
       </c>
     </row>
     <row r="145">
-      <c r="A145" s="100" t="n">
+      <c r="A145" s="107" t="n">
         <v>142</v>
       </c>
-      <c r="B145" s="101" t="inlineStr">
+      <c r="B145" s="108" t="inlineStr">
         <is>
           <t>피버스</t>
         </is>
       </c>
-      <c r="C145" s="100" t="inlineStr">
+      <c r="C145" s="107" t="inlineStr">
         <is>
           <t>Feverse</t>
         </is>
       </c>
-      <c r="D145" s="101" t="inlineStr">
+      <c r="D145" s="108" t="inlineStr">
         <is>
           <t>카카오엔터테인먼트</t>
         </is>
       </c>
-      <c r="E145" s="100" t="inlineStr">
+      <c r="E145" s="107" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
@@ -6655,30 +6671,30 @@
       </c>
     </row>
     <row r="146">
-      <c r="A146" s="100" t="n">
+      <c r="A146" s="107" t="n">
         <v>143</v>
       </c>
-      <c r="B146" s="101" t="inlineStr">
+      <c r="B146" s="108" t="inlineStr">
         <is>
           <t>이진법소년들</t>
         </is>
       </c>
-      <c r="C146" s="100" t="inlineStr">
+      <c r="C146" s="107" t="inlineStr">
         <is>
           <t>ØXONE</t>
         </is>
       </c>
-      <c r="D146" s="101" t="inlineStr">
+      <c r="D146" s="108" t="inlineStr">
         <is>
           <t>완구 기업(유통 워너뮤직 ADA)</t>
         </is>
       </c>
-      <c r="E146" s="100" t="inlineStr">
+      <c r="E146" s="107" t="inlineStr">
         <is>
           <t>2023</t>
         </is>
       </c>
-      <c r="F146" s="102" t="inlineStr">
+      <c r="F146" s="109" t="inlineStr">
         <is>
           <t>음반/아이돌형</t>
         </is>
@@ -6695,30 +6711,30 @@
       </c>
     </row>
     <row r="147">
-      <c r="A147" s="100" t="n">
+      <c r="A147" s="107" t="n">
         <v>144</v>
       </c>
-      <c r="B147" s="101" t="inlineStr">
+      <c r="B147" s="108" t="inlineStr">
         <is>
           <t>홀린</t>
         </is>
       </c>
-      <c r="C147" s="100" t="inlineStr">
+      <c r="C147" s="107" t="inlineStr">
         <is>
           <t>WhOLLiN</t>
         </is>
       </c>
-      <c r="D147" s="101" t="inlineStr">
+      <c r="D147" s="108" t="inlineStr">
         <is>
           <t>플레이리스트(PLAYLIST)</t>
         </is>
       </c>
-      <c r="E147" s="100" t="inlineStr">
+      <c r="E147" s="107" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F147" s="102" t="inlineStr">
+      <c r="F147" s="109" t="inlineStr">
         <is>
           <t>음반/아이돌형</t>
         </is>
@@ -6735,65 +6751,65 @@
       </c>
     </row>
     <row r="148">
-      <c r="A148" s="100" t="n">
+      <c r="A148" s="107" t="n">
         <v>145</v>
       </c>
-      <c r="B148" s="101" t="inlineStr">
+      <c r="B148" s="108" t="inlineStr">
         <is>
           <t>비그릿츠</t>
         </is>
       </c>
-      <c r="C148" s="100" t="inlineStr">
+      <c r="C148" s="107" t="inlineStr">
         <is>
           <t>BEGRITZ</t>
         </is>
       </c>
-      <c r="D148" s="101" t="inlineStr">
+      <c r="D148" s="108" t="inlineStr">
         <is>
           <t>디네이블(DNABLE)</t>
         </is>
       </c>
-      <c r="E148" s="100" t="inlineStr">
+      <c r="E148" s="107" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F148" s="102" t="inlineStr">
+      <c r="F148" s="109" t="inlineStr">
         <is>
           <t>음반/아이돌형</t>
         </is>
       </c>
-      <c r="G148" s="103" t="inlineStr">
+      <c r="G148" s="110" t="inlineStr">
         <is>
           <t>데뷔전</t>
         </is>
       </c>
       <c r="H148" s="66" t="inlineStr">
         <is>
-          <t>[데뷔 예정 · 2026.8(론칭 예정)] 5인조. '시공간을 모험하는 도깨비' 세계관. 프로듀서 알티(R.Tee) 음악 총괄, 블락비 태일 A&amp;R·보컬디렉터. 실시간 CG·AI·퍼포먼스캡처 결합.</t>
+          <t>[데뷔 예정 · 2026.8(론칭 예정)] 5인조. '시공간을 모험하는 도깨비' 세계관. 프로듀서 알티(R.Tee) 음악 총괄, 블락비 태일 A&amp;R·보컬디렉터. 실시간 CG·AI·퍼포먼스캡처 결합. 2026.10.3~4 자카르타 ICC 2026에서 첫 퍼포먼스 공개(노컷 2026.10.1). 정식 데뷔 일정 미확인.</t>
         </is>
       </c>
     </row>
     <row r="149">
-      <c r="A149" s="100" t="n">
+      <c r="A149" s="107" t="n">
         <v>146</v>
       </c>
-      <c r="B149" s="101" t="inlineStr">
+      <c r="B149" s="108" t="inlineStr">
         <is>
           <t>걸스 아카이브</t>
         </is>
       </c>
-      <c r="C149" s="100" t="inlineStr">
+      <c r="C149" s="107" t="inlineStr">
         <is>
           <t>Girls Archives.</t>
         </is>
       </c>
-      <c r="D149" s="101" t="inlineStr">
+      <c r="D149" s="108" t="inlineStr">
         <is>
           <t>하이브 NEB × INCS toenter(일본)</t>
         </is>
       </c>
-      <c r="E149" s="100" t="inlineStr">
+      <c r="E149" s="107" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
@@ -6803,7 +6819,7 @@
           <t>혼합형</t>
         </is>
       </c>
-      <c r="G149" s="103" t="inlineStr">
+      <c r="G149" s="110" t="inlineStr">
         <is>
           <t>데뷔전</t>
         </is>
@@ -6815,115 +6831,115 @@
       </c>
     </row>
     <row r="150">
-      <c r="A150" s="100" t="n">
+      <c r="A150" s="107" t="n">
         <v>147</v>
       </c>
-      <c r="B150" s="101" t="inlineStr">
+      <c r="B150" s="108" t="inlineStr">
         <is>
           <t>코스믹코드</t>
         </is>
       </c>
-      <c r="C150" s="100" t="inlineStr">
+      <c r="C150" s="107" t="inlineStr">
         <is>
           <t>COSMIC CODE</t>
         </is>
       </c>
-      <c r="D150" s="101" t="inlineStr">
+      <c r="D150" s="108" t="inlineStr">
         <is>
           <t>에이탑유니버스</t>
         </is>
       </c>
-      <c r="E150" s="100" t="inlineStr">
+      <c r="E150" s="107" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F150" s="102" t="inlineStr">
+      <c r="F150" s="109" t="inlineStr">
         <is>
           <t>음반/아이돌형</t>
         </is>
       </c>
-      <c r="G150" s="103" t="inlineStr">
+      <c r="G150" s="110" t="inlineStr">
         <is>
           <t>데뷔전</t>
         </is>
       </c>
       <c r="H150" s="66" t="inlineStr">
         <is>
-          <t>[프리데뷔(멤버 순차 공개) · 2026.9.9~] 일본 우타이테 시장 겨냥 2.5D 버추얼 아이돌 5인. 프리데뷔 싱글 'POKER FACE', 2026.11 도쿄·오사카 공연 추진. 日 YOANI 3억엔 투자. (한국일보 2026.9.9)</t>
+          <t>[프리데뷔(멤버 순차 공개) · 2026.9.9~] 일본 우타이테 시장 겨냥 2.5D 버추얼 아이돌 5인. 프리데뷔 싱글 'POKER FACE', 2026.11 도쿄·오사카 공연 추진. 日 YOANI 3억엔 투자. (한국일보 2026.9.9) 10.21 팀 앨범 예정, 11.13~14 도쿄·오사카 재팬 프리데뷔 콘서트. 日 YOANI 3억엔 투자(톱셀럽 2026.9.10).</t>
         </is>
       </c>
     </row>
     <row r="151">
-      <c r="A151" s="100" t="n">
+      <c r="A151" s="107" t="n">
         <v>148</v>
       </c>
-      <c r="B151" s="101" t="inlineStr">
+      <c r="B151" s="108" t="inlineStr">
         <is>
           <t>STUN-X</t>
         </is>
       </c>
-      <c r="C151" s="100" t="inlineStr">
+      <c r="C151" s="107" t="inlineStr">
         <is>
           <t>우주아이돌리그</t>
         </is>
       </c>
-      <c r="D151" s="101" t="inlineStr">
+      <c r="D151" s="108" t="inlineStr">
         <is>
           <t>밀리언볼트(애니 스튜디오)</t>
         </is>
       </c>
-      <c r="E151" s="100" t="inlineStr">
+      <c r="E151" s="107" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F151" s="102" t="inlineStr">
+      <c r="F151" s="109" t="inlineStr">
         <is>
           <t>음반/아이돌형</t>
         </is>
       </c>
-      <c r="G151" s="103" t="inlineStr">
+      <c r="G151" s="110" t="inlineStr">
         <is>
           <t>데뷔전</t>
         </is>
       </c>
       <c r="H151" s="66" t="inlineStr">
         <is>
-          <t>[데뷔 예정 · 2026.10.2] 2D 버추얼 아이돌 IP. 웹소설 2026.9.10 카카오페이지 연재, 10.2 첫 디지털 싱글 예정. 캐릭터 콘텐츠 누적 2,000만뷰. (MBN 2026.9.11)</t>
+          <t>[데뷔 예정 · 2026.10.2] 2D 버추얼 아이돌 IP. 웹소설 2026.9.10 카카오페이지 연재, 10.2 첫 디지털 싱글 예정. 캐릭터 콘텐츠 누적 2,000만뷰. (MBN 2026.9.11) 10.2 싱글 발매 기사 미확인(2026-10-06 기준).</t>
         </is>
       </c>
     </row>
     <row r="152">
-      <c r="A152" s="100" t="n">
+      <c r="A152" s="107" t="n">
         <v>149</v>
       </c>
-      <c r="B152" s="101" t="inlineStr">
+      <c r="B152" s="108" t="inlineStr">
         <is>
           <t>WINKX</t>
         </is>
       </c>
-      <c r="C152" s="100" t="inlineStr">
+      <c r="C152" s="107" t="inlineStr">
         <is>
           <t>윙스</t>
         </is>
       </c>
-      <c r="D152" s="101" t="inlineStr">
+      <c r="D152" s="108" t="inlineStr">
         <is>
           <t>타이탄콘텐츠 × 대원미디어</t>
         </is>
       </c>
-      <c r="E152" s="100" t="inlineStr">
+      <c r="E152" s="107" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F152" s="102" t="inlineStr">
+      <c r="F152" s="109" t="inlineStr">
         <is>
           <t>음반/아이돌형</t>
         </is>
       </c>
-      <c r="G152" s="103" t="inlineStr">
+      <c r="G152" s="110" t="inlineStr">
         <is>
           <t>데뷔전</t>
         </is>
@@ -6935,25 +6951,25 @@
       </c>
     </row>
     <row r="153">
-      <c r="A153" s="100" t="n">
+      <c r="A153" s="107" t="n">
         <v>150</v>
       </c>
-      <c r="B153" s="101" t="inlineStr">
+      <c r="B153" s="108" t="inlineStr">
         <is>
           <t>레드소다써클</t>
         </is>
       </c>
-      <c r="C153" s="100" t="inlineStr">
+      <c r="C153" s="107" t="inlineStr">
         <is>
           <t>Red Soda Circle</t>
         </is>
       </c>
-      <c r="D153" s="101" t="inlineStr">
+      <c r="D153" s="108" t="inlineStr">
         <is>
           <t>코드판타지아</t>
         </is>
       </c>
-      <c r="E153" s="100" t="inlineStr">
+      <c r="E153" s="107" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
@@ -6963,7 +6979,7 @@
           <t>혼합형</t>
         </is>
       </c>
-      <c r="G153" s="103" t="inlineStr">
+      <c r="G153" s="110" t="inlineStr">
         <is>
           <t>데뷔전</t>
         </is>
@@ -6974,7 +6990,7 @@
         </is>
       </c>
     </row>
-    <row r="154">
+    <row r="154" s="41">
       <c r="A154" s="107" t="n">
         <v>151</v>
       </c>
@@ -7010,7 +7026,127 @@
       </c>
       <c r="H154" s="66" t="inlineStr">
         <is>
-          <t>[프리데뷔 · 선공개 3장] 5인조(이언·제이스·퍼비·기류·루안). 'Lowkey'(6.26)·'The Baddest'(7.31)·'JADED'(8.21, 정식 데뷔 전 마지막 선공개). 다크SF 세계관. 유튜브 개설 7주 만에 구독 10만, 쇼츠 500만뷰. 정식 데뷔 시 활동중 전환.</t>
+          <t>[프리데뷔 · 선공개 3장] 5인조(이언·제이스·퍼비·기류·루안). 'Lowkey'(6.26)·'The Baddest'(7.31)·'JADED'(8.21, 정식 데뷔 전 마지막 선공개). 다크SF 세계관. 유튜브 개설 7주 만에 구독 10만, 쇼츠 500만뷰. 정식 데뷔 시 활동중 전환. → 2026.10.20 데뷔 앨범 'THE REAL DEAL' 발매 확정(네이트 2026.10.1). 10.20 이후 활동중 전환.</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" s="41">
+      <c r="A155" s="107" t="n">
+        <v>152</v>
+      </c>
+      <c r="B155" s="108" t="inlineStr">
+        <is>
+          <t>라피드아이</t>
+        </is>
+      </c>
+      <c r="C155" s="107" t="inlineStr">
+        <is>
+          <t>RapidEye</t>
+        </is>
+      </c>
+      <c r="D155" s="108" t="inlineStr">
+        <is>
+          <t>FM STUDIO(에프엠 스튜디오)</t>
+        </is>
+      </c>
+      <c r="E155" s="107" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F155" s="109" t="inlineStr">
+        <is>
+          <t>음반/아이돌형</t>
+        </is>
+      </c>
+      <c r="G155" s="90" t="inlineStr">
+        <is>
+          <t>활동중</t>
+        </is>
+      </c>
+      <c r="H155" s="66" t="inlineStr">
+        <is>
+          <t>여성 4인조. 무의식 세계 '레베리(REVE:RE)' 세계관. 2025.9.27 디지털 싱글 'Energy'로 정식 데뷔(고려대 축제 데뷔 무대). 2025.11 가상융합산업대전 공연, 한국메타버스협회 성과사례. (톱셀럽 2025.9.8·9.15, 머니투데이 2025.11.12·12.8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" s="41">
+      <c r="A156" s="107" t="n">
+        <v>153</v>
+      </c>
+      <c r="B156" s="108" t="inlineStr">
+        <is>
+          <t>트윌릿 스튜디오</t>
+        </is>
+      </c>
+      <c r="C156" s="107" t="inlineStr">
+        <is>
+          <t>TWILLIT STUDIO</t>
+        </is>
+      </c>
+      <c r="D156" s="108" t="inlineStr">
+        <is>
+          <t>SAMG엔터테인먼트(에스에이엠지)</t>
+        </is>
+      </c>
+      <c r="E156" s="107" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F156" s="91" t="inlineStr">
+        <is>
+          <t>스트리밍/MCN형</t>
+        </is>
+      </c>
+      <c r="G156" s="94" t="inlineStr">
+        <is>
+          <t>확인필요</t>
+        </is>
+      </c>
+      <c r="H156" s="66" t="inlineStr">
+        <is>
+          <t>SAMG의 2D 버츄얼 브랜드, 2025.3 런칭. 멤버 카페 카르테·모코 파르페·유우희·댕키·한서린·에루·솔스티스(현시후 2025.12.2 계약종료). 기사 미확인·나무위키 목록에만 있음. (나무위키 버츄얼 그룹 목록 4.5.5, 2026-10-06)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157" s="41">
+      <c r="A157" s="107" t="n">
+        <v>154</v>
+      </c>
+      <c r="B157" s="108" t="inlineStr">
+        <is>
+          <t>수니문</t>
+        </is>
+      </c>
+      <c r="C157" s="107" t="inlineStr">
+        <is>
+          <t>SOONIMOON(구 버니문)</t>
+        </is>
+      </c>
+      <c r="D157" s="108" t="inlineStr">
+        <is>
+          <t>수니그룹</t>
+        </is>
+      </c>
+      <c r="E157" s="107" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F157" s="91" t="inlineStr">
+        <is>
+          <t>스트리밍/MCN형</t>
+        </is>
+      </c>
+      <c r="G157" s="95" t="inlineStr">
+        <is>
+          <t>해체/종료</t>
+        </is>
+      </c>
+      <c r="H157" s="66" t="inlineStr">
+        <is>
+          <t>SOOP 버튜버 크루, 커버 무대 위주. 2025.9.12 결성 → 2026.3.26 해체. 기사 미확인·나무위키에만 있음. (나무위키 「수니문」)</t>
         </is>
       </c>
     </row>
@@ -7032,7 +7168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D63"/>
+  <dimension ref="A1:D66"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="40" min="1" max="1"/>
@@ -8369,6 +8505,72 @@
       <c r="D63" s="86" t="inlineStr">
         <is>
           <t>AI 보이스 기반 버추얼 걸그룹</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="86" t="inlineStr">
+        <is>
+          <t>FM STUDIO(에프엠 스튜디오)</t>
+        </is>
+      </c>
+      <c r="B64" s="86" t="inlineStr">
+        <is>
+          <t>버추얼 아이돌 기획사</t>
+        </is>
+      </c>
+      <c r="C64" s="86" t="inlineStr">
+        <is>
+          <t>라피드아이</t>
+        </is>
+      </c>
+      <c r="D64" s="86" t="inlineStr">
+        <is>
+          <t>2025.9 데뷔. 한국메타버스협회 인력양성 성과사례</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="86" t="inlineStr">
+        <is>
+          <t>SAMG엔터테인먼트</t>
+        </is>
+      </c>
+      <c r="B65" s="86" t="inlineStr">
+        <is>
+          <t>애니메이션사(티니핑)</t>
+        </is>
+      </c>
+      <c r="C65" s="86" t="inlineStr">
+        <is>
+          <t>트윌릿 스튜디오</t>
+        </is>
+      </c>
+      <c r="D65" s="86" t="inlineStr">
+        <is>
+          <t>2025.3 2D 버츄얼 브랜드 런칭</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="86" t="inlineStr">
+        <is>
+          <t>수니그룹</t>
+        </is>
+      </c>
+      <c r="B66" s="86" t="inlineStr">
+        <is>
+          <t>버튜버 크루 운영</t>
+        </is>
+      </c>
+      <c r="C66" s="86" t="inlineStr">
+        <is>
+          <t>수니문(해체)</t>
+        </is>
+      </c>
+      <c r="D66" s="86" t="inlineStr">
+        <is>
+          <t>2026.3.26 해체</t>
         </is>
       </c>
     </row>
@@ -8402,6 +8604,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="41">
       <c r="A3" s="71" t="inlineStr">
         <is>
@@ -8409,7 +8612,7 @@
         </is>
       </c>
       <c r="B3" s="46">
-        <f>COUNTA('버추얼 그룹 전수목록'!B4:B153)</f>
+        <f>COUNTA('버추얼 그룹 전수목록'!B4:B157)</f>
         <v/>
       </c>
     </row>
@@ -8420,7 +8623,7 @@
         </is>
       </c>
       <c r="B4" s="46">
-        <f>COUNTIF('버추얼 그룹 전수목록'!G4:G153,"활동중")</f>
+        <f>COUNTIF('버추얼 그룹 전수목록'!G4:G157,"활동중")</f>
         <v/>
       </c>
     </row>
@@ -8431,7 +8634,7 @@
         </is>
       </c>
       <c r="B5" s="46">
-        <f>COUNTIF('버추얼 그룹 전수목록'!G4:G153,"해체/종료")</f>
+        <f>COUNTIF('버추얼 그룹 전수목록'!G4:G157,"해체/종료")</f>
         <v/>
       </c>
     </row>
@@ -8442,7 +8645,7 @@
         </is>
       </c>
       <c r="B6" s="46">
-        <f>COUNTIF('버추얼 그룹 전수목록'!G4:G153,"전환")</f>
+        <f>COUNTIF('버추얼 그룹 전수목록'!G4:G157,"전환")</f>
         <v/>
       </c>
     </row>
@@ -8453,7 +8656,7 @@
         </is>
       </c>
       <c r="B7" s="46">
-        <f>COUNTIF('버추얼 그룹 전수목록'!G4:G153,"확인필요")</f>
+        <f>COUNTIF('버추얼 그룹 전수목록'!G4:G157,"확인필요")</f>
         <v/>
       </c>
     </row>
@@ -8464,7 +8667,7 @@
         </is>
       </c>
       <c r="B8" s="73">
-        <f>COUNTIF('버추얼 그룹 전수목록'!G4:G153,"휴면")</f>
+        <f>COUNTIF('버추얼 그룹 전수목록'!G4:G157,"휴면")</f>
         <v/>
       </c>
     </row>
@@ -8475,7 +8678,7 @@
         </is>
       </c>
       <c r="B9" s="106">
-        <f>COUNTIF('버추얼 그룹 전수목록'!G4:G153,"데뷔전")</f>
+        <f>COUNTIF('버추얼 그룹 전수목록'!G4:G157,"데뷔전")</f>
         <v/>
       </c>
     </row>
@@ -8494,7 +8697,7 @@
         </is>
       </c>
       <c r="B11" s="46">
-        <f>COUNTIF('버추얼 그룹 전수목록'!F4:F153,"음반/아이돌형")</f>
+        <f>COUNTIF('버추얼 그룹 전수목록'!F4:F157,"음반/아이돌형")</f>
         <v/>
       </c>
     </row>
@@ -8505,7 +8708,7 @@
         </is>
       </c>
       <c r="B12" s="46">
-        <f>COUNTIF('버추얼 그룹 전수목록'!F4:F153,"버추얼휴먼/솔로")</f>
+        <f>COUNTIF('버추얼 그룹 전수목록'!F4:F157,"버추얼휴먼/솔로")</f>
         <v/>
       </c>
     </row>
@@ -8516,7 +8719,7 @@
         </is>
       </c>
       <c r="B13" s="46">
-        <f>COUNTIF('버추얼 그룹 전수목록'!F4:F153,"스트리밍/MCN형")</f>
+        <f>COUNTIF('버추얼 그룹 전수목록'!F4:F157,"스트리밍/MCN형")</f>
         <v/>
       </c>
     </row>
@@ -8527,7 +8730,7 @@
         </is>
       </c>
       <c r="B14" s="46">
-        <f>COUNTIF('버추얼 그룹 전수목록'!F4:F153,"혼합형")</f>
+        <f>COUNTIF('버추얼 그룹 전수목록'!F4:F157,"혼합형")</f>
         <v/>
       </c>
     </row>
@@ -8604,7 +8807,7 @@
       </c>
       <c r="C3" s="48" t="inlineStr">
         <is>
-          <t>프리데뷔→정식 예정</t>
+          <t>정식 데뷔 10월 확정</t>
         </is>
       </c>
       <c r="D3" s="47" t="inlineStr">
@@ -8614,7 +8817,7 @@
       </c>
       <c r="E3" s="54" t="inlineStr">
         <is>
-          <t>멀티페르소나 6인 보이그룹. 5월 첫 라이브, 정식데뷔 준비 중</t>
+          <t>멀티페르소나 6인 보이그룹. 5월 첫 라이브, 정식데뷔 준비 중 2026.9.22 프롤로그 싱글 '괴물', 10월 정식 데뷔 확정·첫 일본인 멤버 쿠우타 공개(톱셀럽 2026.9.24).</t>
         </is>
       </c>
     </row>
@@ -8862,49 +9065,49 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="101" t="inlineStr">
+      <c r="A13" s="108" t="inlineStr">
         <is>
           <t>비더후드 (B THE HOOD)</t>
         </is>
       </c>
-      <c r="B13" s="100" t="inlineStr">
+      <c r="B13" s="107" t="inlineStr">
         <is>
           <t>레벨스(LEVVELS·하이브×두나무 합작)</t>
         </is>
       </c>
-      <c r="C13" s="101" t="inlineStr">
-        <is>
-          <t>프리데뷔 완료(선공개 3장) · 정식 데뷔 임박</t>
-        </is>
-      </c>
-      <c r="D13" s="100" t="inlineStr">
+      <c r="C13" s="108" t="inlineStr">
+        <is>
+          <t>정식 데뷔 확정(2026.10.20)</t>
+        </is>
+      </c>
+      <c r="D13" s="107" t="inlineStr">
         <is>
           <t>선공개 2026.6.26/7.31/8.21 · 정식 데뷔일 미확인</t>
         </is>
       </c>
       <c r="E13" s="66" t="inlineStr">
         <is>
-          <t>5인조(이언·제이스·퍼비·기류·루안). 선공개 싱글 3장 — 'Lowkey'(6.26), 'The Baddest'(7.31), 'JADED'(8.21, 기사상 '정식 데뷔 전 마지막 선공개'). 행성 노버스를 떠난 외계인 다크SF 세계관. 유튜브 개설 7주 만에 구독 10만, 쇼츠 누적 500만뷰. 정식 데뷔 시 전수목록 편입 예정. (스포츠경향 2026.8.13, 텐아시아 2026.7.29)</t>
+          <t>5인조(이언·제이스·퍼비·기류·루안). 선공개 싱글 3장 — 'Lowkey'(6.26), 'The Baddest'(7.31), 'JADED'(8.21, 기사상 '정식 데뷔 전 마지막 선공개'). 행성 노버스를 떠난 외계인 다크SF 세계관. 유튜브 개설 7주 만에 구독 10만, 쇼츠 누적 500만뷰. 정식 데뷔 시 전수목록 편입 예정. (스포츠경향 2026.8.13, 텐아시아 2026.7.29) 데뷔 앨범 'THE REAL DEAL' 10.20 발매 확정(네이트 2026.10.1).</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="101" t="inlineStr">
+      <c r="A14" s="108" t="inlineStr">
         <is>
           <t>비그릿츠 (BEGRITZ)</t>
         </is>
       </c>
-      <c r="B14" s="100" t="inlineStr">
+      <c r="B14" s="107" t="inlineStr">
         <is>
           <t>디네이블(DNABLE)</t>
         </is>
       </c>
-      <c r="C14" s="101" t="inlineStr">
+      <c r="C14" s="108" t="inlineStr">
         <is>
           <t>데뷔 예정</t>
         </is>
       </c>
-      <c r="D14" s="100" t="inlineStr">
+      <c r="D14" s="107" t="inlineStr">
         <is>
           <t>2026.8(론칭 예정)</t>
         </is>
@@ -8916,22 +9119,22 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="101" t="inlineStr">
+      <c r="A15" s="108" t="inlineStr">
         <is>
           <t>홀린 (WhOLLiN)</t>
         </is>
       </c>
-      <c r="B15" s="100" t="inlineStr">
+      <c r="B15" s="107" t="inlineStr">
         <is>
           <t>플레이리스트(PLAYLIST)</t>
         </is>
       </c>
-      <c r="C15" s="101" t="inlineStr">
+      <c r="C15" s="108" t="inlineStr">
         <is>
           <t>정식 데뷔 완료(2026.9.1) → 전수목록 편입</t>
         </is>
       </c>
-      <c r="D15" s="100" t="inlineStr">
+      <c r="D15" s="107" t="inlineStr">
         <is>
           <t>2026.9.1</t>
         </is>
@@ -8943,22 +9146,22 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="101" t="inlineStr">
+      <c r="A16" s="108" t="inlineStr">
         <is>
           <t>걸스 아카이브 (Girls Archives.)</t>
         </is>
       </c>
-      <c r="B16" s="100" t="inlineStr">
+      <c r="B16" s="107" t="inlineStr">
         <is>
           <t>하이브 NEB × INCS toenter(일본)</t>
         </is>
       </c>
-      <c r="C16" s="101" t="inlineStr">
+      <c r="C16" s="108" t="inlineStr">
         <is>
           <t>프리데뷔 예정</t>
         </is>
       </c>
-      <c r="D16" s="100" t="inlineStr">
+      <c r="D16" s="107" t="inlineStr">
         <is>
           <t>2026.8.7 프리데뷔</t>
         </is>
@@ -8970,22 +9173,22 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="101" t="inlineStr">
+      <c r="A17" s="108" t="inlineStr">
         <is>
           <t>코스믹코드 (COSMIC CODE)</t>
         </is>
       </c>
-      <c r="B17" s="100" t="inlineStr">
+      <c r="B17" s="107" t="inlineStr">
         <is>
           <t>에이탑유니버스</t>
         </is>
       </c>
-      <c r="C17" s="101" t="inlineStr">
+      <c r="C17" s="108" t="inlineStr">
         <is>
           <t>프리데뷔(멤버 순차 공개)</t>
         </is>
       </c>
-      <c r="D17" s="100" t="inlineStr">
+      <c r="D17" s="107" t="inlineStr">
         <is>
           <t>2026.9.9~</t>
         </is>
@@ -8997,22 +9200,22 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="101" t="inlineStr">
+      <c r="A18" s="108" t="inlineStr">
         <is>
           <t>STUN-X (우주아이돌리그)</t>
         </is>
       </c>
-      <c r="B18" s="100" t="inlineStr">
+      <c r="B18" s="107" t="inlineStr">
         <is>
           <t>밀리언볼트(애니 스튜디오)</t>
         </is>
       </c>
-      <c r="C18" s="101" t="inlineStr">
+      <c r="C18" s="108" t="inlineStr">
         <is>
           <t>데뷔 예정</t>
         </is>
       </c>
-      <c r="D18" s="100" t="inlineStr">
+      <c r="D18" s="107" t="inlineStr">
         <is>
           <t>2026.10.2</t>
         </is>
@@ -9024,22 +9227,22 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="101" t="inlineStr">
+      <c r="A19" s="108" t="inlineStr">
         <is>
           <t>WINKX (윙스)</t>
         </is>
       </c>
-      <c r="B19" s="100" t="inlineStr">
+      <c r="B19" s="107" t="inlineStr">
         <is>
           <t>타이탄콘텐츠 × 대원미디어</t>
         </is>
       </c>
-      <c r="C19" s="101" t="inlineStr">
+      <c r="C19" s="108" t="inlineStr">
         <is>
           <t>데뷔 예정(MOU 단계)</t>
         </is>
       </c>
-      <c r="D19" s="100" t="inlineStr">
+      <c r="D19" s="107" t="inlineStr">
         <is>
           <t>미확인</t>
         </is>
@@ -9051,22 +9254,22 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="101" t="inlineStr">
+      <c r="A20" s="108" t="inlineStr">
         <is>
           <t>레드소다써클 (Red Soda Circle)</t>
         </is>
       </c>
-      <c r="B20" s="100" t="inlineStr">
+      <c r="B20" s="107" t="inlineStr">
         <is>
           <t>코드판타지아</t>
         </is>
       </c>
-      <c r="C20" s="101" t="inlineStr">
+      <c r="C20" s="108" t="inlineStr">
         <is>
           <t>프리데뷔</t>
         </is>
       </c>
-      <c r="D20" s="100" t="inlineStr">
+      <c r="D20" s="107" t="inlineStr">
         <is>
           <t>2025.12.22</t>
         </is>
@@ -12215,7 +12418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I9"/>
+  <dimension ref="A1:I11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="41" min="1" max="1"/>
@@ -12525,6 +12728,100 @@
         </is>
       </c>
     </row>
+    <row r="10">
+      <c r="A10" s="99" t="inlineStr">
+        <is>
+          <t>뉴라</t>
+        </is>
+      </c>
+      <c r="B10" s="99" t="inlineStr">
+        <is>
+          <t>NEURA</t>
+        </is>
+      </c>
+      <c r="C10" s="99" t="inlineStr">
+        <is>
+          <t>프롬레코드(PROM RECORD)</t>
+        </is>
+      </c>
+      <c r="D10" s="99" t="inlineStr">
+        <is>
+          <t>생성형 AI 버추얼 아이돌 IP(12 별자리)</t>
+        </is>
+      </c>
+      <c r="E10" s="99" t="inlineStr">
+        <is>
+          <t>첫 공개(전시)</t>
+        </is>
+      </c>
+      <c r="F10" s="99" t="inlineStr">
+        <is>
+          <t>2026.3.23</t>
+        </is>
+      </c>
+      <c r="G10" s="99" t="inlineStr">
+        <is>
+          <t>전시 '별에서 온 첫 만남, NEURA'(판교, 경기콘텐츠진흥원) MV형 콘텐츠</t>
+        </is>
+      </c>
+      <c r="H10" s="99" t="inlineStr">
+        <is>
+          <t>음원 발매 미확인. A2O MAY AI MV 제작사 자체 IP.</t>
+        </is>
+      </c>
+      <c r="I10" s="99" t="inlineStr">
+        <is>
+          <t>KMJ 2026.3.23</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="99" t="inlineStr">
+        <is>
+          <t>밤하늘극장</t>
+        </is>
+      </c>
+      <c r="B11" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C11" s="99" t="inlineStr">
+        <is>
+          <t>창작자 프로젝트(소속사 미기재)</t>
+        </is>
+      </c>
+      <c r="D11" s="99" t="inlineStr">
+        <is>
+          <t>AI 혼합 버추얼 인디밴드</t>
+        </is>
+      </c>
+      <c r="E11" s="99" t="inlineStr">
+        <is>
+          <t>활동</t>
+        </is>
+      </c>
+      <c r="F11" s="99" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="G11" s="99" t="inlineStr">
+        <is>
+          <t>앨범 '이 파도가 멈추지 않았으면 해'(8.4), 싱글 '완전한 무조건적 사랑의 형태'(9.6)</t>
+        </is>
+      </c>
+      <c r="H11" s="99" t="inlineStr">
+        <is>
+          <t>기획·작사·프로듀싱은 사람, 제작에 생성형 AI 사용 공개. 가창 AI 여부 미확인 → 경계 사례.</t>
+        </is>
+      </c>
+      <c r="I11" s="99" t="inlineStr">
+        <is>
+          <t>톱셀럽 2026.8.26</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/한국_버추얼아이돌_전수조사_v8.xlsx
+++ b/data/한국_버추얼아이돌_전수조사_v8.xlsx
@@ -1,19 +1,19 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="버추얼 그룹 전수목록" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="소속사·운영사 정리" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="요약 통계" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="데뷔예정·신규(2026)" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개인세(무소속) 기준안+시드" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개인세 수집PoC(3만+)" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="AI 생성형 아티스트" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="버추얼 그룹 전수목록" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="소속사·운영사 정리" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="요약 통계" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="데뷔예정·신규(2026)" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="개인세(무소속) 기준안+시드" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="개인세 수집PoC(3만+)" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="AI 생성형 아티스트" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'버추얼 그룹 전수목록'!$A$3:$H$126</definedName>
@@ -3134,7 +3134,7 @@
       </c>
       <c r="H55" s="51" t="inlineStr">
         <is>
-          <t>2024.1 데뷔. 2024.2 치지직 이적 2026.9.22 멤버 망내 전속계약 위반으로 퇴출(톱셀럽 2026.9.29).</t>
+          <t>2024.1 데뷔(프로젝트아이), 2024.2 치지직 이적. 2026.9.22 멤버 망내 전속계약 위반(정보 누설·무단 이적 협의 등)으로 퇴출 → 허니츄러스·아야·담유이·디디디용·오화요 5인 체제. (톱셀럽 2026.9.29)</t>
         </is>
       </c>
     </row>
@@ -7026,7 +7026,7 @@
       </c>
       <c r="H154" s="66" t="inlineStr">
         <is>
-          <t>[프리데뷔 · 선공개 3장] 5인조(이언·제이스·퍼비·기류·루안). 'Lowkey'(6.26)·'The Baddest'(7.31)·'JADED'(8.21, 정식 데뷔 전 마지막 선공개). 다크SF 세계관. 유튜브 개설 7주 만에 구독 10만, 쇼츠 500만뷰. 정식 데뷔 시 활동중 전환. → 2026.10.20 데뷔 앨범 'THE REAL DEAL' 발매 확정(네이트 2026.10.1). 10.20 이후 활동중 전환.</t>
+          <t>[데뷔 확정 · 2026.10.20] 5인조(이언·제이스·퍼비·기류·루안), 레벨스. 선공개 'Lowkey'(6.26)·'The Baddest'(7.31)·'JADED'(8.21, 쇼츠 일간 1위). 다크SF 세계관. 유튜브 개설 7주 만에 구독 10만. 9.30 데뷔 포스터, 10.2 첫 공식 라이브. 데뷔 앨범 'THE REAL DEAL' 10.20 전세계 동시 발매 → 발매 후 활동중 전환. (아시아뉴스통신 2026.10.1)</t>
         </is>
       </c>
     </row>
@@ -8604,7 +8604,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="41">
       <c r="A3" s="71" t="inlineStr">
         <is>
@@ -9077,12 +9076,12 @@
       </c>
       <c r="C13" s="108" t="inlineStr">
         <is>
-          <t>정식 데뷔 확정(2026.10.20)</t>
+          <t>정식 데뷔 확정</t>
         </is>
       </c>
       <c r="D13" s="107" t="inlineStr">
         <is>
-          <t>선공개 2026.6.26/7.31/8.21 · 정식 데뷔일 미확인</t>
+          <t>2026.10.20 (선공개 6.26/7.31/8.21)</t>
         </is>
       </c>
       <c r="E13" s="66" t="inlineStr">

--- a/data/한국_버추얼아이돌_전수조사_v8.xlsx
+++ b/data/한국_버추얼아이돌_전수조사_v8.xlsx
@@ -365,7 +365,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="111">
+  <cellXfs count="112">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -686,6 +686,9 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1335,14 +1338,14 @@
           <t>음반/아이돌형</t>
         </is>
       </c>
-      <c r="G9" s="50" t="inlineStr">
-        <is>
-          <t>활동중</t>
+      <c r="G9" s="111" t="inlineStr">
+        <is>
+          <t>데뷔전</t>
         </is>
       </c>
       <c r="H9" s="51" t="inlineStr">
         <is>
-          <t>6인조 보이그룹. 멀티페르소나·동물캐릭터 사족보행 모캡. 시리즈A 40억 투자</t>
+          <t>[정식 데뷔 예정 · 2026.10] 23세기아이들 5인조(시우·우연·태강·제로·쿠우타, 첫 일본인 멤버 쿠우타). 멀티페르소나 세계관(전 멤버가 모든 유닛 참여). 2026.5.3 유튜브 라이브 데뷔 신고식, 9.22 프롤로그 싱글 '괴물' 공개, 9.27 첫 유튜브 라이브. 시리즈A 40억 투자. 10월 정식 데뷔 시 활동중 전환. (스포츠경향 2026.9.24/27)</t>
         </is>
       </c>
     </row>
@@ -6786,7 +6789,7 @@
       </c>
       <c r="H148" s="66" t="inlineStr">
         <is>
-          <t>[데뷔 예정 · 2026.8(론칭 예정)] 5인조. '시공간을 모험하는 도깨비' 세계관. 프로듀서 알티(R.Tee) 음악 총괄, 블락비 태일 A&amp;R·보컬디렉터. 실시간 CG·AI·퍼포먼스캡처 결합. 2026.10.3~4 자카르타 ICC 2026에서 첫 퍼포먼스 공개(노컷 2026.10.1). 정식 데뷔 일정 미확인.</t>
+          <t>[데뷔전 · 정식 데뷔일 미확인] 디네이블 5인조(문찬·도하·태범·루빈·신의). '시공간을 모험하는 도깨비' 세계관. 알티(R.Tee) 음악 총괄·블락비 태일 A&amp;R. 2026.8 론칭(공식 웹 '달빛상회'), 10.3~4 자카르타 ICC 2026에서 데뷔 전 첫 퍼포먼스 공개. (노컷 2026.10.1, 톱셀럽 2026.10.1)</t>
         </is>
       </c>
     </row>
@@ -6826,7 +6829,7 @@
       </c>
       <c r="H149" s="66" t="inlineStr">
         <is>
-          <t>[프리데뷔 예정 · 2026.8.7 프리데뷔] ※실사 멤버+버추얼 캐릭터 연동 하이브리드(2.5D) — 완전 버추얼 아님, 경계 사례. 5인(유이사·에나·서연·히나리·소정). 싱글 'Reborn'=넷플릭스 '리본 히어로' 주제곡. 숀·허니웍스 프로듀싱, 캐릭터 디자인 LAM.</t>
+          <t>[프리데뷔 완료 · 2026.8.7 'Reborn' · 정식 데뷔일 미확인] ※실사 멤버+버추얼 캐릭터 연동 하이브리드(2.5D) — 완전 버추얼 아님, 경계 사례. 5인(유이사·에나·서연·히나리·소정). 싱글 'Reborn'=넷플릭스 '리본 히어로' 주제곡. 숀·허니웍스 프로듀싱, 캐릭터 디자인 LAM.</t>
         </is>
       </c>
     </row>
@@ -6906,7 +6909,7 @@
       </c>
       <c r="H151" s="66" t="inlineStr">
         <is>
-          <t>[데뷔 예정 · 2026.10.2] 2D 버추얼 아이돌 IP. 웹소설 2026.9.10 카카오페이지 연재, 10.2 첫 디지털 싱글 예정. 캐릭터 콘텐츠 누적 2,000만뷰. (MBN 2026.9.11) 10.2 싱글 발매 기사 미확인(2026-10-06 기준).</t>
+          <t>[데뷔 예정 · 2026.10.2 첫 싱글 예고 — 발매 기사 미확인(10.7 기준)] 밀리언볼트 2D 버추얼 아이돌 IP '우주아이돌리그'(152개 행성 서바이벌 설정). 웹소설 2026.9.10 카카오페이지 연재. 캐릭터 콘텐츠 누적 2,000만뷰. 발매 확인 시 상태 재판정. (톱셀럽 2026.9.12)</t>
         </is>
       </c>
     </row>
@@ -8762,7 +8765,7 @@
     <row r="1" ht="25.5" customHeight="1" s="41">
       <c r="A1" s="74" t="inlineStr">
         <is>
-          <t>2026 신규 데뷔 · 데뷔 예정 워치리스트 (2026-09-12 3갈래 조사 반영)</t>
+          <t>2026 신규 데뷔 · 데뷔 예정 워치리스트 (2026-10-07 전수 점검)</t>
         </is>
       </c>
     </row>
@@ -8806,12 +8809,12 @@
       </c>
       <c r="C3" s="48" t="inlineStr">
         <is>
-          <t>정식 데뷔 10월 확정</t>
+          <t>정식 데뷔 예정(10월)</t>
         </is>
       </c>
       <c r="D3" s="47" t="inlineStr">
         <is>
-          <t>2026 여름(목표)</t>
+          <t>2026.10 (프롤로그 '괴물' 9.22)</t>
         </is>
       </c>
       <c r="E3" s="54" t="inlineStr">
@@ -9103,12 +9106,12 @@
       </c>
       <c r="C14" s="108" t="inlineStr">
         <is>
-          <t>데뷔 예정</t>
+          <t>론칭 완료·정식 데뷔 전</t>
         </is>
       </c>
       <c r="D14" s="107" t="inlineStr">
         <is>
-          <t>2026.8(론칭 예정)</t>
+          <t>2026.8 론칭 · 정식 데뷔일 미확인</t>
         </is>
       </c>
       <c r="E14" s="66" t="inlineStr">
@@ -9157,12 +9160,12 @@
       </c>
       <c r="C16" s="108" t="inlineStr">
         <is>
-          <t>프리데뷔 예정</t>
+          <t>프리데뷔 완료</t>
         </is>
       </c>
       <c r="D16" s="107" t="inlineStr">
         <is>
-          <t>2026.8.7 프리데뷔</t>
+          <t>2026.8.7 'Reborn' · 정식 데뷔일 미확인</t>
         </is>
       </c>
       <c r="E16" s="66" t="inlineStr">
@@ -9211,12 +9214,12 @@
       </c>
       <c r="C18" s="108" t="inlineStr">
         <is>
-          <t>데뷔 예정</t>
+          <t>데뷔 예정(발매 확인 필요)</t>
         </is>
       </c>
       <c r="D18" s="107" t="inlineStr">
         <is>
-          <t>2026.10.2</t>
+          <t>2026.10.2 예고</t>
         </is>
       </c>
       <c r="E18" s="66" t="inlineStr">

--- a/data/한국_버추얼아이돌_전수조사_v8.xlsx
+++ b/data/한국_버추얼아이돌_전수조사_v8.xlsx
@@ -365,7 +365,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="112">
+  <cellXfs count="116">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -689,6 +689,18 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="6">
@@ -1040,7 +1052,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H157"/>
+  <dimension ref="A1:H158"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="40" min="1" max="1"/>
@@ -1345,7 +1357,7 @@
       </c>
       <c r="H9" s="51" t="inlineStr">
         <is>
-          <t>[정식 데뷔 예정 · 2026.10] 23세기아이들 5인조(시우·우연·태강·제로·쿠우타, 첫 일본인 멤버 쿠우타). 멀티페르소나 세계관(전 멤버가 모든 유닛 참여). 2026.5.3 유튜브 라이브 데뷔 신고식, 9.22 프롤로그 싱글 '괴물' 공개, 9.27 첫 유튜브 라이브. 시리즈A 40억 투자. 10월 정식 데뷔 시 활동중 전환. (스포츠경향 2026.9.24/27)</t>
+          <t>[정식 데뷔 예정 · 2026.10] 23세기아이들 5인조(시우·우연·태강·제로·쿠우타, 첫 일본인 멤버 쿠우타; 전 멤버 해일). 멀티페르소나 세계관(전 멤버가 모든 유닛 참여). 2026.5.3 유튜브 라이브 데뷔 신고식, 9.22 프롤로그 싱글 '괴물' 공개, 9.27 첫 유튜브 라이브. 시리즈A 40억 투자. 10월 정식 데뷔 시 활동중 전환. (스포츠경향 2026.9.24/27)</t>
         </is>
       </c>
     </row>
@@ -7150,6 +7162,46 @@
       <c r="H157" s="66" t="inlineStr">
         <is>
           <t>SOOP 버튜버 크루, 커버 무대 위주. 2025.9.12 결성 → 2026.3.26 해체. 기사 미확인·나무위키에만 있음. (나무위키 「수니문」)</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" s="112" t="n">
+        <v>155</v>
+      </c>
+      <c r="B158" s="113" t="inlineStr">
+        <is>
+          <t>하이프버스</t>
+        </is>
+      </c>
+      <c r="C158" s="112" t="inlineStr">
+        <is>
+          <t>HYPEVERSE</t>
+        </is>
+      </c>
+      <c r="D158" s="113" t="inlineStr">
+        <is>
+          <t>필랜다트스튜디오</t>
+        </is>
+      </c>
+      <c r="E158" s="112" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F158" s="114" t="inlineStr">
+        <is>
+          <t>음반/아이돌형</t>
+        </is>
+      </c>
+      <c r="G158" s="115" t="inlineStr">
+        <is>
+          <t>데뷔전</t>
+        </is>
+      </c>
+      <c r="H158" s="66" t="inlineStr">
+        <is>
+          <t>[프리데뷔 · 2026.10.7 'Weirdo'] 5인조 K-POP 버추얼 아이돌(멤버 MAKO 등). 기획 단계부터 미국 핵심 시장, 영어 중심 음악·콘텐츠(멤버 전원 네이티브급 영어). 도깨비·구미호 동양 판타지 × 미국 대중문화·스트리트 패션. 유니버설뮤직 코리아 유통. 자체 모션캡처·AI·CG로 VR 콘서트 구현. 정식 데뷔일 미확인. (전자신문 2026.10.7, 톱스타뉴스)</t>
         </is>
       </c>
     </row>
@@ -7171,7 +7223,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:D66"/>
+  <dimension ref="A1:D67"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="40" min="1" max="1"/>
@@ -8574,6 +8626,28 @@
       <c r="D66" s="86" t="inlineStr">
         <is>
           <t>2026.3.26 해체</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="86" t="inlineStr">
+        <is>
+          <t>필랜다트스튜디오</t>
+        </is>
+      </c>
+      <c r="B67" s="86" t="inlineStr">
+        <is>
+          <t>콘텐츠 기술 스타트업</t>
+        </is>
+      </c>
+      <c r="C67" s="86" t="inlineStr">
+        <is>
+          <t>하이프버스(HYPEVERSE)</t>
+        </is>
+      </c>
+      <c r="D67" s="86" t="inlineStr">
+        <is>
+          <t>청년 중심. 자체 모션캡처·AI·CG. 미국 시장 겨냥 버추얼 아이돌</t>
         </is>
       </c>
     </row>
@@ -8752,7 +8826,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E20"/>
+  <dimension ref="A1:E21"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="40" min="1" max="1"/>
@@ -9279,6 +9353,33 @@
       <c r="E20" s="66" t="inlineStr">
         <is>
           <t>※실사+버추얼 병행 하이브리드('리얼 라이프 듀얼 포맷'). 한일 2인조(리나·하루). 2025.12.22 첫 버추얼 라이브. (스포츠경향 2025.12.22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="113" t="inlineStr">
+        <is>
+          <t>하이프버스 (HYPEVERSE)</t>
+        </is>
+      </c>
+      <c r="B21" s="112" t="inlineStr">
+        <is>
+          <t>필랜다트스튜디오</t>
+        </is>
+      </c>
+      <c r="C21" s="113" t="inlineStr">
+        <is>
+          <t>프리데뷔</t>
+        </is>
+      </c>
+      <c r="D21" s="112" t="inlineStr">
+        <is>
+          <t>2026.10.7 프리데뷔 싱글 · 정식 데뷔일 미확인</t>
+        </is>
+      </c>
+      <c r="E21" s="66" t="inlineStr">
+        <is>
+          <t>5인조, 미국 시장 겨냥 영어 중심. 동양 판타지×미국 대중문화 컨셉. 유니버설뮤직 코리아 유통. (전자신문 2026.10.7)</t>
         </is>
       </c>
     </row>

--- a/data/한국_버추얼아이돌_전수조사_v8.xlsx
+++ b/data/한국_버추얼아이돌_전수조사_v8.xlsx
@@ -365,7 +365,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="116">
+  <cellXfs count="117">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -700,6 +700,9 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="16" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1350,14 +1353,14 @@
           <t>음반/아이돌형</t>
         </is>
       </c>
-      <c r="G9" s="111" t="inlineStr">
-        <is>
-          <t>데뷔전</t>
+      <c r="G9" s="50" t="inlineStr">
+        <is>
+          <t>활동중</t>
         </is>
       </c>
       <c r="H9" s="51" t="inlineStr">
         <is>
-          <t>[정식 데뷔 예정 · 2026.10] 23세기아이들 5인조(시우·우연·태강·제로·쿠우타, 첫 일본인 멤버 쿠우타; 전 멤버 해일). 멀티페르소나 세계관(전 멤버가 모든 유닛 참여). 2026.5.3 유튜브 라이브 데뷔 신고식, 9.22 프롤로그 싱글 '괴물' 공개, 9.27 첫 유튜브 라이브. 시리즈A 40억 투자. 10월 정식 데뷔 시 활동중 전환. (스포츠경향 2026.9.24/27)</t>
+          <t>[정식 데뷔 · 2026.10.26] 2026.10.26 데뷔 싱글 '럭키참(Lucky Charm)' 발매로 정식 데뷔('늑대 유닛'). 10.27 유튜브 데뷔 쇼케이스, 첫 EP 'SIX HEARTS' 11.17 예정. (톱스타뉴스 2026.10.27) — 이전: 23세기아이들 5인조(시우·우연·태강·제로·쿠우타, 첫 일본인 멤버 쿠우타; 전 멤버 해일). 멀티페르소나 세계관(전 멤버가 모든 유닛 참여). 2026.5.3 유튜브 라이브 데뷔 신고식, 9.22 프롤로그 싱글 '괴물' 공개, 9.27 첫 유튜브 라이브. 시리즈A 40억 투자. 10월 정식 데뷔 시 활동중 전환. (스포츠경향 2026.9.24/27)</t>
         </is>
       </c>
     </row>
@@ -1870,14 +1873,14 @@
           <t>버추얼휴먼/솔로</t>
         </is>
       </c>
-      <c r="G22" s="57" t="inlineStr">
-        <is>
-          <t>확인필요</t>
+      <c r="G22" s="52" t="inlineStr">
+        <is>
+          <t>휴면</t>
         </is>
       </c>
       <c r="H22" s="51" t="inlineStr">
         <is>
-          <t>SM 첫 버추얼 아티스트. 2024.9 Done 데뷔, 2025.8.7 Sensitive 발매 후 ~10개월 공백—간헐 활동 패턴</t>
+          <t>〔2026.10.27 점검: 휴면〕 마지막 음원 2025.8.7 'Sensitive', 공식 유튜브 마지막 업로드 2025.11.4(퍼포먼스·연습 영상) 이후 약 12개월 업로드 없음. 2026년 활동 기사 미확인. (공식 유튜브 RSS 확인 2026.10.27) | SM 첫 버추얼 아티스트. 2024.9 Done 데뷔, 2025.8.7 Sensitive 발매 후 ~10개월 공백—간헐 활동 패턴</t>
         </is>
       </c>
     </row>
@@ -4394,14 +4397,14 @@
           <t>스트리밍/MCN형</t>
         </is>
       </c>
-      <c r="G88" s="57" t="inlineStr">
-        <is>
-          <t>확인필요</t>
+      <c r="G88" s="52" t="inlineStr">
+        <is>
+          <t>휴면</t>
         </is>
       </c>
       <c r="H88" s="61" t="inlineStr">
         <is>
-          <t>2025.8 레벨스 자체 버추얼 보이그룹으로 공개(아카이브엔터 80% 인수 연계). 최근 업로드 빈도 미확인</t>
+          <t>〔2026.10.27 점검: 휴면〕 공식 유튜브 마지막 업로드 2025.8.12(KAYENNE '소요카제' 리릭비디오) 이후 14개월 공백. 2026년 활동 기사 미확인. (공식 유튜브 RSS 확인 2026.10.27) | 2025.8 레벨스 자체 버추얼 보이그룹으로 공개(아카이브엔터 80% 인수 연계). 최근 업로드 빈도 미확인</t>
         </is>
       </c>
     </row>
@@ -5926,30 +5929,30 @@
       </c>
     </row>
     <row r="127">
-      <c r="A127" s="107" t="n">
+      <c r="A127" s="112" t="n">
         <v>124</v>
       </c>
-      <c r="B127" s="108" t="inlineStr">
+      <c r="B127" s="113" t="inlineStr">
         <is>
           <t>오위스</t>
         </is>
       </c>
-      <c r="C127" s="107" t="inlineStr">
+      <c r="C127" s="112" t="inlineStr">
         <is>
           <t>OWIS</t>
         </is>
       </c>
-      <c r="D127" s="108" t="inlineStr">
+      <c r="D127" s="113" t="inlineStr">
         <is>
           <t>올마이애닉도츠(ama)</t>
         </is>
       </c>
-      <c r="E127" s="107" t="inlineStr">
+      <c r="E127" s="112" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F127" s="109" t="inlineStr">
+      <c r="F127" s="114" t="inlineStr">
         <is>
           <t>음반/아이돌형</t>
         </is>
@@ -5966,25 +5969,25 @@
       </c>
     </row>
     <row r="128">
-      <c r="A128" s="107" t="n">
+      <c r="A128" s="112" t="n">
         <v>125</v>
       </c>
-      <c r="B128" s="108" t="inlineStr">
+      <c r="B128" s="113" t="inlineStr">
         <is>
           <t>우주괴담</t>
         </is>
       </c>
-      <c r="C128" s="107" t="inlineStr">
+      <c r="C128" s="112" t="inlineStr">
         <is>
           <t>SPACE HORROR</t>
         </is>
       </c>
-      <c r="D128" s="108" t="inlineStr">
+      <c r="D128" s="113" t="inlineStr">
         <is>
           <t>그림 프로덕션(마운드미디어)</t>
         </is>
       </c>
-      <c r="E128" s="107" t="inlineStr">
+      <c r="E128" s="112" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
@@ -6006,30 +6009,30 @@
       </c>
     </row>
     <row r="129">
-      <c r="A129" s="107" t="n">
+      <c r="A129" s="112" t="n">
         <v>126</v>
       </c>
-      <c r="B129" s="108" t="inlineStr">
+      <c r="B129" s="113" t="inlineStr">
         <is>
           <t>미완소년</t>
         </is>
       </c>
-      <c r="C129" s="107" t="inlineStr">
+      <c r="C129" s="112" t="inlineStr">
         <is>
           <t>美完少年</t>
         </is>
       </c>
-      <c r="D129" s="108" t="inlineStr">
+      <c r="D129" s="113" t="inlineStr">
         <is>
           <t>어비스컴퍼니</t>
         </is>
       </c>
-      <c r="E129" s="107" t="inlineStr">
+      <c r="E129" s="112" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
       </c>
-      <c r="F129" s="109" t="inlineStr">
+      <c r="F129" s="114" t="inlineStr">
         <is>
           <t>음반/아이돌형</t>
         </is>
@@ -6046,30 +6049,30 @@
       </c>
     </row>
     <row r="130">
-      <c r="A130" s="107" t="n">
+      <c r="A130" s="112" t="n">
         <v>127</v>
       </c>
-      <c r="B130" s="108" t="inlineStr">
+      <c r="B130" s="113" t="inlineStr">
         <is>
           <t>이브닛</t>
         </is>
       </c>
-      <c r="C130" s="107" t="inlineStr">
+      <c r="C130" s="112" t="inlineStr">
         <is>
           <t>IVNIT</t>
         </is>
       </c>
-      <c r="D130" s="108" t="inlineStr">
+      <c r="D130" s="113" t="inlineStr">
         <is>
           <t>아카이브 스튜디오(AkaiV Studio)</t>
         </is>
       </c>
-      <c r="E130" s="107" t="inlineStr">
+      <c r="E130" s="112" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F130" s="109" t="inlineStr">
+      <c r="F130" s="114" t="inlineStr">
         <is>
           <t>음반/아이돌형</t>
         </is>
@@ -6086,30 +6089,30 @@
       </c>
     </row>
     <row r="131">
-      <c r="A131" s="107" t="n">
+      <c r="A131" s="112" t="n">
         <v>128</v>
       </c>
-      <c r="B131" s="108" t="inlineStr">
+      <c r="B131" s="113" t="inlineStr">
         <is>
           <t>수소진</t>
         </is>
       </c>
-      <c r="C131" s="107" t="inlineStr">
+      <c r="C131" s="112" t="inlineStr">
         <is>
           <t>SOOSOJIN</t>
         </is>
       </c>
-      <c r="D131" s="108" t="inlineStr">
+      <c r="D131" s="113" t="inlineStr">
         <is>
           <t>브라더후드 엔터테인먼트(제작 로코베리)</t>
         </is>
       </c>
-      <c r="E131" s="107" t="inlineStr">
+      <c r="E131" s="112" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F131" s="109" t="inlineStr">
+      <c r="F131" s="114" t="inlineStr">
         <is>
           <t>음반/아이돌형</t>
         </is>
@@ -6126,30 +6129,30 @@
       </c>
     </row>
     <row r="132">
-      <c r="A132" s="107" t="n">
+      <c r="A132" s="112" t="n">
         <v>129</v>
       </c>
-      <c r="B132" s="108" t="inlineStr">
+      <c r="B132" s="113" t="inlineStr">
         <is>
           <t>스파클즈</t>
         </is>
       </c>
-      <c r="C132" s="107" t="inlineStr">
+      <c r="C132" s="112" t="inlineStr">
         <is>
           <t>SPAKLZ</t>
         </is>
       </c>
-      <c r="D132" s="108" t="inlineStr">
+      <c r="D132" s="113" t="inlineStr">
         <is>
           <t>레진엔터테인먼트</t>
         </is>
       </c>
-      <c r="E132" s="107" t="inlineStr">
+      <c r="E132" s="112" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F132" s="109" t="inlineStr">
+      <c r="F132" s="114" t="inlineStr">
         <is>
           <t>음반/아이돌형</t>
         </is>
@@ -6166,25 +6169,25 @@
       </c>
     </row>
     <row r="133">
-      <c r="A133" s="107" t="n">
+      <c r="A133" s="112" t="n">
         <v>130</v>
       </c>
-      <c r="B133" s="108" t="inlineStr">
+      <c r="B133" s="113" t="inlineStr">
         <is>
           <t>헥시아</t>
         </is>
       </c>
-      <c r="C133" s="107" t="inlineStr">
+      <c r="C133" s="112" t="inlineStr">
         <is>
           <t>HEXIA</t>
         </is>
       </c>
-      <c r="D133" s="108" t="inlineStr">
+      <c r="D133" s="113" t="inlineStr">
         <is>
           <t>스콘(SCON)</t>
         </is>
       </c>
-      <c r="E133" s="107" t="inlineStr">
+      <c r="E133" s="112" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
@@ -6206,25 +6209,25 @@
       </c>
     </row>
     <row r="134">
-      <c r="A134" s="107" t="n">
+      <c r="A134" s="112" t="n">
         <v>131</v>
       </c>
-      <c r="B134" s="108" t="inlineStr">
+      <c r="B134" s="113" t="inlineStr">
         <is>
           <t>h.a.l.o</t>
         </is>
       </c>
-      <c r="C134" s="107" t="inlineStr">
+      <c r="C134" s="112" t="inlineStr">
         <is>
           <t>헤일로</t>
         </is>
       </c>
-      <c r="D134" s="108" t="inlineStr">
+      <c r="D134" s="113" t="inlineStr">
         <is>
           <t>스콘(SCON)</t>
         </is>
       </c>
-      <c r="E134" s="107" t="inlineStr">
+      <c r="E134" s="112" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
@@ -6246,25 +6249,25 @@
       </c>
     </row>
     <row r="135">
-      <c r="A135" s="107" t="n">
+      <c r="A135" s="112" t="n">
         <v>132</v>
       </c>
-      <c r="B135" s="108" t="inlineStr">
+      <c r="B135" s="113" t="inlineStr">
         <is>
           <t>제나</t>
         </is>
       </c>
-      <c r="C135" s="107" t="inlineStr">
+      <c r="C135" s="112" t="inlineStr">
         <is>
           <t>JENA</t>
         </is>
       </c>
-      <c r="D135" s="108" t="inlineStr">
+      <c r="D135" s="113" t="inlineStr">
         <is>
           <t>뮤즈온</t>
         </is>
       </c>
-      <c r="E135" s="107" t="inlineStr">
+      <c r="E135" s="112" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
@@ -6286,25 +6289,25 @@
       </c>
     </row>
     <row r="136">
-      <c r="A136" s="107" t="n">
+      <c r="A136" s="112" t="n">
         <v>133</v>
       </c>
-      <c r="B136" s="108" t="inlineStr">
+      <c r="B136" s="113" t="inlineStr">
         <is>
           <t>청솔</t>
         </is>
       </c>
-      <c r="C136" s="107" t="inlineStr">
+      <c r="C136" s="112" t="inlineStr">
         <is>
           <t>CHEONGSOL</t>
         </is>
       </c>
-      <c r="D136" s="108" t="inlineStr">
+      <c r="D136" s="113" t="inlineStr">
         <is>
           <t>(미확인)</t>
         </is>
       </c>
-      <c r="E136" s="107" t="inlineStr">
+      <c r="E136" s="112" t="inlineStr">
         <is>
           <t>2026</t>
         </is>
@@ -6326,825 +6329,825 @@
       </c>
     </row>
     <row r="137">
-      <c r="A137" s="107" t="n">
+      <c r="A137" s="112" t="n">
         <v>134</v>
       </c>
-      <c r="B137" s="108" t="inlineStr">
+      <c r="B137" s="113" t="inlineStr">
         <is>
           <t>아이시아</t>
         </is>
       </c>
-      <c r="C137" s="107" t="inlineStr">
+      <c r="C137" s="112" t="inlineStr">
         <is>
           <t>IXIA</t>
         </is>
       </c>
-      <c r="D137" s="108" t="inlineStr">
+      <c r="D137" s="113" t="inlineStr">
         <is>
           <t>(미확인)</t>
         </is>
       </c>
-      <c r="E137" s="107" t="inlineStr">
+      <c r="E137" s="112" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F137" s="109" t="inlineStr">
+      <c r="F137" s="114" t="inlineStr">
         <is>
           <t>음반/아이돌형</t>
         </is>
       </c>
-      <c r="G137" s="94" t="inlineStr">
+      <c r="G137" s="116" t="inlineStr">
+        <is>
+          <t>휴면</t>
+        </is>
+      </c>
+      <c r="H137" s="66" t="inlineStr">
+        <is>
+          <t>〔2026.10.27 점검: 휴면〕 소속사는 메가메타(엔터테인먼트)로 확인(스타뉴스 2025.8.12). 공식 유튜브 마지막 업로드 2025.12.12 이후 10개월 이상 공백, 2026년 신곡·기사 미확인. | 2025.8 데뷔 싱글 'Hide &amp; Find'. 소속·현황 추가 확인 필요. (톱셀럽 2025.10.23)</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="112" t="n">
+        <v>135</v>
+      </c>
+      <c r="B138" s="113" t="inlineStr">
+        <is>
+          <t>클루즈</t>
+        </is>
+      </c>
+      <c r="C138" s="112" t="inlineStr">
+        <is>
+          <t>CLUEZ</t>
+        </is>
+      </c>
+      <c r="D138" s="113" t="inlineStr">
+        <is>
+          <t>카론 유니버스(카론 크리에이티브)</t>
+        </is>
+      </c>
+      <c r="E138" s="112" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F138" s="114" t="inlineStr">
+        <is>
+          <t>음반/아이돌형</t>
+        </is>
+      </c>
+      <c r="G138" s="90" t="inlineStr">
+        <is>
+          <t>활동중</t>
+        </is>
+      </c>
+      <c r="H138" s="66" t="inlineStr">
+        <is>
+          <t>2인조 버추얼 걸그룹(키유·미하루). 2025.11.29 데뷔. 에스더(AESTHER)·PJX와 같은 카론 유니버스 소속. 추가 멤버 합류 가능성. (나무위키 카론 유니버스)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="112" t="n">
+        <v>136</v>
+      </c>
+      <c r="B139" s="113" t="inlineStr">
+        <is>
+          <t>루나데이즈</t>
+        </is>
+      </c>
+      <c r="C139" s="112" t="inlineStr">
+        <is>
+          <t>LUNADAYS</t>
+        </is>
+      </c>
+      <c r="D139" s="113" t="inlineStr">
+        <is>
+          <t>루나데이즈(개인사업자 MCN)</t>
+        </is>
+      </c>
+      <c r="E139" s="112" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F139" s="91" t="inlineStr">
+        <is>
+          <t>스트리밍/MCN형</t>
+        </is>
+      </c>
+      <c r="G139" s="90" t="inlineStr">
+        <is>
+          <t>활동중</t>
+        </is>
+      </c>
+      <c r="H139" s="66" t="inlineStr">
+        <is>
+          <t>〔2026.10.27 점검: 활동중〕 공식 유튜브에 3기 츠키아라 커버 영상이 2026.9.30·10.2·10.4 연속 업로드되어 최근 6개월 내 활동 확인. 기사는 여전히 미확인. | 2025.3 1기 셀레네 3인 SOOP 데뷔→2025.9 계약해지. 2기 아이즈키 2025.8 치지직, 3기 츠키아라 3인 2026.6 PV 공개. 기사 미확인(나무위키 단일).</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="112" t="n">
+        <v>137</v>
+      </c>
+      <c r="B140" s="113" t="inlineStr">
+        <is>
+          <t>애프터라이브</t>
+        </is>
+      </c>
+      <c r="C140" s="112" t="inlineStr">
+        <is>
+          <t>AfterLive</t>
+        </is>
+      </c>
+      <c r="D140" s="113" t="inlineStr">
+        <is>
+          <t>애프터라이브(자체 런칭)</t>
+        </is>
+      </c>
+      <c r="E140" s="112" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F140" s="91" t="inlineStr">
+        <is>
+          <t>스트리밍/MCN형</t>
+        </is>
+      </c>
+      <c r="G140" s="90" t="inlineStr">
+        <is>
+          <t>활동중</t>
+        </is>
+      </c>
+      <c r="H140" s="66" t="inlineStr">
+        <is>
+          <t>〔2026.10.27 점검: 활동중〕 공식 유튜브 2026.8.18 업로드, 비바체 콘야 유메이 다시보기 채널 2026.9.3 업로드로 최근 6개월 내 활동 확인. 기사 미확인(나무위키·유튜브 근거). | 2026.1.3~4 소속 그룹 '비바체' 4인(아마네루 피요·콘야 유메이·하루야 치에·시노 레이) 데뷔. 기사 미확인(나무위키 단일).</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="112" t="n">
+        <v>138</v>
+      </c>
+      <c r="B141" s="113" t="inlineStr">
+        <is>
+          <t>벨로디</t>
+        </is>
+      </c>
+      <c r="C141" s="112" t="inlineStr">
+        <is>
+          <t>VELODY</t>
+        </is>
+      </c>
+      <c r="D141" s="113" t="inlineStr">
+        <is>
+          <t>벨로디(자체 런칭)</t>
+        </is>
+      </c>
+      <c r="E141" s="112" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F141" s="91" t="inlineStr">
+        <is>
+          <t>스트리밍/MCN형</t>
+        </is>
+      </c>
+      <c r="G141" s="90" t="inlineStr">
+        <is>
+          <t>활동중</t>
+        </is>
+      </c>
+      <c r="H141" s="66" t="inlineStr">
+        <is>
+          <t>〔2026.10.27 점검: 활동중〕 공식 유튜브 2026.9.29 '2차 간담회', 10.17 업로드. 하나메 멤버 쿠로사와 쿄코·토카미 키나 채널도 10.26~27 업로드 중. 기사 미확인. | 2026.3.28 1기 유닛 하나메(HANAME) 2인(쿠로사와 쿄코·토카미 키나) 치지직 데뷔, 2026.9.4 2.0 비주얼 재데뷔. 기사 미확인(나무위키 단일).</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="112" t="n">
+        <v>139</v>
+      </c>
+      <c r="B142" s="113" t="inlineStr">
+        <is>
+          <t>아르포나</t>
+        </is>
+      </c>
+      <c r="C142" s="112" t="inlineStr">
+        <is>
+          <t>Arfauna</t>
+        </is>
+      </c>
+      <c r="D142" s="113" t="inlineStr">
+        <is>
+          <t>아르포나(버추얼 기획사)</t>
+        </is>
+      </c>
+      <c r="E142" s="112" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F142" s="91" t="inlineStr">
+        <is>
+          <t>스트리밍/MCN형</t>
+        </is>
+      </c>
+      <c r="G142" s="90" t="inlineStr">
+        <is>
+          <t>활동중</t>
+        </is>
+      </c>
+      <c r="H142" s="66" t="inlineStr">
+        <is>
+          <t>〔2026.10.27 점검: 활동중〕 유모어 1st 디지털 싱글 '경계를 넘어' MV 2026.7.6 공개(공식 유튜브), 클립 채널 10.11까지 업로드. 나무위키상 디아푸는 '이전 멤버'로 표기돼 2인(냐페르·선아린) 체제 가능성—확인 필요. | 2026.5.16 소속 그룹 '유모어' 3인(냐페르·디아푸·선아린) 데뷔. 기사 미확인(나무위키 단일).</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="112" t="n">
+        <v>140</v>
+      </c>
+      <c r="B143" s="113" t="inlineStr">
+        <is>
+          <t>바라바라</t>
+        </is>
+      </c>
+      <c r="C143" s="112" t="inlineStr">
+        <is>
+          <t>BARABARA</t>
+        </is>
+      </c>
+      <c r="D143" s="113" t="inlineStr">
+        <is>
+          <t>보쿠하이</t>
+        </is>
+      </c>
+      <c r="E143" s="112" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F143" s="91" t="inlineStr">
+        <is>
+          <t>스트리밍/MCN형</t>
+        </is>
+      </c>
+      <c r="G143" s="95" t="inlineStr">
+        <is>
+          <t>해체/종료</t>
+        </is>
+      </c>
+      <c r="H143" s="66" t="inlineStr">
+        <is>
+          <t>동아리형 6인조, 치지직. 2025.8.9~2026.2.27 순차 데뷔, 2025.12 보쿠하이 소속 전환. 2026.9.1 해체(카페 9.8 폐쇄). (나무위키)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" s="112" t="n">
+        <v>141</v>
+      </c>
+      <c r="B144" s="113" t="inlineStr">
+        <is>
+          <t>신디에잇</t>
+        </is>
+      </c>
+      <c r="C144" s="112" t="inlineStr">
+        <is>
+          <t>SYNDI8</t>
+        </is>
+      </c>
+      <c r="D144" s="113" t="inlineStr">
+        <is>
+          <t>수퍼톤(HYBE 자회사)</t>
+        </is>
+      </c>
+      <c r="E144" s="112" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="F144" s="114" t="inlineStr">
+        <is>
+          <t>음반/아이돌형</t>
+        </is>
+      </c>
+      <c r="G144" s="116" t="inlineStr">
+        <is>
+          <t>휴면</t>
+        </is>
+      </c>
+      <c r="H144" s="66" t="inlineStr">
+        <is>
+          <t>〔2026.10.27 점검: 휴면〕 공식 유튜브 마지막 업로드 2024.9.27. 운영사 수퍼톤이 2026.7 임시주총에서 해산 결의(더벨 2026.7.23), 단 그룹 해체 공지는 미확인 → 공지 확인 시 해체·종료로 전환. | AI 보이스 기반 4인조 버추얼 걸그룹(카나리·네스트·고요·레이븐). 2024.6.27 데뷔 음반 'MVP'. 2026 활동 여부 미확인. 표절 논란 문서화. (나무위키)</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="112" t="n">
+        <v>142</v>
+      </c>
+      <c r="B145" s="113" t="inlineStr">
+        <is>
+          <t>피버스</t>
+        </is>
+      </c>
+      <c r="C145" s="112" t="inlineStr">
+        <is>
+          <t>Feverse</t>
+        </is>
+      </c>
+      <c r="D145" s="113" t="inlineStr">
+        <is>
+          <t>카카오엔터테인먼트</t>
+        </is>
+      </c>
+      <c r="E145" s="112" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F145" s="104" t="inlineStr">
+        <is>
+          <t>혼합형</t>
+        </is>
+      </c>
+      <c r="G145" s="95" t="inlineStr">
+        <is>
+          <t>해체/종료</t>
+        </is>
+      </c>
+      <c r="H145" s="66" t="inlineStr">
+        <is>
+          <t>'소녀 리버스' 출신 현역 아이돌 5인의 버추얼 걸그룹. 2023.5.9 1집 'CHO' 데뷔, 일본어판 발매. 2024.3.8 해체. (나무위키)</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="112" t="n">
+        <v>143</v>
+      </c>
+      <c r="B146" s="113" t="inlineStr">
+        <is>
+          <t>이진법소년들</t>
+        </is>
+      </c>
+      <c r="C146" s="112" t="inlineStr">
+        <is>
+          <t>ØXONE</t>
+        </is>
+      </c>
+      <c r="D146" s="113" t="inlineStr">
+        <is>
+          <t>완구 기업(유통 워너뮤직 ADA)</t>
+        </is>
+      </c>
+      <c r="E146" s="112" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="F146" s="114" t="inlineStr">
+        <is>
+          <t>음반/아이돌형</t>
+        </is>
+      </c>
+      <c r="G146" s="95" t="inlineStr">
+        <is>
+          <t>해체/종료</t>
+        </is>
+      </c>
+      <c r="H146" s="66" t="inlineStr">
+        <is>
+          <t>5인조 버추얼 보이그룹(세계·비한·윤·아민·혜규). 2023.6.14 디지털싱글 'Designer' 데뷔. 2023.9 이후 활동중단·영상 비공개(해체 추정). (나무위키)</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="112" t="n">
+        <v>144</v>
+      </c>
+      <c r="B147" s="113" t="inlineStr">
+        <is>
+          <t>홀린</t>
+        </is>
+      </c>
+      <c r="C147" s="112" t="inlineStr">
+        <is>
+          <t>WhOLLiN</t>
+        </is>
+      </c>
+      <c r="D147" s="113" t="inlineStr">
+        <is>
+          <t>플레이리스트(PLAYLIST)</t>
+        </is>
+      </c>
+      <c r="E147" s="112" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F147" s="114" t="inlineStr">
+        <is>
+          <t>음반/아이돌형</t>
+        </is>
+      </c>
+      <c r="G147" s="90" t="inlineStr">
+        <is>
+          <t>활동중</t>
+        </is>
+      </c>
+      <c r="H147" s="66" t="inlineStr">
+        <is>
+          <t>'약한영웅' 제작사 플레이리스트 첫 버추얼 보이그룹 5인(시오·태이·이소·강우·도언). 2026.9.1 디지털 싱글 '깨어나다'(타이틀 Time Sleep, 펜타곤 후이 프로듀싱)로 정식 데뷔. (톱셀럽 2026.9.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="112" t="n">
+        <v>145</v>
+      </c>
+      <c r="B148" s="113" t="inlineStr">
+        <is>
+          <t>비그릿츠</t>
+        </is>
+      </c>
+      <c r="C148" s="112" t="inlineStr">
+        <is>
+          <t>BEGRITZ</t>
+        </is>
+      </c>
+      <c r="D148" s="113" t="inlineStr">
+        <is>
+          <t>디네이블(DNABLE)</t>
+        </is>
+      </c>
+      <c r="E148" s="112" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F148" s="114" t="inlineStr">
+        <is>
+          <t>음반/아이돌형</t>
+        </is>
+      </c>
+      <c r="G148" s="115" t="inlineStr">
+        <is>
+          <t>데뷔전</t>
+        </is>
+      </c>
+      <c r="H148" s="66" t="inlineStr">
+        <is>
+          <t>[데뷔전 · 정식 데뷔일 미확인] 디네이블 5인조(문찬·도하·태범·루빈·신의). '시공간을 모험하는 도깨비' 세계관. 알티(R.Tee) 음악 총괄·블락비 태일 A&amp;R. 2026.8 론칭(공식 웹 '달빛상회'), 10.3~4 자카르타 ICC 2026에서 데뷔 전 첫 퍼포먼스 공개. (노컷 2026.10.1, 톱셀럽 2026.10.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="112" t="n">
+        <v>146</v>
+      </c>
+      <c r="B149" s="113" t="inlineStr">
+        <is>
+          <t>걸스 아카이브</t>
+        </is>
+      </c>
+      <c r="C149" s="112" t="inlineStr">
+        <is>
+          <t>Girls Archives.</t>
+        </is>
+      </c>
+      <c r="D149" s="113" t="inlineStr">
+        <is>
+          <t>하이브 NEB × INCS toenter(일본)</t>
+        </is>
+      </c>
+      <c r="E149" s="112" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F149" s="104" t="inlineStr">
+        <is>
+          <t>혼합형</t>
+        </is>
+      </c>
+      <c r="G149" s="115" t="inlineStr">
+        <is>
+          <t>데뷔전</t>
+        </is>
+      </c>
+      <c r="H149" s="66" t="inlineStr">
+        <is>
+          <t>[프리데뷔 완료 · 2026.8.7 'Reborn' · 정식 데뷔일 미확인] ※실사 멤버+버추얼 캐릭터 연동 하이브리드(2.5D) — 완전 버추얼 아님, 경계 사례. 5인(유이사·에나·서연·히나리·소정). 싱글 'Reborn'=넷플릭스 '리본 히어로' 주제곡. 숀·허니웍스 프로듀싱, 캐릭터 디자인 LAM.</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="112" t="n">
+        <v>147</v>
+      </c>
+      <c r="B150" s="113" t="inlineStr">
+        <is>
+          <t>코스믹코드</t>
+        </is>
+      </c>
+      <c r="C150" s="112" t="inlineStr">
+        <is>
+          <t>COSMIC CODE</t>
+        </is>
+      </c>
+      <c r="D150" s="113" t="inlineStr">
+        <is>
+          <t>에이탑유니버스</t>
+        </is>
+      </c>
+      <c r="E150" s="112" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F150" s="114" t="inlineStr">
+        <is>
+          <t>음반/아이돌형</t>
+        </is>
+      </c>
+      <c r="G150" s="115" t="inlineStr">
+        <is>
+          <t>데뷔전</t>
+        </is>
+      </c>
+      <c r="H150" s="66" t="inlineStr">
+        <is>
+          <t>[프리데뷔(멤버 순차 공개) · 2026.9.9~] 일본 우타이테 시장 겨냥 2.5D 버추얼 아이돌 5인. 프리데뷔 싱글 'POKER FACE', 2026.11 도쿄·오사카 공연 추진. 日 YOANI 3억엔 투자. (한국일보 2026.9.9) 10.21 팀 앨범 예정, 11.13~14 도쿄·오사카 재팬 프리데뷔 콘서트. 日 YOANI 3억엔 투자(톱셀럽 2026.9.10).</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="112" t="n">
+        <v>148</v>
+      </c>
+      <c r="B151" s="113" t="inlineStr">
+        <is>
+          <t>STUN-X</t>
+        </is>
+      </c>
+      <c r="C151" s="112" t="inlineStr">
+        <is>
+          <t>우주아이돌리그</t>
+        </is>
+      </c>
+      <c r="D151" s="113" t="inlineStr">
+        <is>
+          <t>밀리언볼트(애니 스튜디오)</t>
+        </is>
+      </c>
+      <c r="E151" s="112" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F151" s="114" t="inlineStr">
+        <is>
+          <t>음반/아이돌형</t>
+        </is>
+      </c>
+      <c r="G151" s="115" t="inlineStr">
+        <is>
+          <t>데뷔전</t>
+        </is>
+      </c>
+      <c r="H151" s="66" t="inlineStr">
+        <is>
+          <t>[첫 싱글 'STUNing' 발매 2026.10.2 · 애니 '우주아이돌리그' 주제곡(OST)·성우 기반 IP라 아이돌 데뷔 판정 보류] (데일리한국 2026.10.27) 밀리언볼트 2D 버추얼 아이돌 IP '우주아이돌리그'(152개 행성 서바이벌 설정). 웹소설 2026.9.10 카카오페이지 연재. 캐릭터 콘텐츠 누적 2,000만뷰. 발매 확인 시 상태 재판정. (톱셀럽 2026.9.12)</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="112" t="n">
+        <v>149</v>
+      </c>
+      <c r="B152" s="113" t="inlineStr">
+        <is>
+          <t>WINKX</t>
+        </is>
+      </c>
+      <c r="C152" s="112" t="inlineStr">
+        <is>
+          <t>윙스</t>
+        </is>
+      </c>
+      <c r="D152" s="113" t="inlineStr">
+        <is>
+          <t>타이탄콘텐츠 × 대원미디어</t>
+        </is>
+      </c>
+      <c r="E152" s="112" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F152" s="114" t="inlineStr">
+        <is>
+          <t>음반/아이돌형</t>
+        </is>
+      </c>
+      <c r="G152" s="115" t="inlineStr">
+        <is>
+          <t>데뷔전</t>
+        </is>
+      </c>
+      <c r="H152" s="66" t="inlineStr">
+        <is>
+          <t>[데뷔 예정(MOU 단계) · 미확인] 360도 글로벌 IP(음악·만화·애니) 공동사업. 모션캡처 대원 자회사 이엠피. 일정 미확인. (스타뉴스 2026.4.15)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="112" t="n">
+        <v>150</v>
+      </c>
+      <c r="B153" s="113" t="inlineStr">
+        <is>
+          <t>레드소다써클</t>
+        </is>
+      </c>
+      <c r="C153" s="112" t="inlineStr">
+        <is>
+          <t>Red Soda Circle</t>
+        </is>
+      </c>
+      <c r="D153" s="113" t="inlineStr">
+        <is>
+          <t>코드판타지아</t>
+        </is>
+      </c>
+      <c r="E153" s="112" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="F153" s="104" t="inlineStr">
+        <is>
+          <t>혼합형</t>
+        </is>
+      </c>
+      <c r="G153" s="116" t="inlineStr">
         <is>
           <t>확인필요</t>
         </is>
       </c>
-      <c r="H137" s="66" t="inlineStr">
-        <is>
-          <t>2025.8 데뷔 싱글 'Hide &amp; Find'. 소속·현황 추가 확인 필요. (톱셀럽 2025.10.23)</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" s="107" t="n">
-        <v>135</v>
-      </c>
-      <c r="B138" s="108" t="inlineStr">
-        <is>
-          <t>클루즈</t>
-        </is>
-      </c>
-      <c r="C138" s="107" t="inlineStr">
-        <is>
-          <t>CLUEZ</t>
-        </is>
-      </c>
-      <c r="D138" s="108" t="inlineStr">
-        <is>
-          <t>카론 유니버스(카론 크리에이티브)</t>
-        </is>
-      </c>
-      <c r="E138" s="107" t="inlineStr">
+      <c r="H153" s="66" t="inlineStr">
+        <is>
+          <t>[활동 중단 추정 · 2026.5.8 마지막 업로드] 공식 유튜브 2026.5.8 '그동안 감사했습니다...레소클 여러분....' 영상 이후 업로드 중단. 설명란·기사에 해체 공지 미확인 → 공지 확인 시 해체·종료, 11월 이후에도 공백이면 휴면. — 이전: ※실사+버추얼 병행 하이브리드('리얼 라이프 듀얼 포맷'). 한일 2인조(리나·하루). 2025.12.22 첫 버추얼 라이브. (스포츠경향 2025.12.22)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154" s="41">
+      <c r="A154" s="112" t="n">
+        <v>151</v>
+      </c>
+      <c r="B154" s="113" t="inlineStr">
+        <is>
+          <t>비더후드</t>
+        </is>
+      </c>
+      <c r="C154" s="112" t="inlineStr">
+        <is>
+          <t>B THE HOOD</t>
+        </is>
+      </c>
+      <c r="D154" s="113" t="inlineStr">
+        <is>
+          <t>레벨스(LEVVELS·하이브×두나무 합작)</t>
+        </is>
+      </c>
+      <c r="E154" s="112" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F154" s="114" t="inlineStr">
+        <is>
+          <t>음반/아이돌형</t>
+        </is>
+      </c>
+      <c r="G154" s="90" t="inlineStr">
+        <is>
+          <t>활동중</t>
+        </is>
+      </c>
+      <c r="H154" s="66" t="inlineStr">
+        <is>
+          <t>[정식 데뷔 · 2026.10.20] 2026.10.20 첫 미니앨범 'THE REAL DEAL'(타이틀 'CHOP!') 전 세계 발매와 유튜브 라이브 데뷔 쇼케이스로 정식 데뷔. (OSEN/미주중앙일보 2026.10.19, 스포츠경향 2026.10.20) — 이전: 5인조(이언·제이스·퍼비·기류·루안), 레벨스. 선공개 'Lowkey'(6.26)·'The Baddest'(7.31)·'JADED'(8.21, 쇼츠 일간 1위). 다크SF 세계관. 유튜브 개설 7주 만에 구독 10만. 9.30 데뷔 포스터, 10.2 첫 공식 라이브. 데뷔 앨범 'THE REAL DEAL' 10.20 전세계 동시 발매 → 발매 후 활동중 전환. (아시아뉴스통신 2026.10.1)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155" s="41">
+      <c r="A155" s="112" t="n">
+        <v>152</v>
+      </c>
+      <c r="B155" s="113" t="inlineStr">
+        <is>
+          <t>라피드아이</t>
+        </is>
+      </c>
+      <c r="C155" s="112" t="inlineStr">
+        <is>
+          <t>RapidEye</t>
+        </is>
+      </c>
+      <c r="D155" s="113" t="inlineStr">
+        <is>
+          <t>FM STUDIO(에프엠 스튜디오)</t>
+        </is>
+      </c>
+      <c r="E155" s="112" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F138" s="109" t="inlineStr">
+      <c r="F155" s="114" t="inlineStr">
         <is>
           <t>음반/아이돌형</t>
         </is>
       </c>
-      <c r="G138" s="90" t="inlineStr">
+      <c r="G155" s="90" t="inlineStr">
         <is>
           <t>활동중</t>
         </is>
       </c>
-      <c r="H138" s="66" t="inlineStr">
-        <is>
-          <t>2인조 버추얼 걸그룹(키유·미하루). 2025.11.29 데뷔. 에스더(AESTHER)·PJX와 같은 카론 유니버스 소속. 추가 멤버 합류 가능성. (나무위키 카론 유니버스)</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" s="107" t="n">
-        <v>136</v>
-      </c>
-      <c r="B139" s="108" t="inlineStr">
-        <is>
-          <t>루나데이즈</t>
-        </is>
-      </c>
-      <c r="C139" s="107" t="inlineStr">
-        <is>
-          <t>LUNADAYS</t>
-        </is>
-      </c>
-      <c r="D139" s="108" t="inlineStr">
-        <is>
-          <t>루나데이즈(개인사업자 MCN)</t>
-        </is>
-      </c>
-      <c r="E139" s="107" t="inlineStr">
+      <c r="H155" s="66" t="inlineStr">
+        <is>
+          <t>여성 4인조. 무의식 세계 '레베리(REVE:RE)' 세계관. 2025.9.27 디지털 싱글 'Energy'로 정식 데뷔(고려대 축제 데뷔 무대). 2025.11 가상융합산업대전 공연, 한국메타버스협회 성과사례. (톱셀럽 2025.9.8·9.15, 머니투데이 2025.11.12·12.8)</t>
+        </is>
+      </c>
+    </row>
+    <row r="156" s="41">
+      <c r="A156" s="112" t="n">
+        <v>153</v>
+      </c>
+      <c r="B156" s="113" t="inlineStr">
+        <is>
+          <t>트윌릿 스튜디오</t>
+        </is>
+      </c>
+      <c r="C156" s="112" t="inlineStr">
+        <is>
+          <t>TWILLIT STUDIO</t>
+        </is>
+      </c>
+      <c r="D156" s="113" t="inlineStr">
+        <is>
+          <t>SAMG엔터테인먼트(에스에이엠지)</t>
+        </is>
+      </c>
+      <c r="E156" s="112" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
       </c>
-      <c r="F139" s="91" t="inlineStr">
+      <c r="F156" s="91" t="inlineStr">
         <is>
           <t>스트리밍/MCN형</t>
         </is>
       </c>
-      <c r="G139" s="94" t="inlineStr">
-        <is>
-          <t>확인필요</t>
-        </is>
-      </c>
-      <c r="H139" s="66" t="inlineStr">
-        <is>
-          <t>2025.3 1기 셀레네 3인 SOOP 데뷔→2025.9 계약해지. 2기 아이즈키 2025.8 치지직, 3기 츠키아라 3인 2026.6 PV 공개. 기사 미확인(나무위키 단일).</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" s="107" t="n">
-        <v>137</v>
-      </c>
-      <c r="B140" s="108" t="inlineStr">
-        <is>
-          <t>애프터라이브</t>
-        </is>
-      </c>
-      <c r="C140" s="107" t="inlineStr">
-        <is>
-          <t>AfterLive</t>
-        </is>
-      </c>
-      <c r="D140" s="108" t="inlineStr">
-        <is>
-          <t>애프터라이브(자체 런칭)</t>
-        </is>
-      </c>
-      <c r="E140" s="107" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="F140" s="91" t="inlineStr">
-        <is>
-          <t>스트리밍/MCN형</t>
-        </is>
-      </c>
-      <c r="G140" s="94" t="inlineStr">
-        <is>
-          <t>확인필요</t>
-        </is>
-      </c>
-      <c r="H140" s="66" t="inlineStr">
-        <is>
-          <t>2026.1.3~4 소속 그룹 '비바체' 4인(아마네루 피요·콘야 유메이·하루야 치에·시노 레이) 데뷔. 기사 미확인(나무위키 단일).</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" s="107" t="n">
-        <v>138</v>
-      </c>
-      <c r="B141" s="108" t="inlineStr">
-        <is>
-          <t>벨로디</t>
-        </is>
-      </c>
-      <c r="C141" s="107" t="inlineStr">
-        <is>
-          <t>VELODY</t>
-        </is>
-      </c>
-      <c r="D141" s="108" t="inlineStr">
-        <is>
-          <t>벨로디(자체 런칭)</t>
-        </is>
-      </c>
-      <c r="E141" s="107" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="F141" s="91" t="inlineStr">
-        <is>
-          <t>스트리밍/MCN형</t>
-        </is>
-      </c>
-      <c r="G141" s="94" t="inlineStr">
-        <is>
-          <t>확인필요</t>
-        </is>
-      </c>
-      <c r="H141" s="66" t="inlineStr">
-        <is>
-          <t>2026.3.28 1기 유닛 하나메(HANAME) 2인(쿠로사와 쿄코·토카미 키나) 치지직 데뷔, 2026.9.4 2.0 비주얼 재데뷔. 기사 미확인(나무위키 단일).</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="107" t="n">
-        <v>139</v>
-      </c>
-      <c r="B142" s="108" t="inlineStr">
-        <is>
-          <t>아르포나</t>
-        </is>
-      </c>
-      <c r="C142" s="107" t="inlineStr">
-        <is>
-          <t>Arfauna</t>
-        </is>
-      </c>
-      <c r="D142" s="108" t="inlineStr">
-        <is>
-          <t>아르포나(버추얼 기획사)</t>
-        </is>
-      </c>
-      <c r="E142" s="107" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="F142" s="91" t="inlineStr">
-        <is>
-          <t>스트리밍/MCN형</t>
-        </is>
-      </c>
-      <c r="G142" s="94" t="inlineStr">
-        <is>
-          <t>확인필요</t>
-        </is>
-      </c>
-      <c r="H142" s="66" t="inlineStr">
-        <is>
-          <t>2026.5.16 소속 그룹 '유모어' 3인(냐페르·디아푸·선아린) 데뷔. 기사 미확인(나무위키 단일).</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="107" t="n">
-        <v>140</v>
-      </c>
-      <c r="B143" s="108" t="inlineStr">
-        <is>
-          <t>바라바라</t>
-        </is>
-      </c>
-      <c r="C143" s="107" t="inlineStr">
-        <is>
-          <t>BARABARA</t>
-        </is>
-      </c>
-      <c r="D143" s="108" t="inlineStr">
-        <is>
-          <t>보쿠하이</t>
-        </is>
-      </c>
-      <c r="E143" s="107" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F143" s="91" t="inlineStr">
-        <is>
-          <t>스트리밍/MCN형</t>
-        </is>
-      </c>
-      <c r="G143" s="95" t="inlineStr">
-        <is>
-          <t>해체/종료</t>
-        </is>
-      </c>
-      <c r="H143" s="66" t="inlineStr">
-        <is>
-          <t>동아리형 6인조, 치지직. 2025.8.9~2026.2.27 순차 데뷔, 2025.12 보쿠하이 소속 전환. 2026.9.1 해체(카페 9.8 폐쇄). (나무위키)</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="107" t="n">
-        <v>141</v>
-      </c>
-      <c r="B144" s="108" t="inlineStr">
-        <is>
-          <t>신디에잇</t>
-        </is>
-      </c>
-      <c r="C144" s="107" t="inlineStr">
-        <is>
-          <t>SYNDI8</t>
-        </is>
-      </c>
-      <c r="D144" s="108" t="inlineStr">
-        <is>
-          <t>수퍼톤(HYBE 자회사)</t>
-        </is>
-      </c>
-      <c r="E144" s="107" t="inlineStr">
-        <is>
-          <t>2024</t>
-        </is>
-      </c>
-      <c r="F144" s="109" t="inlineStr">
-        <is>
-          <t>음반/아이돌형</t>
-        </is>
-      </c>
-      <c r="G144" s="94" t="inlineStr">
-        <is>
-          <t>확인필요</t>
-        </is>
-      </c>
-      <c r="H144" s="66" t="inlineStr">
-        <is>
-          <t>AI 보이스 기반 4인조 버추얼 걸그룹(카나리·네스트·고요·레이븐). 2024.6.27 데뷔 음반 'MVP'. 2026 활동 여부 미확인. 표절 논란 문서화. (나무위키)</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="107" t="n">
-        <v>142</v>
-      </c>
-      <c r="B145" s="108" t="inlineStr">
-        <is>
-          <t>피버스</t>
-        </is>
-      </c>
-      <c r="C145" s="107" t="inlineStr">
-        <is>
-          <t>Feverse</t>
-        </is>
-      </c>
-      <c r="D145" s="108" t="inlineStr">
-        <is>
-          <t>카카오엔터테인먼트</t>
-        </is>
-      </c>
-      <c r="E145" s="107" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F145" s="104" t="inlineStr">
-        <is>
-          <t>혼합형</t>
-        </is>
-      </c>
-      <c r="G145" s="95" t="inlineStr">
-        <is>
-          <t>해체/종료</t>
-        </is>
-      </c>
-      <c r="H145" s="66" t="inlineStr">
-        <is>
-          <t>'소녀 리버스' 출신 현역 아이돌 5인의 버추얼 걸그룹. 2023.5.9 1집 'CHO' 데뷔, 일본어판 발매. 2024.3.8 해체. (나무위키)</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="107" t="n">
-        <v>143</v>
-      </c>
-      <c r="B146" s="108" t="inlineStr">
-        <is>
-          <t>이진법소년들</t>
-        </is>
-      </c>
-      <c r="C146" s="107" t="inlineStr">
-        <is>
-          <t>ØXONE</t>
-        </is>
-      </c>
-      <c r="D146" s="108" t="inlineStr">
-        <is>
-          <t>완구 기업(유통 워너뮤직 ADA)</t>
-        </is>
-      </c>
-      <c r="E146" s="107" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
-      <c r="F146" s="109" t="inlineStr">
-        <is>
-          <t>음반/아이돌형</t>
-        </is>
-      </c>
-      <c r="G146" s="95" t="inlineStr">
-        <is>
-          <t>해체/종료</t>
-        </is>
-      </c>
-      <c r="H146" s="66" t="inlineStr">
-        <is>
-          <t>5인조 버추얼 보이그룹(세계·비한·윤·아민·혜규). 2023.6.14 디지털싱글 'Designer' 데뷔. 2023.9 이후 활동중단·영상 비공개(해체 추정). (나무위키)</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="107" t="n">
-        <v>144</v>
-      </c>
-      <c r="B147" s="108" t="inlineStr">
-        <is>
-          <t>홀린</t>
-        </is>
-      </c>
-      <c r="C147" s="107" t="inlineStr">
-        <is>
-          <t>WhOLLiN</t>
-        </is>
-      </c>
-      <c r="D147" s="108" t="inlineStr">
-        <is>
-          <t>플레이리스트(PLAYLIST)</t>
-        </is>
-      </c>
-      <c r="E147" s="107" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="F147" s="109" t="inlineStr">
-        <is>
-          <t>음반/아이돌형</t>
-        </is>
-      </c>
-      <c r="G147" s="90" t="inlineStr">
+      <c r="G156" s="90" t="inlineStr">
         <is>
           <t>활동중</t>
         </is>
       </c>
-      <c r="H147" s="66" t="inlineStr">
-        <is>
-          <t>'약한영웅' 제작사 플레이리스트 첫 버추얼 보이그룹 5인(시오·태이·이소·강우·도언). 2026.9.1 디지털 싱글 '깨어나다'(타이틀 Time Sleep, 펜타곤 후이 프로듀싱)로 정식 데뷔. (톱셀럽 2026.9.1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="107" t="n">
-        <v>145</v>
-      </c>
-      <c r="B148" s="108" t="inlineStr">
-        <is>
-          <t>비그릿츠</t>
-        </is>
-      </c>
-      <c r="C148" s="107" t="inlineStr">
-        <is>
-          <t>BEGRITZ</t>
-        </is>
-      </c>
-      <c r="D148" s="108" t="inlineStr">
-        <is>
-          <t>디네이블(DNABLE)</t>
-        </is>
-      </c>
-      <c r="E148" s="107" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="F148" s="109" t="inlineStr">
-        <is>
-          <t>음반/아이돌형</t>
-        </is>
-      </c>
-      <c r="G148" s="110" t="inlineStr">
-        <is>
-          <t>데뷔전</t>
-        </is>
-      </c>
-      <c r="H148" s="66" t="inlineStr">
-        <is>
-          <t>[데뷔전 · 정식 데뷔일 미확인] 디네이블 5인조(문찬·도하·태범·루빈·신의). '시공간을 모험하는 도깨비' 세계관. 알티(R.Tee) 음악 총괄·블락비 태일 A&amp;R. 2026.8 론칭(공식 웹 '달빛상회'), 10.3~4 자카르타 ICC 2026에서 데뷔 전 첫 퍼포먼스 공개. (노컷 2026.10.1, 톱셀럽 2026.10.1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="107" t="n">
-        <v>146</v>
-      </c>
-      <c r="B149" s="108" t="inlineStr">
-        <is>
-          <t>걸스 아카이브</t>
-        </is>
-      </c>
-      <c r="C149" s="107" t="inlineStr">
-        <is>
-          <t>Girls Archives.</t>
-        </is>
-      </c>
-      <c r="D149" s="108" t="inlineStr">
-        <is>
-          <t>하이브 NEB × INCS toenter(일본)</t>
-        </is>
-      </c>
-      <c r="E149" s="107" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="F149" s="104" t="inlineStr">
-        <is>
-          <t>혼합형</t>
-        </is>
-      </c>
-      <c r="G149" s="110" t="inlineStr">
-        <is>
-          <t>데뷔전</t>
-        </is>
-      </c>
-      <c r="H149" s="66" t="inlineStr">
-        <is>
-          <t>[프리데뷔 완료 · 2026.8.7 'Reborn' · 정식 데뷔일 미확인] ※실사 멤버+버추얼 캐릭터 연동 하이브리드(2.5D) — 완전 버추얼 아님, 경계 사례. 5인(유이사·에나·서연·히나리·소정). 싱글 'Reborn'=넷플릭스 '리본 히어로' 주제곡. 숀·허니웍스 프로듀싱, 캐릭터 디자인 LAM.</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="107" t="n">
-        <v>147</v>
-      </c>
-      <c r="B150" s="108" t="inlineStr">
-        <is>
-          <t>코스믹코드</t>
-        </is>
-      </c>
-      <c r="C150" s="107" t="inlineStr">
-        <is>
-          <t>COSMIC CODE</t>
-        </is>
-      </c>
-      <c r="D150" s="108" t="inlineStr">
-        <is>
-          <t>에이탑유니버스</t>
-        </is>
-      </c>
-      <c r="E150" s="107" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="F150" s="109" t="inlineStr">
-        <is>
-          <t>음반/아이돌형</t>
-        </is>
-      </c>
-      <c r="G150" s="110" t="inlineStr">
-        <is>
-          <t>데뷔전</t>
-        </is>
-      </c>
-      <c r="H150" s="66" t="inlineStr">
-        <is>
-          <t>[프리데뷔(멤버 순차 공개) · 2026.9.9~] 일본 우타이테 시장 겨냥 2.5D 버추얼 아이돌 5인. 프리데뷔 싱글 'POKER FACE', 2026.11 도쿄·오사카 공연 추진. 日 YOANI 3억엔 투자. (한국일보 2026.9.9) 10.21 팀 앨범 예정, 11.13~14 도쿄·오사카 재팬 프리데뷔 콘서트. 日 YOANI 3억엔 투자(톱셀럽 2026.9.10).</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" s="107" t="n">
-        <v>148</v>
-      </c>
-      <c r="B151" s="108" t="inlineStr">
-        <is>
-          <t>STUN-X</t>
-        </is>
-      </c>
-      <c r="C151" s="107" t="inlineStr">
-        <is>
-          <t>우주아이돌리그</t>
-        </is>
-      </c>
-      <c r="D151" s="108" t="inlineStr">
-        <is>
-          <t>밀리언볼트(애니 스튜디오)</t>
-        </is>
-      </c>
-      <c r="E151" s="107" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="F151" s="109" t="inlineStr">
-        <is>
-          <t>음반/아이돌형</t>
-        </is>
-      </c>
-      <c r="G151" s="110" t="inlineStr">
-        <is>
-          <t>데뷔전</t>
-        </is>
-      </c>
-      <c r="H151" s="66" t="inlineStr">
-        <is>
-          <t>[데뷔 예정 · 2026.10.2 첫 싱글 예고 — 발매 기사 미확인(10.7 기준)] 밀리언볼트 2D 버추얼 아이돌 IP '우주아이돌리그'(152개 행성 서바이벌 설정). 웹소설 2026.9.10 카카오페이지 연재. 캐릭터 콘텐츠 누적 2,000만뷰. 발매 확인 시 상태 재판정. (톱셀럽 2026.9.12)</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" s="107" t="n">
-        <v>149</v>
-      </c>
-      <c r="B152" s="108" t="inlineStr">
-        <is>
-          <t>WINKX</t>
-        </is>
-      </c>
-      <c r="C152" s="107" t="inlineStr">
-        <is>
-          <t>윙스</t>
-        </is>
-      </c>
-      <c r="D152" s="108" t="inlineStr">
-        <is>
-          <t>타이탄콘텐츠 × 대원미디어</t>
-        </is>
-      </c>
-      <c r="E152" s="107" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="F152" s="109" t="inlineStr">
-        <is>
-          <t>음반/아이돌형</t>
-        </is>
-      </c>
-      <c r="G152" s="110" t="inlineStr">
-        <is>
-          <t>데뷔전</t>
-        </is>
-      </c>
-      <c r="H152" s="66" t="inlineStr">
-        <is>
-          <t>[데뷔 예정(MOU 단계) · 미확인] 360도 글로벌 IP(음악·만화·애니) 공동사업. 모션캡처 대원 자회사 이엠피. 일정 미확인. (스타뉴스 2026.4.15)</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" s="107" t="n">
-        <v>150</v>
-      </c>
-      <c r="B153" s="108" t="inlineStr">
-        <is>
-          <t>레드소다써클</t>
-        </is>
-      </c>
-      <c r="C153" s="107" t="inlineStr">
-        <is>
-          <t>Red Soda Circle</t>
-        </is>
-      </c>
-      <c r="D153" s="108" t="inlineStr">
-        <is>
-          <t>코드판타지아</t>
-        </is>
-      </c>
-      <c r="E153" s="107" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F153" s="104" t="inlineStr">
-        <is>
-          <t>혼합형</t>
-        </is>
-      </c>
-      <c r="G153" s="110" t="inlineStr">
-        <is>
-          <t>데뷔전</t>
-        </is>
-      </c>
-      <c r="H153" s="66" t="inlineStr">
-        <is>
-          <t>[프리데뷔 · 2025.12.22] ※실사+버추얼 병행 하이브리드('리얼 라이프 듀얼 포맷'). 한일 2인조(리나·하루). 2025.12.22 첫 버추얼 라이브. (스포츠경향 2025.12.22)</t>
-        </is>
-      </c>
-    </row>
-    <row r="154" s="41">
-      <c r="A154" s="107" t="n">
-        <v>151</v>
-      </c>
-      <c r="B154" s="108" t="inlineStr">
-        <is>
-          <t>비더후드</t>
-        </is>
-      </c>
-      <c r="C154" s="107" t="inlineStr">
-        <is>
-          <t>B THE HOOD</t>
-        </is>
-      </c>
-      <c r="D154" s="108" t="inlineStr">
-        <is>
-          <t>레벨스(LEVVELS·하이브×두나무 합작)</t>
-        </is>
-      </c>
-      <c r="E154" s="107" t="inlineStr">
-        <is>
-          <t>2026</t>
-        </is>
-      </c>
-      <c r="F154" s="109" t="inlineStr">
-        <is>
-          <t>음반/아이돌형</t>
-        </is>
-      </c>
-      <c r="G154" s="110" t="inlineStr">
-        <is>
-          <t>데뷔전</t>
-        </is>
-      </c>
-      <c r="H154" s="66" t="inlineStr">
-        <is>
-          <t>[데뷔 확정 · 2026.10.20] 5인조(이언·제이스·퍼비·기류·루안), 레벨스. 선공개 'Lowkey'(6.26)·'The Baddest'(7.31)·'JADED'(8.21, 쇼츠 일간 1위). 다크SF 세계관. 유튜브 개설 7주 만에 구독 10만. 9.30 데뷔 포스터, 10.2 첫 공식 라이브. 데뷔 앨범 'THE REAL DEAL' 10.20 전세계 동시 발매 → 발매 후 활동중 전환. (아시아뉴스통신 2026.10.1)</t>
-        </is>
-      </c>
-    </row>
-    <row r="155" s="41">
-      <c r="A155" s="107" t="n">
-        <v>152</v>
-      </c>
-      <c r="B155" s="108" t="inlineStr">
-        <is>
-          <t>라피드아이</t>
-        </is>
-      </c>
-      <c r="C155" s="107" t="inlineStr">
-        <is>
-          <t>RapidEye</t>
-        </is>
-      </c>
-      <c r="D155" s="108" t="inlineStr">
-        <is>
-          <t>FM STUDIO(에프엠 스튜디오)</t>
-        </is>
-      </c>
-      <c r="E155" s="107" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F155" s="109" t="inlineStr">
-        <is>
-          <t>음반/아이돌형</t>
-        </is>
-      </c>
-      <c r="G155" s="90" t="inlineStr">
-        <is>
-          <t>활동중</t>
-        </is>
-      </c>
-      <c r="H155" s="66" t="inlineStr">
-        <is>
-          <t>여성 4인조. 무의식 세계 '레베리(REVE:RE)' 세계관. 2025.9.27 디지털 싱글 'Energy'로 정식 데뷔(고려대 축제 데뷔 무대). 2025.11 가상융합산업대전 공연, 한국메타버스협회 성과사례. (톱셀럽 2025.9.8·9.15, 머니투데이 2025.11.12·12.8)</t>
-        </is>
-      </c>
-    </row>
-    <row r="156" s="41">
-      <c r="A156" s="107" t="n">
-        <v>153</v>
-      </c>
-      <c r="B156" s="108" t="inlineStr">
-        <is>
-          <t>트윌릿 스튜디오</t>
-        </is>
-      </c>
-      <c r="C156" s="107" t="inlineStr">
-        <is>
-          <t>TWILLIT STUDIO</t>
-        </is>
-      </c>
-      <c r="D156" s="108" t="inlineStr">
-        <is>
-          <t>SAMG엔터테인먼트(에스에이엠지)</t>
-        </is>
-      </c>
-      <c r="E156" s="107" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="F156" s="91" t="inlineStr">
-        <is>
-          <t>스트리밍/MCN형</t>
-        </is>
-      </c>
-      <c r="G156" s="94" t="inlineStr">
-        <is>
-          <t>확인필요</t>
-        </is>
-      </c>
       <c r="H156" s="66" t="inlineStr">
         <is>
-          <t>SAMG의 2D 버츄얼 브랜드, 2025.3 런칭. 멤버 카페 카르테·모코 파르페·유우희·댕키·한서린·에루·솔스티스(현시후 2025.12.2 계약종료). 기사 미확인·나무위키 목록에만 있음. (나무위키 버츄얼 그룹 목록 4.5.5, 2026-10-06)</t>
+          <t>〔2026.10.27 점검: 활동중〕 공식 유튜브 2026.9.23·9.25·10.2 업로드(카페 카르테 합방 등), 멤버 한서린 채널 10.26 업로드. 기사 미확인. | SAMG의 2D 버츄얼 브랜드, 2025.3 런칭. 멤버 카페 카르테·모코 파르페·유우희·댕키·한서린·에루·솔스티스(현시후 2025.12.2 계약종료). 기사 미확인·나무위키 목록에만 있음. (나무위키 버츄얼 그룹 목록 4.5.5, 2026-10-06)</t>
         </is>
       </c>
     </row>
     <row r="157" s="41">
-      <c r="A157" s="107" t="n">
+      <c r="A157" s="112" t="n">
         <v>154</v>
       </c>
-      <c r="B157" s="108" t="inlineStr">
+      <c r="B157" s="113" t="inlineStr">
         <is>
           <t>수니문</t>
         </is>
       </c>
-      <c r="C157" s="107" t="inlineStr">
+      <c r="C157" s="112" t="inlineStr">
         <is>
           <t>SOONIMOON(구 버니문)</t>
         </is>
       </c>
-      <c r="D157" s="108" t="inlineStr">
+      <c r="D157" s="113" t="inlineStr">
         <is>
           <t>수니그룹</t>
         </is>
       </c>
-      <c r="E157" s="107" t="inlineStr">
+      <c r="E157" s="112" t="inlineStr">
         <is>
           <t>2025</t>
         </is>
@@ -7201,7 +7204,7 @@
       </c>
       <c r="H158" s="66" t="inlineStr">
         <is>
-          <t>[프리데뷔 · 2026.10.7 'Weirdo'] 5인조 K-POP 버추얼 아이돌(멤버 MAKO 등). 기획 단계부터 미국 핵심 시장, 영어 중심 음악·콘텐츠(멤버 전원 네이티브급 영어). 도깨비·구미호 동양 판타지 × 미국 대중문화·스트리트 패션. 유니버설뮤직 코리아 유통. 자체 모션캡처·AI·CG로 VR 콘서트 구현. 정식 데뷔일 미확인. (전자신문 2026.10.7, 톱스타뉴스)</t>
+          <t>[프리데뷔 · 2026.10.7 'Weirdo' · 정식 데뷔 2027 상반기 예정] 5인조 K-POP 버추얼 아이돌(레빈·아토·타쿠미·렌·키로; MAKO는 마스코트 불독). 기획 단계부터 미국 핵심 시장, 영어 중심 음악·콘텐츠(멤버 전원 네이티브급 영어). 도깨비·구미호 동양 판타지 × 미국 대중문화·스트리트 패션. 유니버설뮤직 코리아 유통. 자체 모션캡처·AI·CG로 VR 콘서트 구현. 정식 데뷔일 미확인. (전자신문 2026.10.7, 톱스타뉴스) (코리아중앙데일리 2026.10.7, 톱셀럽 2026.10)</t>
         </is>
       </c>
     </row>
@@ -8681,6 +8684,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="41">
       <c r="A3" s="71" t="inlineStr">
         <is>
@@ -8688,7 +8692,7 @@
         </is>
       </c>
       <c r="B3" s="46">
-        <f>COUNTA('버추얼 그룹 전수목록'!B4:B157)</f>
+        <f>COUNTA('버추얼 그룹 전수목록'!B4:B1000)</f>
         <v/>
       </c>
     </row>
@@ -8699,7 +8703,7 @@
         </is>
       </c>
       <c r="B4" s="46">
-        <f>COUNTIF('버추얼 그룹 전수목록'!G4:G157,"활동중")</f>
+        <f>COUNTIF('버추얼 그룹 전수목록'!G4:G1000,"활동중")</f>
         <v/>
       </c>
     </row>
@@ -8710,7 +8714,7 @@
         </is>
       </c>
       <c r="B5" s="46">
-        <f>COUNTIF('버추얼 그룹 전수목록'!G4:G157,"해체/종료")</f>
+        <f>COUNTIF('버추얼 그룹 전수목록'!G4:G1000,"해체/종료")</f>
         <v/>
       </c>
     </row>
@@ -8721,7 +8725,7 @@
         </is>
       </c>
       <c r="B6" s="46">
-        <f>COUNTIF('버추얼 그룹 전수목록'!G4:G157,"전환")</f>
+        <f>COUNTIF('버추얼 그룹 전수목록'!G4:G1000,"전환")</f>
         <v/>
       </c>
     </row>
@@ -8732,7 +8736,7 @@
         </is>
       </c>
       <c r="B7" s="46">
-        <f>COUNTIF('버추얼 그룹 전수목록'!G4:G157,"확인필요")</f>
+        <f>COUNTIF('버추얼 그룹 전수목록'!G4:G1000,"확인필요")</f>
         <v/>
       </c>
     </row>
@@ -8743,7 +8747,7 @@
         </is>
       </c>
       <c r="B8" s="73">
-        <f>COUNTIF('버추얼 그룹 전수목록'!G4:G157,"휴면")</f>
+        <f>COUNTIF('버추얼 그룹 전수목록'!G4:G1000,"휴면")</f>
         <v/>
       </c>
     </row>
@@ -8754,7 +8758,7 @@
         </is>
       </c>
       <c r="B9" s="106">
-        <f>COUNTIF('버추얼 그룹 전수목록'!G4:G157,"데뷔전")</f>
+        <f>COUNTIF('버추얼 그룹 전수목록'!G4:G1000,"데뷔전")</f>
         <v/>
       </c>
     </row>
@@ -8773,7 +8777,7 @@
         </is>
       </c>
       <c r="B11" s="46">
-        <f>COUNTIF('버추얼 그룹 전수목록'!F4:F157,"음반/아이돌형")</f>
+        <f>COUNTIF('버추얼 그룹 전수목록'!F4:F1000,"음반/아이돌형")</f>
         <v/>
       </c>
     </row>
@@ -8784,7 +8788,7 @@
         </is>
       </c>
       <c r="B12" s="46">
-        <f>COUNTIF('버추얼 그룹 전수목록'!F4:F157,"버추얼휴먼/솔로")</f>
+        <f>COUNTIF('버추얼 그룹 전수목록'!F4:F1000,"버추얼휴먼/솔로")</f>
         <v/>
       </c>
     </row>
@@ -8795,7 +8799,7 @@
         </is>
       </c>
       <c r="B13" s="46">
-        <f>COUNTIF('버추얼 그룹 전수목록'!F4:F157,"스트리밍/MCN형")</f>
+        <f>COUNTIF('버추얼 그룹 전수목록'!F4:F1000,"스트리밍/MCN형")</f>
         <v/>
       </c>
     </row>
@@ -8806,7 +8810,7 @@
         </is>
       </c>
       <c r="B14" s="46">
-        <f>COUNTIF('버추얼 그룹 전수목록'!F4:F157,"혼합형")</f>
+        <f>COUNTIF('버추얼 그룹 전수목록'!F4:F1000,"혼합형")</f>
         <v/>
       </c>
     </row>
@@ -8883,17 +8887,17 @@
       </c>
       <c r="C3" s="48" t="inlineStr">
         <is>
-          <t>정식 데뷔 예정(10월)</t>
+          <t>정식 데뷔 완료(2026.10.26) → 전수목록 활동중 전환</t>
         </is>
       </c>
       <c r="D3" s="47" t="inlineStr">
         <is>
-          <t>2026.10 (프롤로그 '괴물' 9.22)</t>
+          <t>2026.10.26</t>
         </is>
       </c>
       <c r="E3" s="54" t="inlineStr">
         <is>
-          <t>멀티페르소나 6인 보이그룹. 5월 첫 라이브, 정식데뷔 준비 중 2026.9.22 프롤로그 싱글 '괴물', 10월 정식 데뷔 확정·첫 일본인 멤버 쿠우타 공개(톱셀럽 2026.9.24).</t>
+          <t>(2026.10.27 점검) 데뷔 싱글 '럭키참', 10.27 데뷔 쇼케이스 라이브, 첫 EP 'SIX HEARTS' 11.17 예정. 기사상 멤버 5인(시우·우연·태강·제로·쿠우타). (톱스타뉴스 2026.10.27) | 멀티페르소나 6인 보이그룹. 5월 첫 라이브, 정식데뷔 준비 중 2026.9.22 프롤로그 싱글 '괴물', 10월 정식 데뷔 확정·첫 일본인 멤버 쿠우타 공개(톱셀럽 2026.9.24).</t>
         </is>
       </c>
     </row>
@@ -8910,17 +8914,17 @@
       </c>
       <c r="C4" s="48" t="inlineStr">
         <is>
-          <t>데뷔 예정</t>
+          <t>데뷔 예정(그룹명 미확인)</t>
         </is>
       </c>
       <c r="D4" s="47" t="inlineStr">
         <is>
-          <t>2026 내</t>
+          <t>미확인</t>
         </is>
       </c>
       <c r="E4" s="54" t="inlineStr">
         <is>
-          <t>위고식스에 이은 두 번째 버추얼 보이그룹(회사 발표)</t>
+          <t>(2026.10.27 점검) 2026.4 '연내 2팀 데뷔' 발표(톱셀럽·와우테일 2026.4.14) 이후 그룹명·데뷔일 공개 기사 미확인. 위고식스 데뷔 기사(10.27)에도 언급 없음. | 위고식스에 이은 두 번째 버추얼 보이그룹(회사 발표)</t>
         </is>
       </c>
     </row>
@@ -9141,76 +9145,76 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="108" t="inlineStr">
+      <c r="A13" s="113" t="inlineStr">
         <is>
           <t>비더후드 (B THE HOOD)</t>
         </is>
       </c>
-      <c r="B13" s="107" t="inlineStr">
+      <c r="B13" s="112" t="inlineStr">
         <is>
           <t>레벨스(LEVVELS·하이브×두나무 합작)</t>
         </is>
       </c>
-      <c r="C13" s="108" t="inlineStr">
-        <is>
-          <t>정식 데뷔 확정</t>
-        </is>
-      </c>
-      <c r="D13" s="107" t="inlineStr">
-        <is>
-          <t>2026.10.20 (선공개 6.26/7.31/8.21)</t>
+      <c r="C13" s="113" t="inlineStr">
+        <is>
+          <t>정식 데뷔 완료(2026.10.20) → 전수목록 편입</t>
+        </is>
+      </c>
+      <c r="D13" s="112" t="inlineStr">
+        <is>
+          <t>2026.10.20</t>
         </is>
       </c>
       <c r="E13" s="66" t="inlineStr">
         <is>
-          <t>5인조(이언·제이스·퍼비·기류·루안). 선공개 싱글 3장 — 'Lowkey'(6.26), 'The Baddest'(7.31), 'JADED'(8.21, 기사상 '정식 데뷔 전 마지막 선공개'). 행성 노버스를 떠난 외계인 다크SF 세계관. 유튜브 개설 7주 만에 구독 10만, 쇼츠 누적 500만뷰. 정식 데뷔 시 전수목록 편입 예정. (스포츠경향 2026.8.13, 텐아시아 2026.7.29) 데뷔 앨범 'THE REAL DEAL' 10.20 발매 확정(네이트 2026.10.1).</t>
+          <t>(2026.10.27 점검) 첫 미니 'THE REAL DEAL'(타이틀 'CHOP!', 6곡) 발매·유튜브 데뷔 쇼케이스. (OSEN 2026.10.19) | 5인조(이언·제이스·퍼비·기류·루안). 선공개 싱글 3장 — 'Lowkey'(6.26), 'The Baddest'(7.31), 'JADED'(8.21, 기사상 '정식 데뷔 전 마지막 선공개'). 행성 노버스를 떠난 외계인 다크SF 세계관. 유튜브 개설 7주 만에 구독 10만, 쇼츠 누적 500만뷰. 정식 데뷔 시 전수목록 편입 예정. (스포츠경향 2026.8.13, 텐아시아 2026.7.29) 데뷔 앨범 'THE REAL DEAL' 10.20 발매 확정(네이트 2026.10.1).</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="108" t="inlineStr">
+      <c r="A14" s="113" t="inlineStr">
         <is>
           <t>비그릿츠 (BEGRITZ)</t>
         </is>
       </c>
-      <c r="B14" s="107" t="inlineStr">
+      <c r="B14" s="112" t="inlineStr">
         <is>
           <t>디네이블(DNABLE)</t>
         </is>
       </c>
-      <c r="C14" s="108" t="inlineStr">
+      <c r="C14" s="113" t="inlineStr">
         <is>
           <t>론칭 완료·정식 데뷔 전</t>
         </is>
       </c>
-      <c r="D14" s="107" t="inlineStr">
-        <is>
-          <t>2026.8 론칭 · 정식 데뷔일 미확인</t>
+      <c r="D14" s="112" t="inlineStr">
+        <is>
+          <t>정식 데뷔일 미확인</t>
         </is>
       </c>
       <c r="E14" s="66" t="inlineStr">
         <is>
-          <t>5인조. '시공간을 모험하는 도깨비' 세계관. 프로듀서 알티(R.Tee) 음악 총괄, 블락비 태일 A&amp;R·보컬디렉터. 실시간 CG·AI·퍼포먼스캡처 결합.</t>
+          <t>(2026.10.27 점검) 10.3~4 ICC 2026(자카르타) 데뷔 전 무대. 라이브로 자작곡 선공개 중. 공식 유튜브 @BEGRITZ 활발. | 5인조. '시공간을 모험하는 도깨비' 세계관. 프로듀서 알티(R.Tee) 음악 총괄, 블락비 태일 A&amp;R·보컬디렉터. 실시간 CG·AI·퍼포먼스캡처 결합.</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="108" t="inlineStr">
+      <c r="A15" s="113" t="inlineStr">
         <is>
           <t>홀린 (WhOLLiN)</t>
         </is>
       </c>
-      <c r="B15" s="107" t="inlineStr">
+      <c r="B15" s="112" t="inlineStr">
         <is>
           <t>플레이리스트(PLAYLIST)</t>
         </is>
       </c>
-      <c r="C15" s="108" t="inlineStr">
+      <c r="C15" s="113" t="inlineStr">
         <is>
           <t>정식 데뷔 완료(2026.9.1) → 전수목록 편입</t>
         </is>
       </c>
-      <c r="D15" s="107" t="inlineStr">
+      <c r="D15" s="112" t="inlineStr">
         <is>
           <t>2026.9.1</t>
         </is>
@@ -9222,137 +9226,137 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="108" t="inlineStr">
+      <c r="A16" s="113" t="inlineStr">
         <is>
           <t>걸스 아카이브 (Girls Archives.)</t>
         </is>
       </c>
-      <c r="B16" s="107" t="inlineStr">
+      <c r="B16" s="112" t="inlineStr">
         <is>
           <t>하이브 NEB × INCS toenter(일본)</t>
         </is>
       </c>
-      <c r="C16" s="108" t="inlineStr">
+      <c r="C16" s="113" t="inlineStr">
         <is>
           <t>프리데뷔 완료</t>
         </is>
       </c>
-      <c r="D16" s="107" t="inlineStr">
-        <is>
-          <t>2026.8.7 'Reborn' · 정식 데뷔일 미확인</t>
+      <c r="D16" s="112" t="inlineStr">
+        <is>
+          <t>정식 데뷔일 미확인</t>
         </is>
       </c>
       <c r="E16" s="66" t="inlineStr">
         <is>
-          <t>※실사 멤버+버추얼 캐릭터 연동 하이브리드(2.5D) — 완전 버추얼 아님, 경계 사례. 5인(유이사·에나·서연·히나리·소정). 싱글 'Reborn'=넷플릭스 '리본 히어로' 주제곡. 숀·허니웍스 프로듀싱, 캐릭터 디자인 LAM.</t>
+          <t>(2026.10.27 점검) 공식 발표 미확인(나무위키는 2027 상반기 예정으로 기재—기사 근거 없음). | ※실사 멤버+버추얼 캐릭터 연동 하이브리드(2.5D) — 완전 버추얼 아님, 경계 사례. 5인(유이사·에나·서연·히나리·소정). 싱글 'Reborn'=넷플릭스 '리본 히어로' 주제곡. 숀·허니웍스 프로듀싱, 캐릭터 디자인 LAM.</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="108" t="inlineStr">
+      <c r="A17" s="113" t="inlineStr">
         <is>
           <t>코스믹코드 (COSMIC CODE)</t>
         </is>
       </c>
-      <c r="B17" s="107" t="inlineStr">
+      <c r="B17" s="112" t="inlineStr">
         <is>
           <t>에이탑유니버스</t>
         </is>
       </c>
-      <c r="C17" s="108" t="inlineStr">
-        <is>
-          <t>프리데뷔(멤버 순차 공개)</t>
-        </is>
-      </c>
-      <c r="D17" s="107" t="inlineStr">
+      <c r="C17" s="113" t="inlineStr">
+        <is>
+          <t>프리데뷔 진행 중</t>
+        </is>
+      </c>
+      <c r="D17" s="112" t="inlineStr">
         <is>
           <t>2026.9.9~</t>
         </is>
       </c>
       <c r="E17" s="66" t="inlineStr">
         <is>
-          <t>일본 우타이테 시장 겨냥 2.5D 버추얼 아이돌 5인. 프리데뷔 싱글 'POKER FACE', 2026.11 도쿄·오사카 공연 추진. 日 YOANI 3억엔 투자. (한국일보 2026.9.9)</t>
+          <t>(2026.10.27 점검) 10.21 팀 앨범 발매 기사 미확인. 공식 유튜브(@COSMICCODE_official_atop)에 첫 그룹곡 'CODE RED' MV 10.23 공개, 10.24~27 멤버 자기소개·커버 업로드. 11.13~14 재팬 프리데뷔 콘서트. | 일본 우타이테 시장 겨냥 2.5D 버추얼 아이돌 5인. 프리데뷔 싱글 'POKER FACE', 2026.11 도쿄·오사카 공연 추진. 日 YOANI 3억엔 투자. (한국일보 2026.9.9)</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="108" t="inlineStr">
+      <c r="A18" s="113" t="inlineStr">
         <is>
           <t>STUN-X (우주아이돌리그)</t>
         </is>
       </c>
-      <c r="B18" s="107" t="inlineStr">
+      <c r="B18" s="112" t="inlineStr">
         <is>
           <t>밀리언볼트(애니 스튜디오)</t>
         </is>
       </c>
-      <c r="C18" s="108" t="inlineStr">
-        <is>
-          <t>데뷔 예정(발매 확인 필요)</t>
-        </is>
-      </c>
-      <c r="D18" s="107" t="inlineStr">
-        <is>
-          <t>2026.10.2 예고</t>
+      <c r="C18" s="113" t="inlineStr">
+        <is>
+          <t>첫 싱글 발매 완료(2026.10.2)</t>
+        </is>
+      </c>
+      <c r="D18" s="112" t="inlineStr">
+        <is>
+          <t>2026.10.2</t>
         </is>
       </c>
       <c r="E18" s="66" t="inlineStr">
         <is>
-          <t>2D 버추얼 아이돌 IP. 웹소설 2026.9.10 카카오페이지 연재, 10.2 첫 디지털 싱글 예정. 캐릭터 콘텐츠 누적 2,000만뷰. (MBN 2026.9.11)</t>
+          <t>(2026.10.27 점검) 'STUNing' 음원·MV 공개(데일리한국 2026.10.27). 공식 유튜브는 주제곡(OST)으로 표기 — 정식 아이돌 데뷔로 볼지 판단 필요. | 2D 버추얼 아이돌 IP. 웹소설 2026.9.10 카카오페이지 연재, 10.2 첫 디지털 싱글 예정. 캐릭터 콘텐츠 누적 2,000만뷰. (MBN 2026.9.11)</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="108" t="inlineStr">
+      <c r="A19" s="113" t="inlineStr">
         <is>
           <t>WINKX (윙스)</t>
         </is>
       </c>
-      <c r="B19" s="107" t="inlineStr">
+      <c r="B19" s="112" t="inlineStr">
         <is>
           <t>타이탄콘텐츠 × 대원미디어</t>
         </is>
       </c>
-      <c r="C19" s="108" t="inlineStr">
+      <c r="C19" s="113" t="inlineStr">
         <is>
           <t>데뷔 예정(MOU 단계)</t>
         </is>
       </c>
-      <c r="D19" s="107" t="inlineStr">
+      <c r="D19" s="112" t="inlineStr">
         <is>
           <t>미확인</t>
         </is>
       </c>
       <c r="E19" s="66" t="inlineStr">
         <is>
-          <t>360도 글로벌 IP(음악·만화·애니) 공동사업. 모션캡처 대원 자회사 이엠피. 일정 미확인. (스타뉴스 2026.4.15)</t>
+          <t>(2026.10.27 점검) 4.14 MOU 이후 후속 기사 미확인. 기사에 따라 '올해' 또는 '내년' 데뷔 목표로 엇갈림. | 360도 글로벌 IP(음악·만화·애니) 공동사업. 모션캡처 대원 자회사 이엠피. 일정 미확인. (스타뉴스 2026.4.15)</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="108" t="inlineStr">
+      <c r="A20" s="113" t="inlineStr">
         <is>
           <t>레드소다써클 (Red Soda Circle)</t>
         </is>
       </c>
-      <c r="B20" s="107" t="inlineStr">
+      <c r="B20" s="112" t="inlineStr">
         <is>
           <t>코드판타지아</t>
         </is>
       </c>
-      <c r="C20" s="108" t="inlineStr">
-        <is>
-          <t>프리데뷔</t>
-        </is>
-      </c>
-      <c r="D20" s="107" t="inlineStr">
-        <is>
-          <t>2025.12.22</t>
+      <c r="C20" s="113" t="inlineStr">
+        <is>
+          <t>활동 중단 추정(확인필요)</t>
+        </is>
+      </c>
+      <c r="D20" s="112" t="inlineStr">
+        <is>
+          <t>2026.5.8 마지막 업로드</t>
         </is>
       </c>
       <c r="E20" s="66" t="inlineStr">
         <is>
-          <t>※실사+버추얼 병행 하이브리드('리얼 라이프 듀얼 포맷'). 한일 2인조(리나·하루). 2025.12.22 첫 버추얼 라이브. (스포츠경향 2025.12.22)</t>
+          <t>(2026.10.27 점검) 공식 유튜브 '그동안 감사했습니다' 영상(5.8) 이후 업로드 없음. 해체 공지·기사 미확인. | ※실사+버추얼 병행 하이브리드('리얼 라이프 듀얼 포맷'). 한일 2인조(리나·하루). 2025.12.22 첫 버추얼 라이브. (스포츠경향 2025.12.22)</t>
         </is>
       </c>
     </row>
@@ -9374,12 +9378,12 @@
       </c>
       <c r="D21" s="112" t="inlineStr">
         <is>
-          <t>2026.10.7 프리데뷔 싱글 · 정식 데뷔일 미확인</t>
+          <t>2026.10.7 프리데뷔 · 정식 데뷔 2027 상반기 예정</t>
         </is>
       </c>
       <c r="E21" s="66" t="inlineStr">
         <is>
-          <t>5인조, 미국 시장 겨냥 영어 중심. 동양 판타지×미국 대중문화 컨셉. 유니버설뮤직 코리아 유통. (전자신문 2026.10.7)</t>
+          <t>(2026.10.27 점검) 정식 데뷔 '내년 상반기' 예정(코리아중앙데일리 2026.10.7). 멤버 레빈·아토·타쿠미·렌·키로. 공식 유튜브 @hypeverse_world. | 5인조, 미국 시장 겨냥 영어 중심. 동양 판타지×미국 대중문화 컨셉. 유니버설뮤직 코리아 유통. (전자신문 2026.10.7)</t>
         </is>
       </c>
     </row>

--- a/data/한국_버추얼아이돌_전수조사_v8.xlsx
+++ b/data/한국_버추얼아이돌_전수조사_v8.xlsx
@@ -1055,7 +1055,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:H158"/>
+  <dimension ref="A1:H160"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="5" customWidth="1" style="40" min="1" max="1"/>
@@ -6917,14 +6917,14 @@
           <t>음반/아이돌형</t>
         </is>
       </c>
-      <c r="G151" s="115" t="inlineStr">
-        <is>
-          <t>데뷔전</t>
+      <c r="G151" s="90" t="inlineStr">
+        <is>
+          <t>활동중</t>
         </is>
       </c>
       <c r="H151" s="66" t="inlineStr">
         <is>
-          <t>[첫 싱글 'STUNing' 발매 2026.10.2 · 애니 '우주아이돌리그' 주제곡(OST)·성우 기반 IP라 아이돌 데뷔 판정 보류] (데일리한국 2026.10.27) 밀리언볼트 2D 버추얼 아이돌 IP '우주아이돌리그'(152개 행성 서바이벌 설정). 웹소설 2026.9.10 카카오페이지 연재. 캐릭터 콘텐츠 누적 2,000만뷰. 발매 확인 시 상태 재판정. (톱셀럽 2026.9.12)</t>
+          <t>[정식 데뷔 · 2026.10.2 첫 싱글 'STUNing'] 애니 '우주아이돌리그' 주제곡 겸 데뷔곡, 성우 기반 2D 버추얼 아이돌 IP. (데일리한국 2026.10.27) (데일리한국 2026.10.27) 밀리언볼트 2D 버추얼 아이돌 IP '우주아이돌리그'(152개 행성 서바이벌 설정). 웹소설 2026.9.10 카카오페이지 연재. 캐릭터 콘텐츠 누적 2,000만뷰. 발매 확인 시 상태 재판정. (톱셀럽 2026.9.12)</t>
         </is>
       </c>
     </row>
@@ -7205,6 +7205,86 @@
       <c r="H158" s="66" t="inlineStr">
         <is>
           <t>[프리데뷔 · 2026.10.7 'Weirdo' · 정식 데뷔 2027 상반기 예정] 5인조 K-POP 버추얼 아이돌(레빈·아토·타쿠미·렌·키로; MAKO는 마스코트 불독). 기획 단계부터 미국 핵심 시장, 영어 중심 음악·콘텐츠(멤버 전원 네이티브급 영어). 도깨비·구미호 동양 판타지 × 미국 대중문화·스트리트 패션. 유니버설뮤직 코리아 유통. 자체 모션캡처·AI·CG로 VR 콘서트 구현. 정식 데뷔일 미확인. (전자신문 2026.10.7, 톱스타뉴스) (코리아중앙데일리 2026.10.7, 톱셀럽 2026.10)</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" s="112" t="n">
+        <v>156</v>
+      </c>
+      <c r="B159" s="113" t="inlineStr">
+        <is>
+          <t>WON</t>
+        </is>
+      </c>
+      <c r="C159" s="112" t="inlineStr">
+        <is>
+          <t>원</t>
+        </is>
+      </c>
+      <c r="D159" s="113" t="inlineStr">
+        <is>
+          <t>브이토피안(VTOPIAN)</t>
+        </is>
+      </c>
+      <c r="E159" s="112" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="F159" s="114" t="inlineStr">
+        <is>
+          <t>버추얼휴먼/솔로</t>
+        </is>
+      </c>
+      <c r="G159" s="115" t="inlineStr">
+        <is>
+          <t>데뷔전</t>
+        </is>
+      </c>
+      <c r="H159" s="66" t="inlineStr">
+        <is>
+          <t>[론칭 공개 · 2026.10.26 · 정식 데뷔일 미확인] 작곡가 조영수 프로듀싱 버추얼 가수. 소속사 유튜브 인터뷰 영상 끝에 외형과 라이브 한 소절 첫 공개, 프로모션 순차 공개 예정. (마이데일리 2026.10.26)</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" s="112" t="n">
+        <v>157</v>
+      </c>
+      <c r="B160" s="113" t="inlineStr">
+        <is>
+          <t>시유</t>
+        </is>
+      </c>
+      <c r="C160" s="112" t="inlineStr">
+        <is>
+          <t>SeeU</t>
+        </is>
+      </c>
+      <c r="D160" s="113" t="inlineStr">
+        <is>
+          <t>SBS A&amp;T</t>
+        </is>
+      </c>
+      <c r="E160" s="112" t="inlineStr">
+        <is>
+          <t>2011</t>
+        </is>
+      </c>
+      <c r="F160" s="114" t="inlineStr">
+        <is>
+          <t>버추얼휴먼/솔로</t>
+        </is>
+      </c>
+      <c r="G160" s="90" t="inlineStr">
+        <is>
+          <t>활동중</t>
+        </is>
+      </c>
+      <c r="H160" s="66" t="inlineStr">
+        <is>
+          <t>한국어 보컬로이드 버추얼 싱어. 2026.10.9 국산 가창 합성 엔진 'VOX Factory'로 새 보이스 공개, 장기 프로젝트 'SeeU Re'로 신곡·대표곡 재해석 순차 공개 예정. (bnt뉴스 2026.10.9)</t>
         </is>
       </c>
     </row>
@@ -8684,7 +8764,6 @@
         </is>
       </c>
     </row>
-    <row r="2"/>
     <row r="3" ht="15" customHeight="1" s="41">
       <c r="A3" s="71" t="inlineStr">
         <is>
@@ -8830,7 +8909,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:E21"/>
+  <dimension ref="A1:E22"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" customHeight="0" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="26" customWidth="1" style="40" min="1" max="1"/>
@@ -9384,6 +9463,33 @@
       <c r="E21" s="66" t="inlineStr">
         <is>
           <t>(2026.10.27 점검) 정식 데뷔 '내년 상반기' 예정(코리아중앙데일리 2026.10.7). 멤버 레빈·아토·타쿠미·렌·키로. 공식 유튜브 @hypeverse_world. | 5인조, 미국 시장 겨냥 영어 중심. 동양 판타지×미국 대중문화 컨셉. 유니버설뮤직 코리아 유통. (전자신문 2026.10.7)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="113" t="inlineStr">
+        <is>
+          <t>WON (원)</t>
+        </is>
+      </c>
+      <c r="B22" s="112" t="inlineStr">
+        <is>
+          <t>브이토피안(VTOPIAN)</t>
+        </is>
+      </c>
+      <c r="C22" s="113" t="inlineStr">
+        <is>
+          <t>론칭 공개(데뷔 전)</t>
+        </is>
+      </c>
+      <c r="D22" s="112" t="inlineStr">
+        <is>
+          <t>정식 데뷔일 미확인</t>
+        </is>
+      </c>
+      <c r="E22" s="66" t="inlineStr">
+        <is>
+          <t>조영수 프로듀싱 버추얼 가수, 2026.10.26 외형·라이브 한 소절 첫 공개. (마이데일리 2026.10.26)</t>
         </is>
       </c>
     </row>
@@ -12525,7 +12631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I11"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" style="41" min="1" max="1"/>
@@ -12670,12 +12776,12 @@
       </c>
       <c r="E6" s="99" t="inlineStr">
         <is>
-          <t>데뷔 예정</t>
+          <t>프리데뷔</t>
         </is>
       </c>
       <c r="F6" s="99" t="inlineStr">
         <is>
-          <t>2026.10 중순</t>
+          <t>2026.10.14 (프리데뷔)</t>
         </is>
       </c>
       <c r="G6" s="99" t="inlineStr">
@@ -12690,7 +12796,7 @@
       </c>
       <c r="I6" s="99" t="inlineStr">
         <is>
-          <t>뉴스1 2026.9.1 / 머니투데이 2026.9.9</t>
+          <t>뉴스1 2026.9.1 / 머니투데이 2026.9.9 / 한국경제 2026.10.8</t>
         </is>
       </c>
     </row>
@@ -12926,6 +13032,100 @@
       <c r="I11" s="99" t="inlineStr">
         <is>
           <t>톱셀럽 2026.8.26</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="99" t="inlineStr">
+        <is>
+          <t>루미나</t>
+        </is>
+      </c>
+      <c r="B12" s="99" t="inlineStr">
+        <is>
+          <t>LUMINA</t>
+        </is>
+      </c>
+      <c r="C12" s="99" t="inlineStr">
+        <is>
+          <t>삼성증권(자체 제작)</t>
+        </is>
+      </c>
+      <c r="D12" s="99" t="inlineStr">
+        <is>
+          <t>생성형 AI 걸그룹 4인</t>
+        </is>
+      </c>
+      <c r="E12" s="99" t="inlineStr">
+        <is>
+          <t>데뷔</t>
+        </is>
+      </c>
+      <c r="F12" s="99" t="inlineStr">
+        <is>
+          <t>2026.9</t>
+        </is>
+      </c>
+      <c r="G12" s="99" t="inlineStr">
+        <is>
+          <t>데뷔곡 'OVERRIDE' MV</t>
+        </is>
+      </c>
+      <c r="H12" s="99" t="inlineStr">
+        <is>
+          <t>증권사가 연예인 모델 대신 만든 AI 아이돌. MV 공개 약 한 달 만에 250만 뷰. 명부의 버튜버 그룹 루미나(Lumina, 2025 종료)와 다른 팀.</t>
+        </is>
+      </c>
+      <c r="I12" s="99" t="inlineStr">
+        <is>
+          <t>뉴시스 2026.10.21 / 스마트투데이</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="99" t="inlineStr">
+        <is>
+          <t>넥스뮤즈</t>
+        </is>
+      </c>
+      <c r="B13" s="99" t="inlineStr">
+        <is>
+          <t>NEXMUSE</t>
+        </is>
+      </c>
+      <c r="C13" s="99" t="inlineStr">
+        <is>
+          <t>AI아트 × 티그라운드</t>
+        </is>
+      </c>
+      <c r="D13" s="99" t="inlineStr">
+        <is>
+          <t>AI 아이돌·버추얼휴먼 프로젝트(24캐릭터)</t>
+        </is>
+      </c>
+      <c r="E13" s="99" t="inlineStr">
+        <is>
+          <t>프로젝트(공모전 단계)</t>
+        </is>
+      </c>
+      <c r="F13" s="99" t="inlineStr">
+        <is>
+          <t>미정</t>
+        </is>
+      </c>
+      <c r="G13" s="99" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H13" s="99" t="inlineStr">
+        <is>
+          <t>24명 AI 캐릭터 중 하나로 MV를 만드는 공모전(~2026.12.28), 입상작에 음원 발매·데뷔 기회. 그룹 데뷔 전 단계.</t>
+        </is>
+      </c>
+      <c r="I13" s="99" t="inlineStr">
+        <is>
+          <t>이데일리 2026.10.13</t>
         </is>
       </c>
     </row>
